--- a/BW_Scrap_RAM_Purchases.xlsx
+++ b/BW_Scrap_RAM_Purchases.xlsx
@@ -24,12 +24,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="56">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
   <si>
     <t xml:space="preserve">B&amp;W Scrap Yard – RAM Purchase Log</t>
   </si>
   <si>
-    <t xml:space="preserve">Fill in the yellow-header columns (A–K, P). Gray-header columns (L–O) calculate automatically. Row 4 is an example – overwrite or delete it.</t>
+    <t xml:space="preserve">Fill in the yellow-header columns (A–K, P). Gray-header columns (L–O) calculate automatically. Row 4 is an example – overwrite or delete it. Tip: if the yard weighs gaming (heat spreader) RAM separately, log it as its own row with the same Receipt #.</t>
   </si>
   <si>
     <t xml:space="preserve">Date</t>
@@ -78,6 +78,12 @@
   </si>
   <si>
     <t xml:space="preserve">Notes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed load incl. gaming RAM w/ aluminum heat spreaders (lower $/lb rate). Split unknown.</t>
   </si>
   <si>
     <t xml:space="preserve">RAM Purchase Summary</t>
@@ -135,9 +141,6 @@
   </si>
   <si>
     <t xml:space="preserve">DDR5</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Mixed</t>
   </si>
   <si>
     <t xml:space="preserve">Other</t>
@@ -774,7 +777,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="16"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="11"/>
@@ -783,7 +786,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="60"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -888,7 +891,9 @@
       </c>
       <c r="B5" s="7"/>
       <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
+      <c r="D5" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
@@ -916,7 +921,9 @@
         <f aca="false">IF(OR(J5="",L5="",L5=0),"",J5/L5)</f>
         <v/>
       </c>
-      <c r="P5" s="7"/>
+      <c r="P5" s="7" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="6"/>
@@ -15866,7 +15873,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:D503" type="list">
-      <formula1>"DIMM (Desktop),SODIMM (Laptop),Server (ECC/RDIMM),Mixed"</formula1>
+      <formula1>"DIMM (Desktop),Gaming DIMM (Heat Spreader),SODIMM (Laptop),Server (ECC/RDIMM),Mixed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K4:K503" type="list">
@@ -15901,12 +15908,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="B3" s="13" t="n">
         <f aca="false">COUNT(Purchases!J4:J503)</f>
@@ -15915,7 +15922,7 @@
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B4" s="14" t="n">
         <f aca="false">SUM(Purchases!J4:J503)</f>
@@ -15924,7 +15931,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="12" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="B5" s="15" t="n">
         <f aca="false">SUM(Purchases!H4:H503)</f>
@@ -15933,7 +15940,7 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="B6" s="16" t="n">
         <f aca="false">SUM(Purchases!I4:I503)</f>
@@ -15951,7 +15958,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="12" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="B8" s="14" t="n">
         <f aca="false">IF(B5=0,0,B4/B5)</f>
@@ -15960,7 +15967,7 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="B9" s="14" t="n">
         <f aca="false">IF(B6=0,0,B4/B6)</f>
@@ -15969,7 +15976,7 @@
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="12" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="B10" s="14" t="n">
         <f aca="false">IF(B7=0,0,B4/B7)</f>
@@ -15978,32 +15985,32 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B14" s="18" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C14" s="18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D14" s="18" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="F14" s="18" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="13" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="B15" s="13" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A15)</f>
@@ -16028,7 +16035,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="13" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="B16" s="13" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A16)</f>
@@ -16053,7 +16060,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="B17" s="13" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A17)</f>
@@ -16078,7 +16085,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B18" s="13" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A18)</f>
@@ -16103,7 +16110,7 @@
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>37</v>
+        <v>18</v>
       </c>
       <c r="B19" s="13" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A19)</f>
@@ -16128,7 +16135,7 @@
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="13" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B20" s="13" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A20)</f>
@@ -16153,18 +16160,18 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="17" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="19" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B24" s="20" t="n">
         <v>2026</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="19"/>
@@ -16172,23 +16179,23 @@
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="18" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="B25" s="18" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C25" s="18" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D25" s="18" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E25" s="19"/>
       <c r="F25" s="19"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="19" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B26" s="19" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,1,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,1+1,1))</f>
@@ -16207,7 +16214,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="19" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B27" s="19" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,2,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,2+1,1))</f>
@@ -16226,7 +16233,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B28" s="19" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,3,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,3+1,1))</f>
@@ -16245,7 +16252,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="19" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="B29" s="19" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,4,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,4+1,1))</f>
@@ -16264,7 +16271,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="19" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B30" s="19" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,5,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,5+1,1))</f>
@@ -16283,7 +16290,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="19" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B31" s="19" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,6,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,6+1,1))</f>
@@ -16302,7 +16309,7 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32" s="19" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,7,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,7+1,1))</f>
@@ -16321,7 +16328,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="19" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B33" s="19" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,8,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,8+1,1))</f>
@@ -16340,7 +16347,7 @@
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="19" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="B34" s="19" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,9,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,9+1,1))</f>
@@ -16359,7 +16366,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="19" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B35" s="19" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,10,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,10+1,1))</f>
@@ -16378,7 +16385,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="19" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="B36" s="19" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,11,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,11+1,1))</f>
@@ -16397,7 +16404,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="19" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B37" s="19" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,12,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,12+1,1))</f>
@@ -16416,7 +16423,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="23" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="B38" s="23" t="n">
         <f aca="false">SUM(B26:B37)</f>

--- a/BW_Scrap_RAM_Purchases.xlsx
+++ b/BW_Scrap_RAM_Purchases.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
   <si>
     <t xml:space="preserve">B&amp;W Scrap Yard – RAM Purchase Log</t>
   </si>
@@ -80,16 +80,31 @@
     <t xml:space="preserve">Notes</t>
   </si>
   <si>
-    <t xml:space="preserve">Mixed</t>
+    <t xml:space="preserve">Regular</t>
   </si>
   <si>
-    <t xml:space="preserve">Mixed load incl. gaming RAM w/ aluminum heat spreaders (lower $/lb rate). Split unknown.</t>
+    <t xml:space="preserve">All regular @ $70/lb.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTIMATE: Oct 17 total ($617.50 / 10 lbs) split using Oct 23 rates ($70 regular / $50 server-gaming).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Server/Gaming (Heat Spreader)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ESTIMATE: see row above.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">~3 lbs @ $70/lb (approximate weight per yard). Oct 23 total paid $915.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">$50/lb; weight calculated as ($915 - $210) / $50.</t>
   </si>
   <si>
     <t xml:space="preserve">RAM Purchase Summary</t>
   </si>
   <si>
-    <t xml:space="preserve">Total purchases</t>
+    <t xml:space="preserve">Line items logged</t>
   </si>
   <si>
     <t xml:space="preserve">Total spent</t>
@@ -113,6 +128,9 @@
     <t xml:space="preserve">By RAM Type</t>
   </si>
   <si>
+    <t xml:space="preserve">By Rate Category / Form Factor</t>
+  </si>
+  <si>
     <t xml:space="preserve">Type</t>
   </si>
   <si>
@@ -131,6 +149,15 @@
     <t xml:space="preserve">Avg $/Stick</t>
   </si>
   <si>
+    <t xml:space="preserve">Category</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Line Items</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Avg $/lb</t>
+  </si>
+  <si>
     <t xml:space="preserve">DDR2</t>
   </si>
   <si>
@@ -140,7 +167,16 @@
     <t xml:space="preserve">DDR4</t>
   </si>
   <si>
+    <t xml:space="preserve">DIMM (Desktop)</t>
+  </si>
+  <si>
     <t xml:space="preserve">DDR5</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SODIMM (Laptop)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mixed</t>
   </si>
   <si>
     <t xml:space="preserve">Other</t>
@@ -201,14 +237,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="7">
+  <numFmts count="9">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
-    <numFmt numFmtId="166" formatCode="0.00"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
     <numFmt numFmtId="167" formatCode="\$#,##0.00"/>
-    <numFmt numFmtId="168" formatCode="General"/>
-    <numFmt numFmtId="169" formatCode="#,##0"/>
-    <numFmt numFmtId="170" formatCode="#,##0.00"/>
+    <numFmt numFmtId="168" formatCode="0.00"/>
+    <numFmt numFmtId="169" formatCode="General"/>
+    <numFmt numFmtId="170" formatCode="#,##0"/>
+    <numFmt numFmtId="171" formatCode="#,##0.00"/>
+    <numFmt numFmtId="172" formatCode="\$#,##0.00"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -374,7 +412,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="31">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -423,11 +461,15 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -435,11 +477,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="169" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="170" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -447,7 +489,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -777,7 +839,7 @@
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="28"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="11"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="8" style="1" width="11"/>
@@ -786,7 +848,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="10"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="14" style="1" width="12"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="60"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="80"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -855,7 +917,9 @@
       </c>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
+      <c r="D4" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="E4" s="7"/>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
@@ -883,7 +947,9 @@
         <f aca="false">IF(OR(J4="",L4="",L4=0),"",J4/L4)</f>
         <v/>
       </c>
-      <c r="P4" s="7"/>
+      <c r="P4" s="7" t="s">
+        <v>19</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="6" t="n">
@@ -899,10 +965,10 @@
       <c r="G5" s="7"/>
       <c r="H5" s="7"/>
       <c r="I5" s="8" t="n">
-        <v>10</v>
+        <v>5.875</v>
       </c>
       <c r="J5" s="9" t="n">
-        <v>617.5</v>
+        <v>411.25</v>
       </c>
       <c r="K5" s="7"/>
       <c r="L5" s="10" t="str">
@@ -915,27 +981,35 @@
       </c>
       <c r="N5" s="11" t="n">
         <f aca="false">IF(OR(J5="",I5="",I5=0),"",J5/I5)</f>
-        <v>61.75</v>
+        <v>70</v>
       </c>
       <c r="O5" s="11" t="str">
         <f aca="false">IF(OR(J5="",L5="",L5=0),"",J5/L5)</f>
         <v/>
       </c>
       <c r="P5" s="7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="6"/>
+      <c r="A6" s="6" t="n">
+        <v>46312</v>
+      </c>
       <c r="B6" s="7"/>
       <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
+      <c r="D6" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="E6" s="7"/>
       <c r="F6" s="7"/>
       <c r="G6" s="7"/>
       <c r="H6" s="7"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="9"/>
+      <c r="I6" s="8" t="n">
+        <v>4.125</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>206.25</v>
+      </c>
       <c r="K6" s="7"/>
       <c r="L6" s="10" t="str">
         <f aca="false">IF(OR(E6="",H6=""),"",E6*H6)</f>
@@ -945,27 +1019,37 @@
         <f aca="false">IF(OR(J6="",H6="",H6=0),"",J6/H6)</f>
         <v/>
       </c>
-      <c r="N6" s="11" t="str">
+      <c r="N6" s="11" t="n">
         <f aca="false">IF(OR(J6="",I6="",I6=0),"",J6/I6)</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="O6" s="11" t="str">
         <f aca="false">IF(OR(J6="",L6="",L6=0),"",J6/L6)</f>
         <v/>
       </c>
-      <c r="P6" s="7"/>
+      <c r="P6" s="7" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6"/>
+      <c r="A7" s="6" t="n">
+        <v>46318</v>
+      </c>
       <c r="B7" s="7"/>
       <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
+      <c r="D7" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
       <c r="H7" s="7"/>
-      <c r="I7" s="8"/>
-      <c r="J7" s="9"/>
+      <c r="I7" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>210</v>
+      </c>
       <c r="K7" s="7"/>
       <c r="L7" s="10" t="str">
         <f aca="false">IF(OR(E7="",H7=""),"",E7*H7)</f>
@@ -975,27 +1059,37 @@
         <f aca="false">IF(OR(J7="",H7="",H7=0),"",J7/H7)</f>
         <v/>
       </c>
-      <c r="N7" s="11" t="str">
+      <c r="N7" s="11" t="n">
         <f aca="false">IF(OR(J7="",I7="",I7=0),"",J7/I7)</f>
-        <v/>
+        <v>70</v>
       </c>
       <c r="O7" s="11" t="str">
         <f aca="false">IF(OR(J7="",L7="",L7=0),"",J7/L7)</f>
         <v/>
       </c>
-      <c r="P7" s="7"/>
+      <c r="P7" s="7" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6"/>
+      <c r="A8" s="6" t="n">
+        <v>46318</v>
+      </c>
       <c r="B8" s="7"/>
       <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
+      <c r="D8" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
       <c r="G8" s="7"/>
       <c r="H8" s="7"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="9"/>
+      <c r="I8" s="8" t="n">
+        <v>14.1</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>705</v>
+      </c>
       <c r="K8" s="7"/>
       <c r="L8" s="10" t="str">
         <f aca="false">IF(OR(E8="",H8=""),"",E8*H8)</f>
@@ -1005,15 +1099,17 @@
         <f aca="false">IF(OR(J8="",H8="",H8=0),"",J8/H8)</f>
         <v/>
       </c>
-      <c r="N8" s="11" t="str">
+      <c r="N8" s="11" t="n">
         <f aca="false">IF(OR(J8="",I8="",I8=0),"",J8/I8)</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="O8" s="11" t="str">
         <f aca="false">IF(OR(J8="",L8="",L8=0),"",J8/L8)</f>
         <v/>
       </c>
-      <c r="P8" s="7"/>
+      <c r="P8" s="7" t="s">
+        <v>24</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="6"/>
@@ -1024,7 +1120,7 @@
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="8"/>
+      <c r="I9" s="12"/>
       <c r="J9" s="9"/>
       <c r="K9" s="7"/>
       <c r="L9" s="10" t="str">
@@ -1054,7 +1150,7 @@
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
-      <c r="I10" s="8"/>
+      <c r="I10" s="12"/>
       <c r="J10" s="9"/>
       <c r="K10" s="7"/>
       <c r="L10" s="10" t="str">
@@ -1084,7 +1180,7 @@
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
       <c r="H11" s="7"/>
-      <c r="I11" s="8"/>
+      <c r="I11" s="12"/>
       <c r="J11" s="9"/>
       <c r="K11" s="7"/>
       <c r="L11" s="10" t="str">
@@ -1114,7 +1210,7 @@
       <c r="F12" s="7"/>
       <c r="G12" s="7"/>
       <c r="H12" s="7"/>
-      <c r="I12" s="8"/>
+      <c r="I12" s="12"/>
       <c r="J12" s="9"/>
       <c r="K12" s="7"/>
       <c r="L12" s="10" t="str">
@@ -1144,7 +1240,7 @@
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
       <c r="H13" s="7"/>
-      <c r="I13" s="8"/>
+      <c r="I13" s="12"/>
       <c r="J13" s="9"/>
       <c r="K13" s="7"/>
       <c r="L13" s="10" t="str">
@@ -1174,7 +1270,7 @@
       <c r="F14" s="7"/>
       <c r="G14" s="7"/>
       <c r="H14" s="7"/>
-      <c r="I14" s="8"/>
+      <c r="I14" s="12"/>
       <c r="J14" s="9"/>
       <c r="K14" s="7"/>
       <c r="L14" s="10" t="str">
@@ -1204,7 +1300,7 @@
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
       <c r="H15" s="7"/>
-      <c r="I15" s="8"/>
+      <c r="I15" s="12"/>
       <c r="J15" s="9"/>
       <c r="K15" s="7"/>
       <c r="L15" s="10" t="str">
@@ -1234,7 +1330,7 @@
       <c r="F16" s="7"/>
       <c r="G16" s="7"/>
       <c r="H16" s="7"/>
-      <c r="I16" s="8"/>
+      <c r="I16" s="12"/>
       <c r="J16" s="9"/>
       <c r="K16" s="7"/>
       <c r="L16" s="10" t="str">
@@ -1264,7 +1360,7 @@
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
       <c r="H17" s="7"/>
-      <c r="I17" s="8"/>
+      <c r="I17" s="12"/>
       <c r="J17" s="9"/>
       <c r="K17" s="7"/>
       <c r="L17" s="10" t="str">
@@ -1294,7 +1390,7 @@
       <c r="F18" s="7"/>
       <c r="G18" s="7"/>
       <c r="H18" s="7"/>
-      <c r="I18" s="8"/>
+      <c r="I18" s="12"/>
       <c r="J18" s="9"/>
       <c r="K18" s="7"/>
       <c r="L18" s="10" t="str">
@@ -1324,7 +1420,7 @@
       <c r="F19" s="7"/>
       <c r="G19" s="7"/>
       <c r="H19" s="7"/>
-      <c r="I19" s="8"/>
+      <c r="I19" s="12"/>
       <c r="J19" s="9"/>
       <c r="K19" s="7"/>
       <c r="L19" s="10" t="str">
@@ -1354,7 +1450,7 @@
       <c r="F20" s="7"/>
       <c r="G20" s="7"/>
       <c r="H20" s="7"/>
-      <c r="I20" s="8"/>
+      <c r="I20" s="12"/>
       <c r="J20" s="9"/>
       <c r="K20" s="7"/>
       <c r="L20" s="10" t="str">
@@ -1384,7 +1480,7 @@
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
       <c r="H21" s="7"/>
-      <c r="I21" s="8"/>
+      <c r="I21" s="12"/>
       <c r="J21" s="9"/>
       <c r="K21" s="7"/>
       <c r="L21" s="10" t="str">
@@ -1414,7 +1510,7 @@
       <c r="F22" s="7"/>
       <c r="G22" s="7"/>
       <c r="H22" s="7"/>
-      <c r="I22" s="8"/>
+      <c r="I22" s="12"/>
       <c r="J22" s="9"/>
       <c r="K22" s="7"/>
       <c r="L22" s="10" t="str">
@@ -1444,7 +1540,7 @@
       <c r="F23" s="7"/>
       <c r="G23" s="7"/>
       <c r="H23" s="7"/>
-      <c r="I23" s="8"/>
+      <c r="I23" s="12"/>
       <c r="J23" s="9"/>
       <c r="K23" s="7"/>
       <c r="L23" s="10" t="str">
@@ -1474,7 +1570,7 @@
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
       <c r="H24" s="7"/>
-      <c r="I24" s="8"/>
+      <c r="I24" s="12"/>
       <c r="J24" s="9"/>
       <c r="K24" s="7"/>
       <c r="L24" s="10" t="str">
@@ -1504,7 +1600,7 @@
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
       <c r="H25" s="7"/>
-      <c r="I25" s="8"/>
+      <c r="I25" s="12"/>
       <c r="J25" s="9"/>
       <c r="K25" s="7"/>
       <c r="L25" s="10" t="str">
@@ -1534,7 +1630,7 @@
       <c r="F26" s="7"/>
       <c r="G26" s="7"/>
       <c r="H26" s="7"/>
-      <c r="I26" s="8"/>
+      <c r="I26" s="12"/>
       <c r="J26" s="9"/>
       <c r="K26" s="7"/>
       <c r="L26" s="10" t="str">
@@ -1564,7 +1660,7 @@
       <c r="F27" s="7"/>
       <c r="G27" s="7"/>
       <c r="H27" s="7"/>
-      <c r="I27" s="8"/>
+      <c r="I27" s="12"/>
       <c r="J27" s="9"/>
       <c r="K27" s="7"/>
       <c r="L27" s="10" t="str">
@@ -1594,7 +1690,7 @@
       <c r="F28" s="7"/>
       <c r="G28" s="7"/>
       <c r="H28" s="7"/>
-      <c r="I28" s="8"/>
+      <c r="I28" s="12"/>
       <c r="J28" s="9"/>
       <c r="K28" s="7"/>
       <c r="L28" s="10" t="str">
@@ -1624,7 +1720,7 @@
       <c r="F29" s="7"/>
       <c r="G29" s="7"/>
       <c r="H29" s="7"/>
-      <c r="I29" s="8"/>
+      <c r="I29" s="12"/>
       <c r="J29" s="9"/>
       <c r="K29" s="7"/>
       <c r="L29" s="10" t="str">
@@ -1654,7 +1750,7 @@
       <c r="F30" s="7"/>
       <c r="G30" s="7"/>
       <c r="H30" s="7"/>
-      <c r="I30" s="8"/>
+      <c r="I30" s="12"/>
       <c r="J30" s="9"/>
       <c r="K30" s="7"/>
       <c r="L30" s="10" t="str">
@@ -1684,7 +1780,7 @@
       <c r="F31" s="7"/>
       <c r="G31" s="7"/>
       <c r="H31" s="7"/>
-      <c r="I31" s="8"/>
+      <c r="I31" s="12"/>
       <c r="J31" s="9"/>
       <c r="K31" s="7"/>
       <c r="L31" s="10" t="str">
@@ -1714,7 +1810,7 @@
       <c r="F32" s="7"/>
       <c r="G32" s="7"/>
       <c r="H32" s="7"/>
-      <c r="I32" s="8"/>
+      <c r="I32" s="12"/>
       <c r="J32" s="9"/>
       <c r="K32" s="7"/>
       <c r="L32" s="10" t="str">
@@ -1744,7 +1840,7 @@
       <c r="F33" s="7"/>
       <c r="G33" s="7"/>
       <c r="H33" s="7"/>
-      <c r="I33" s="8"/>
+      <c r="I33" s="12"/>
       <c r="J33" s="9"/>
       <c r="K33" s="7"/>
       <c r="L33" s="10" t="str">
@@ -1774,7 +1870,7 @@
       <c r="F34" s="7"/>
       <c r="G34" s="7"/>
       <c r="H34" s="7"/>
-      <c r="I34" s="8"/>
+      <c r="I34" s="12"/>
       <c r="J34" s="9"/>
       <c r="K34" s="7"/>
       <c r="L34" s="10" t="str">
@@ -1804,7 +1900,7 @@
       <c r="F35" s="7"/>
       <c r="G35" s="7"/>
       <c r="H35" s="7"/>
-      <c r="I35" s="8"/>
+      <c r="I35" s="12"/>
       <c r="J35" s="9"/>
       <c r="K35" s="7"/>
       <c r="L35" s="10" t="str">
@@ -1834,7 +1930,7 @@
       <c r="F36" s="7"/>
       <c r="G36" s="7"/>
       <c r="H36" s="7"/>
-      <c r="I36" s="8"/>
+      <c r="I36" s="12"/>
       <c r="J36" s="9"/>
       <c r="K36" s="7"/>
       <c r="L36" s="10" t="str">
@@ -1864,7 +1960,7 @@
       <c r="F37" s="7"/>
       <c r="G37" s="7"/>
       <c r="H37" s="7"/>
-      <c r="I37" s="8"/>
+      <c r="I37" s="12"/>
       <c r="J37" s="9"/>
       <c r="K37" s="7"/>
       <c r="L37" s="10" t="str">
@@ -1894,7 +1990,7 @@
       <c r="F38" s="7"/>
       <c r="G38" s="7"/>
       <c r="H38" s="7"/>
-      <c r="I38" s="8"/>
+      <c r="I38" s="12"/>
       <c r="J38" s="9"/>
       <c r="K38" s="7"/>
       <c r="L38" s="10" t="str">
@@ -1924,7 +2020,7 @@
       <c r="F39" s="7"/>
       <c r="G39" s="7"/>
       <c r="H39" s="7"/>
-      <c r="I39" s="8"/>
+      <c r="I39" s="12"/>
       <c r="J39" s="9"/>
       <c r="K39" s="7"/>
       <c r="L39" s="10" t="str">
@@ -1954,7 +2050,7 @@
       <c r="F40" s="7"/>
       <c r="G40" s="7"/>
       <c r="H40" s="7"/>
-      <c r="I40" s="8"/>
+      <c r="I40" s="12"/>
       <c r="J40" s="9"/>
       <c r="K40" s="7"/>
       <c r="L40" s="10" t="str">
@@ -1984,7 +2080,7 @@
       <c r="F41" s="7"/>
       <c r="G41" s="7"/>
       <c r="H41" s="7"/>
-      <c r="I41" s="8"/>
+      <c r="I41" s="12"/>
       <c r="J41" s="9"/>
       <c r="K41" s="7"/>
       <c r="L41" s="10" t="str">
@@ -2014,7 +2110,7 @@
       <c r="F42" s="7"/>
       <c r="G42" s="7"/>
       <c r="H42" s="7"/>
-      <c r="I42" s="8"/>
+      <c r="I42" s="12"/>
       <c r="J42" s="9"/>
       <c r="K42" s="7"/>
       <c r="L42" s="10" t="str">
@@ -2044,7 +2140,7 @@
       <c r="F43" s="7"/>
       <c r="G43" s="7"/>
       <c r="H43" s="7"/>
-      <c r="I43" s="8"/>
+      <c r="I43" s="12"/>
       <c r="J43" s="9"/>
       <c r="K43" s="7"/>
       <c r="L43" s="10" t="str">
@@ -2074,7 +2170,7 @@
       <c r="F44" s="7"/>
       <c r="G44" s="7"/>
       <c r="H44" s="7"/>
-      <c r="I44" s="8"/>
+      <c r="I44" s="12"/>
       <c r="J44" s="9"/>
       <c r="K44" s="7"/>
       <c r="L44" s="10" t="str">
@@ -2104,7 +2200,7 @@
       <c r="F45" s="7"/>
       <c r="G45" s="7"/>
       <c r="H45" s="7"/>
-      <c r="I45" s="8"/>
+      <c r="I45" s="12"/>
       <c r="J45" s="9"/>
       <c r="K45" s="7"/>
       <c r="L45" s="10" t="str">
@@ -2134,7 +2230,7 @@
       <c r="F46" s="7"/>
       <c r="G46" s="7"/>
       <c r="H46" s="7"/>
-      <c r="I46" s="8"/>
+      <c r="I46" s="12"/>
       <c r="J46" s="9"/>
       <c r="K46" s="7"/>
       <c r="L46" s="10" t="str">
@@ -2164,7 +2260,7 @@
       <c r="F47" s="7"/>
       <c r="G47" s="7"/>
       <c r="H47" s="7"/>
-      <c r="I47" s="8"/>
+      <c r="I47" s="12"/>
       <c r="J47" s="9"/>
       <c r="K47" s="7"/>
       <c r="L47" s="10" t="str">
@@ -2194,7 +2290,7 @@
       <c r="F48" s="7"/>
       <c r="G48" s="7"/>
       <c r="H48" s="7"/>
-      <c r="I48" s="8"/>
+      <c r="I48" s="12"/>
       <c r="J48" s="9"/>
       <c r="K48" s="7"/>
       <c r="L48" s="10" t="str">
@@ -2224,7 +2320,7 @@
       <c r="F49" s="7"/>
       <c r="G49" s="7"/>
       <c r="H49" s="7"/>
-      <c r="I49" s="8"/>
+      <c r="I49" s="12"/>
       <c r="J49" s="9"/>
       <c r="K49" s="7"/>
       <c r="L49" s="10" t="str">
@@ -2254,7 +2350,7 @@
       <c r="F50" s="7"/>
       <c r="G50" s="7"/>
       <c r="H50" s="7"/>
-      <c r="I50" s="8"/>
+      <c r="I50" s="12"/>
       <c r="J50" s="9"/>
       <c r="K50" s="7"/>
       <c r="L50" s="10" t="str">
@@ -2284,7 +2380,7 @@
       <c r="F51" s="7"/>
       <c r="G51" s="7"/>
       <c r="H51" s="7"/>
-      <c r="I51" s="8"/>
+      <c r="I51" s="12"/>
       <c r="J51" s="9"/>
       <c r="K51" s="7"/>
       <c r="L51" s="10" t="str">
@@ -2314,7 +2410,7 @@
       <c r="F52" s="7"/>
       <c r="G52" s="7"/>
       <c r="H52" s="7"/>
-      <c r="I52" s="8"/>
+      <c r="I52" s="12"/>
       <c r="J52" s="9"/>
       <c r="K52" s="7"/>
       <c r="L52" s="10" t="str">
@@ -2344,7 +2440,7 @@
       <c r="F53" s="7"/>
       <c r="G53" s="7"/>
       <c r="H53" s="7"/>
-      <c r="I53" s="8"/>
+      <c r="I53" s="12"/>
       <c r="J53" s="9"/>
       <c r="K53" s="7"/>
       <c r="L53" s="10" t="str">
@@ -2374,7 +2470,7 @@
       <c r="F54" s="7"/>
       <c r="G54" s="7"/>
       <c r="H54" s="7"/>
-      <c r="I54" s="8"/>
+      <c r="I54" s="12"/>
       <c r="J54" s="9"/>
       <c r="K54" s="7"/>
       <c r="L54" s="10" t="str">
@@ -2404,7 +2500,7 @@
       <c r="F55" s="7"/>
       <c r="G55" s="7"/>
       <c r="H55" s="7"/>
-      <c r="I55" s="8"/>
+      <c r="I55" s="12"/>
       <c r="J55" s="9"/>
       <c r="K55" s="7"/>
       <c r="L55" s="10" t="str">
@@ -2434,7 +2530,7 @@
       <c r="F56" s="7"/>
       <c r="G56" s="7"/>
       <c r="H56" s="7"/>
-      <c r="I56" s="8"/>
+      <c r="I56" s="12"/>
       <c r="J56" s="9"/>
       <c r="K56" s="7"/>
       <c r="L56" s="10" t="str">
@@ -2464,7 +2560,7 @@
       <c r="F57" s="7"/>
       <c r="G57" s="7"/>
       <c r="H57" s="7"/>
-      <c r="I57" s="8"/>
+      <c r="I57" s="12"/>
       <c r="J57" s="9"/>
       <c r="K57" s="7"/>
       <c r="L57" s="10" t="str">
@@ -2494,7 +2590,7 @@
       <c r="F58" s="7"/>
       <c r="G58" s="7"/>
       <c r="H58" s="7"/>
-      <c r="I58" s="8"/>
+      <c r="I58" s="12"/>
       <c r="J58" s="9"/>
       <c r="K58" s="7"/>
       <c r="L58" s="10" t="str">
@@ -2524,7 +2620,7 @@
       <c r="F59" s="7"/>
       <c r="G59" s="7"/>
       <c r="H59" s="7"/>
-      <c r="I59" s="8"/>
+      <c r="I59" s="12"/>
       <c r="J59" s="9"/>
       <c r="K59" s="7"/>
       <c r="L59" s="10" t="str">
@@ -2554,7 +2650,7 @@
       <c r="F60" s="7"/>
       <c r="G60" s="7"/>
       <c r="H60" s="7"/>
-      <c r="I60" s="8"/>
+      <c r="I60" s="12"/>
       <c r="J60" s="9"/>
       <c r="K60" s="7"/>
       <c r="L60" s="10" t="str">
@@ -2584,7 +2680,7 @@
       <c r="F61" s="7"/>
       <c r="G61" s="7"/>
       <c r="H61" s="7"/>
-      <c r="I61" s="8"/>
+      <c r="I61" s="12"/>
       <c r="J61" s="9"/>
       <c r="K61" s="7"/>
       <c r="L61" s="10" t="str">
@@ -2614,7 +2710,7 @@
       <c r="F62" s="7"/>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
-      <c r="I62" s="8"/>
+      <c r="I62" s="12"/>
       <c r="J62" s="9"/>
       <c r="K62" s="7"/>
       <c r="L62" s="10" t="str">
@@ -2644,7 +2740,7 @@
       <c r="F63" s="7"/>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
-      <c r="I63" s="8"/>
+      <c r="I63" s="12"/>
       <c r="J63" s="9"/>
       <c r="K63" s="7"/>
       <c r="L63" s="10" t="str">
@@ -2674,7 +2770,7 @@
       <c r="F64" s="7"/>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
-      <c r="I64" s="8"/>
+      <c r="I64" s="12"/>
       <c r="J64" s="9"/>
       <c r="K64" s="7"/>
       <c r="L64" s="10" t="str">
@@ -2704,7 +2800,7 @@
       <c r="F65" s="7"/>
       <c r="G65" s="7"/>
       <c r="H65" s="7"/>
-      <c r="I65" s="8"/>
+      <c r="I65" s="12"/>
       <c r="J65" s="9"/>
       <c r="K65" s="7"/>
       <c r="L65" s="10" t="str">
@@ -2734,7 +2830,7 @@
       <c r="F66" s="7"/>
       <c r="G66" s="7"/>
       <c r="H66" s="7"/>
-      <c r="I66" s="8"/>
+      <c r="I66" s="12"/>
       <c r="J66" s="9"/>
       <c r="K66" s="7"/>
       <c r="L66" s="10" t="str">
@@ -2764,7 +2860,7 @@
       <c r="F67" s="7"/>
       <c r="G67" s="7"/>
       <c r="H67" s="7"/>
-      <c r="I67" s="8"/>
+      <c r="I67" s="12"/>
       <c r="J67" s="9"/>
       <c r="K67" s="7"/>
       <c r="L67" s="10" t="str">
@@ -2794,7 +2890,7 @@
       <c r="F68" s="7"/>
       <c r="G68" s="7"/>
       <c r="H68" s="7"/>
-      <c r="I68" s="8"/>
+      <c r="I68" s="12"/>
       <c r="J68" s="9"/>
       <c r="K68" s="7"/>
       <c r="L68" s="10" t="str">
@@ -2824,7 +2920,7 @@
       <c r="F69" s="7"/>
       <c r="G69" s="7"/>
       <c r="H69" s="7"/>
-      <c r="I69" s="8"/>
+      <c r="I69" s="12"/>
       <c r="J69" s="9"/>
       <c r="K69" s="7"/>
       <c r="L69" s="10" t="str">
@@ -2854,7 +2950,7 @@
       <c r="F70" s="7"/>
       <c r="G70" s="7"/>
       <c r="H70" s="7"/>
-      <c r="I70" s="8"/>
+      <c r="I70" s="12"/>
       <c r="J70" s="9"/>
       <c r="K70" s="7"/>
       <c r="L70" s="10" t="str">
@@ -2884,7 +2980,7 @@
       <c r="F71" s="7"/>
       <c r="G71" s="7"/>
       <c r="H71" s="7"/>
-      <c r="I71" s="8"/>
+      <c r="I71" s="12"/>
       <c r="J71" s="9"/>
       <c r="K71" s="7"/>
       <c r="L71" s="10" t="str">
@@ -2914,7 +3010,7 @@
       <c r="F72" s="7"/>
       <c r="G72" s="7"/>
       <c r="H72" s="7"/>
-      <c r="I72" s="8"/>
+      <c r="I72" s="12"/>
       <c r="J72" s="9"/>
       <c r="K72" s="7"/>
       <c r="L72" s="10" t="str">
@@ -2944,7 +3040,7 @@
       <c r="F73" s="7"/>
       <c r="G73" s="7"/>
       <c r="H73" s="7"/>
-      <c r="I73" s="8"/>
+      <c r="I73" s="12"/>
       <c r="J73" s="9"/>
       <c r="K73" s="7"/>
       <c r="L73" s="10" t="str">
@@ -2974,7 +3070,7 @@
       <c r="F74" s="7"/>
       <c r="G74" s="7"/>
       <c r="H74" s="7"/>
-      <c r="I74" s="8"/>
+      <c r="I74" s="12"/>
       <c r="J74" s="9"/>
       <c r="K74" s="7"/>
       <c r="L74" s="10" t="str">
@@ -3004,7 +3100,7 @@
       <c r="F75" s="7"/>
       <c r="G75" s="7"/>
       <c r="H75" s="7"/>
-      <c r="I75" s="8"/>
+      <c r="I75" s="12"/>
       <c r="J75" s="9"/>
       <c r="K75" s="7"/>
       <c r="L75" s="10" t="str">
@@ -3034,7 +3130,7 @@
       <c r="F76" s="7"/>
       <c r="G76" s="7"/>
       <c r="H76" s="7"/>
-      <c r="I76" s="8"/>
+      <c r="I76" s="12"/>
       <c r="J76" s="9"/>
       <c r="K76" s="7"/>
       <c r="L76" s="10" t="str">
@@ -3064,7 +3160,7 @@
       <c r="F77" s="7"/>
       <c r="G77" s="7"/>
       <c r="H77" s="7"/>
-      <c r="I77" s="8"/>
+      <c r="I77" s="12"/>
       <c r="J77" s="9"/>
       <c r="K77" s="7"/>
       <c r="L77" s="10" t="str">
@@ -3094,7 +3190,7 @@
       <c r="F78" s="7"/>
       <c r="G78" s="7"/>
       <c r="H78" s="7"/>
-      <c r="I78" s="8"/>
+      <c r="I78" s="12"/>
       <c r="J78" s="9"/>
       <c r="K78" s="7"/>
       <c r="L78" s="10" t="str">
@@ -3124,7 +3220,7 @@
       <c r="F79" s="7"/>
       <c r="G79" s="7"/>
       <c r="H79" s="7"/>
-      <c r="I79" s="8"/>
+      <c r="I79" s="12"/>
       <c r="J79" s="9"/>
       <c r="K79" s="7"/>
       <c r="L79" s="10" t="str">
@@ -3154,7 +3250,7 @@
       <c r="F80" s="7"/>
       <c r="G80" s="7"/>
       <c r="H80" s="7"/>
-      <c r="I80" s="8"/>
+      <c r="I80" s="12"/>
       <c r="J80" s="9"/>
       <c r="K80" s="7"/>
       <c r="L80" s="10" t="str">
@@ -3184,7 +3280,7 @@
       <c r="F81" s="7"/>
       <c r="G81" s="7"/>
       <c r="H81" s="7"/>
-      <c r="I81" s="8"/>
+      <c r="I81" s="12"/>
       <c r="J81" s="9"/>
       <c r="K81" s="7"/>
       <c r="L81" s="10" t="str">
@@ -3214,7 +3310,7 @@
       <c r="F82" s="7"/>
       <c r="G82" s="7"/>
       <c r="H82" s="7"/>
-      <c r="I82" s="8"/>
+      <c r="I82" s="12"/>
       <c r="J82" s="9"/>
       <c r="K82" s="7"/>
       <c r="L82" s="10" t="str">
@@ -3244,7 +3340,7 @@
       <c r="F83" s="7"/>
       <c r="G83" s="7"/>
       <c r="H83" s="7"/>
-      <c r="I83" s="8"/>
+      <c r="I83" s="12"/>
       <c r="J83" s="9"/>
       <c r="K83" s="7"/>
       <c r="L83" s="10" t="str">
@@ -3274,7 +3370,7 @@
       <c r="F84" s="7"/>
       <c r="G84" s="7"/>
       <c r="H84" s="7"/>
-      <c r="I84" s="8"/>
+      <c r="I84" s="12"/>
       <c r="J84" s="9"/>
       <c r="K84" s="7"/>
       <c r="L84" s="10" t="str">
@@ -3304,7 +3400,7 @@
       <c r="F85" s="7"/>
       <c r="G85" s="7"/>
       <c r="H85" s="7"/>
-      <c r="I85" s="8"/>
+      <c r="I85" s="12"/>
       <c r="J85" s="9"/>
       <c r="K85" s="7"/>
       <c r="L85" s="10" t="str">
@@ -3334,7 +3430,7 @@
       <c r="F86" s="7"/>
       <c r="G86" s="7"/>
       <c r="H86" s="7"/>
-      <c r="I86" s="8"/>
+      <c r="I86" s="12"/>
       <c r="J86" s="9"/>
       <c r="K86" s="7"/>
       <c r="L86" s="10" t="str">
@@ -3364,7 +3460,7 @@
       <c r="F87" s="7"/>
       <c r="G87" s="7"/>
       <c r="H87" s="7"/>
-      <c r="I87" s="8"/>
+      <c r="I87" s="12"/>
       <c r="J87" s="9"/>
       <c r="K87" s="7"/>
       <c r="L87" s="10" t="str">
@@ -3394,7 +3490,7 @@
       <c r="F88" s="7"/>
       <c r="G88" s="7"/>
       <c r="H88" s="7"/>
-      <c r="I88" s="8"/>
+      <c r="I88" s="12"/>
       <c r="J88" s="9"/>
       <c r="K88" s="7"/>
       <c r="L88" s="10" t="str">
@@ -3424,7 +3520,7 @@
       <c r="F89" s="7"/>
       <c r="G89" s="7"/>
       <c r="H89" s="7"/>
-      <c r="I89" s="8"/>
+      <c r="I89" s="12"/>
       <c r="J89" s="9"/>
       <c r="K89" s="7"/>
       <c r="L89" s="10" t="str">
@@ -3454,7 +3550,7 @@
       <c r="F90" s="7"/>
       <c r="G90" s="7"/>
       <c r="H90" s="7"/>
-      <c r="I90" s="8"/>
+      <c r="I90" s="12"/>
       <c r="J90" s="9"/>
       <c r="K90" s="7"/>
       <c r="L90" s="10" t="str">
@@ -3484,7 +3580,7 @@
       <c r="F91" s="7"/>
       <c r="G91" s="7"/>
       <c r="H91" s="7"/>
-      <c r="I91" s="8"/>
+      <c r="I91" s="12"/>
       <c r="J91" s="9"/>
       <c r="K91" s="7"/>
       <c r="L91" s="10" t="str">
@@ -3514,7 +3610,7 @@
       <c r="F92" s="7"/>
       <c r="G92" s="7"/>
       <c r="H92" s="7"/>
-      <c r="I92" s="8"/>
+      <c r="I92" s="12"/>
       <c r="J92" s="9"/>
       <c r="K92" s="7"/>
       <c r="L92" s="10" t="str">
@@ -3544,7 +3640,7 @@
       <c r="F93" s="7"/>
       <c r="G93" s="7"/>
       <c r="H93" s="7"/>
-      <c r="I93" s="8"/>
+      <c r="I93" s="12"/>
       <c r="J93" s="9"/>
       <c r="K93" s="7"/>
       <c r="L93" s="10" t="str">
@@ -3574,7 +3670,7 @@
       <c r="F94" s="7"/>
       <c r="G94" s="7"/>
       <c r="H94" s="7"/>
-      <c r="I94" s="8"/>
+      <c r="I94" s="12"/>
       <c r="J94" s="9"/>
       <c r="K94" s="7"/>
       <c r="L94" s="10" t="str">
@@ -3604,7 +3700,7 @@
       <c r="F95" s="7"/>
       <c r="G95" s="7"/>
       <c r="H95" s="7"/>
-      <c r="I95" s="8"/>
+      <c r="I95" s="12"/>
       <c r="J95" s="9"/>
       <c r="K95" s="7"/>
       <c r="L95" s="10" t="str">
@@ -3634,7 +3730,7 @@
       <c r="F96" s="7"/>
       <c r="G96" s="7"/>
       <c r="H96" s="7"/>
-      <c r="I96" s="8"/>
+      <c r="I96" s="12"/>
       <c r="J96" s="9"/>
       <c r="K96" s="7"/>
       <c r="L96" s="10" t="str">
@@ -3664,7 +3760,7 @@
       <c r="F97" s="7"/>
       <c r="G97" s="7"/>
       <c r="H97" s="7"/>
-      <c r="I97" s="8"/>
+      <c r="I97" s="12"/>
       <c r="J97" s="9"/>
       <c r="K97" s="7"/>
       <c r="L97" s="10" t="str">
@@ -3694,7 +3790,7 @@
       <c r="F98" s="7"/>
       <c r="G98" s="7"/>
       <c r="H98" s="7"/>
-      <c r="I98" s="8"/>
+      <c r="I98" s="12"/>
       <c r="J98" s="9"/>
       <c r="K98" s="7"/>
       <c r="L98" s="10" t="str">
@@ -3724,7 +3820,7 @@
       <c r="F99" s="7"/>
       <c r="G99" s="7"/>
       <c r="H99" s="7"/>
-      <c r="I99" s="8"/>
+      <c r="I99" s="12"/>
       <c r="J99" s="9"/>
       <c r="K99" s="7"/>
       <c r="L99" s="10" t="str">
@@ -3754,7 +3850,7 @@
       <c r="F100" s="7"/>
       <c r="G100" s="7"/>
       <c r="H100" s="7"/>
-      <c r="I100" s="8"/>
+      <c r="I100" s="12"/>
       <c r="J100" s="9"/>
       <c r="K100" s="7"/>
       <c r="L100" s="10" t="str">
@@ -3784,7 +3880,7 @@
       <c r="F101" s="7"/>
       <c r="G101" s="7"/>
       <c r="H101" s="7"/>
-      <c r="I101" s="8"/>
+      <c r="I101" s="12"/>
       <c r="J101" s="9"/>
       <c r="K101" s="7"/>
       <c r="L101" s="10" t="str">
@@ -3814,7 +3910,7 @@
       <c r="F102" s="7"/>
       <c r="G102" s="7"/>
       <c r="H102" s="7"/>
-      <c r="I102" s="8"/>
+      <c r="I102" s="12"/>
       <c r="J102" s="9"/>
       <c r="K102" s="7"/>
       <c r="L102" s="10" t="str">
@@ -3844,7 +3940,7 @@
       <c r="F103" s="7"/>
       <c r="G103" s="7"/>
       <c r="H103" s="7"/>
-      <c r="I103" s="8"/>
+      <c r="I103" s="12"/>
       <c r="J103" s="9"/>
       <c r="K103" s="7"/>
       <c r="L103" s="10" t="str">
@@ -3874,7 +3970,7 @@
       <c r="F104" s="7"/>
       <c r="G104" s="7"/>
       <c r="H104" s="7"/>
-      <c r="I104" s="8"/>
+      <c r="I104" s="12"/>
       <c r="J104" s="9"/>
       <c r="K104" s="7"/>
       <c r="L104" s="10" t="str">
@@ -3904,7 +4000,7 @@
       <c r="F105" s="7"/>
       <c r="G105" s="7"/>
       <c r="H105" s="7"/>
-      <c r="I105" s="8"/>
+      <c r="I105" s="12"/>
       <c r="J105" s="9"/>
       <c r="K105" s="7"/>
       <c r="L105" s="10" t="str">
@@ -3934,7 +4030,7 @@
       <c r="F106" s="7"/>
       <c r="G106" s="7"/>
       <c r="H106" s="7"/>
-      <c r="I106" s="8"/>
+      <c r="I106" s="12"/>
       <c r="J106" s="9"/>
       <c r="K106" s="7"/>
       <c r="L106" s="10" t="str">
@@ -3964,7 +4060,7 @@
       <c r="F107" s="7"/>
       <c r="G107" s="7"/>
       <c r="H107" s="7"/>
-      <c r="I107" s="8"/>
+      <c r="I107" s="12"/>
       <c r="J107" s="9"/>
       <c r="K107" s="7"/>
       <c r="L107" s="10" t="str">
@@ -3994,7 +4090,7 @@
       <c r="F108" s="7"/>
       <c r="G108" s="7"/>
       <c r="H108" s="7"/>
-      <c r="I108" s="8"/>
+      <c r="I108" s="12"/>
       <c r="J108" s="9"/>
       <c r="K108" s="7"/>
       <c r="L108" s="10" t="str">
@@ -4024,7 +4120,7 @@
       <c r="F109" s="7"/>
       <c r="G109" s="7"/>
       <c r="H109" s="7"/>
-      <c r="I109" s="8"/>
+      <c r="I109" s="12"/>
       <c r="J109" s="9"/>
       <c r="K109" s="7"/>
       <c r="L109" s="10" t="str">
@@ -4054,7 +4150,7 @@
       <c r="F110" s="7"/>
       <c r="G110" s="7"/>
       <c r="H110" s="7"/>
-      <c r="I110" s="8"/>
+      <c r="I110" s="12"/>
       <c r="J110" s="9"/>
       <c r="K110" s="7"/>
       <c r="L110" s="10" t="str">
@@ -4084,7 +4180,7 @@
       <c r="F111" s="7"/>
       <c r="G111" s="7"/>
       <c r="H111" s="7"/>
-      <c r="I111" s="8"/>
+      <c r="I111" s="12"/>
       <c r="J111" s="9"/>
       <c r="K111" s="7"/>
       <c r="L111" s="10" t="str">
@@ -4114,7 +4210,7 @@
       <c r="F112" s="7"/>
       <c r="G112" s="7"/>
       <c r="H112" s="7"/>
-      <c r="I112" s="8"/>
+      <c r="I112" s="12"/>
       <c r="J112" s="9"/>
       <c r="K112" s="7"/>
       <c r="L112" s="10" t="str">
@@ -4144,7 +4240,7 @@
       <c r="F113" s="7"/>
       <c r="G113" s="7"/>
       <c r="H113" s="7"/>
-      <c r="I113" s="8"/>
+      <c r="I113" s="12"/>
       <c r="J113" s="9"/>
       <c r="K113" s="7"/>
       <c r="L113" s="10" t="str">
@@ -4174,7 +4270,7 @@
       <c r="F114" s="7"/>
       <c r="G114" s="7"/>
       <c r="H114" s="7"/>
-      <c r="I114" s="8"/>
+      <c r="I114" s="12"/>
       <c r="J114" s="9"/>
       <c r="K114" s="7"/>
       <c r="L114" s="10" t="str">
@@ -4204,7 +4300,7 @@
       <c r="F115" s="7"/>
       <c r="G115" s="7"/>
       <c r="H115" s="7"/>
-      <c r="I115" s="8"/>
+      <c r="I115" s="12"/>
       <c r="J115" s="9"/>
       <c r="K115" s="7"/>
       <c r="L115" s="10" t="str">
@@ -4234,7 +4330,7 @@
       <c r="F116" s="7"/>
       <c r="G116" s="7"/>
       <c r="H116" s="7"/>
-      <c r="I116" s="8"/>
+      <c r="I116" s="12"/>
       <c r="J116" s="9"/>
       <c r="K116" s="7"/>
       <c r="L116" s="10" t="str">
@@ -4264,7 +4360,7 @@
       <c r="F117" s="7"/>
       <c r="G117" s="7"/>
       <c r="H117" s="7"/>
-      <c r="I117" s="8"/>
+      <c r="I117" s="12"/>
       <c r="J117" s="9"/>
       <c r="K117" s="7"/>
       <c r="L117" s="10" t="str">
@@ -4294,7 +4390,7 @@
       <c r="F118" s="7"/>
       <c r="G118" s="7"/>
       <c r="H118" s="7"/>
-      <c r="I118" s="8"/>
+      <c r="I118" s="12"/>
       <c r="J118" s="9"/>
       <c r="K118" s="7"/>
       <c r="L118" s="10" t="str">
@@ -4324,7 +4420,7 @@
       <c r="F119" s="7"/>
       <c r="G119" s="7"/>
       <c r="H119" s="7"/>
-      <c r="I119" s="8"/>
+      <c r="I119" s="12"/>
       <c r="J119" s="9"/>
       <c r="K119" s="7"/>
       <c r="L119" s="10" t="str">
@@ -4354,7 +4450,7 @@
       <c r="F120" s="7"/>
       <c r="G120" s="7"/>
       <c r="H120" s="7"/>
-      <c r="I120" s="8"/>
+      <c r="I120" s="12"/>
       <c r="J120" s="9"/>
       <c r="K120" s="7"/>
       <c r="L120" s="10" t="str">
@@ -4384,7 +4480,7 @@
       <c r="F121" s="7"/>
       <c r="G121" s="7"/>
       <c r="H121" s="7"/>
-      <c r="I121" s="8"/>
+      <c r="I121" s="12"/>
       <c r="J121" s="9"/>
       <c r="K121" s="7"/>
       <c r="L121" s="10" t="str">
@@ -4414,7 +4510,7 @@
       <c r="F122" s="7"/>
       <c r="G122" s="7"/>
       <c r="H122" s="7"/>
-      <c r="I122" s="8"/>
+      <c r="I122" s="12"/>
       <c r="J122" s="9"/>
       <c r="K122" s="7"/>
       <c r="L122" s="10" t="str">
@@ -4444,7 +4540,7 @@
       <c r="F123" s="7"/>
       <c r="G123" s="7"/>
       <c r="H123" s="7"/>
-      <c r="I123" s="8"/>
+      <c r="I123" s="12"/>
       <c r="J123" s="9"/>
       <c r="K123" s="7"/>
       <c r="L123" s="10" t="str">
@@ -4474,7 +4570,7 @@
       <c r="F124" s="7"/>
       <c r="G124" s="7"/>
       <c r="H124" s="7"/>
-      <c r="I124" s="8"/>
+      <c r="I124" s="12"/>
       <c r="J124" s="9"/>
       <c r="K124" s="7"/>
       <c r="L124" s="10" t="str">
@@ -4504,7 +4600,7 @@
       <c r="F125" s="7"/>
       <c r="G125" s="7"/>
       <c r="H125" s="7"/>
-      <c r="I125" s="8"/>
+      <c r="I125" s="12"/>
       <c r="J125" s="9"/>
       <c r="K125" s="7"/>
       <c r="L125" s="10" t="str">
@@ -4534,7 +4630,7 @@
       <c r="F126" s="7"/>
       <c r="G126" s="7"/>
       <c r="H126" s="7"/>
-      <c r="I126" s="8"/>
+      <c r="I126" s="12"/>
       <c r="J126" s="9"/>
       <c r="K126" s="7"/>
       <c r="L126" s="10" t="str">
@@ -4564,7 +4660,7 @@
       <c r="F127" s="7"/>
       <c r="G127" s="7"/>
       <c r="H127" s="7"/>
-      <c r="I127" s="8"/>
+      <c r="I127" s="12"/>
       <c r="J127" s="9"/>
       <c r="K127" s="7"/>
       <c r="L127" s="10" t="str">
@@ -4594,7 +4690,7 @@
       <c r="F128" s="7"/>
       <c r="G128" s="7"/>
       <c r="H128" s="7"/>
-      <c r="I128" s="8"/>
+      <c r="I128" s="12"/>
       <c r="J128" s="9"/>
       <c r="K128" s="7"/>
       <c r="L128" s="10" t="str">
@@ -4624,7 +4720,7 @@
       <c r="F129" s="7"/>
       <c r="G129" s="7"/>
       <c r="H129" s="7"/>
-      <c r="I129" s="8"/>
+      <c r="I129" s="12"/>
       <c r="J129" s="9"/>
       <c r="K129" s="7"/>
       <c r="L129" s="10" t="str">
@@ -4654,7 +4750,7 @@
       <c r="F130" s="7"/>
       <c r="G130" s="7"/>
       <c r="H130" s="7"/>
-      <c r="I130" s="8"/>
+      <c r="I130" s="12"/>
       <c r="J130" s="9"/>
       <c r="K130" s="7"/>
       <c r="L130" s="10" t="str">
@@ -4684,7 +4780,7 @@
       <c r="F131" s="7"/>
       <c r="G131" s="7"/>
       <c r="H131" s="7"/>
-      <c r="I131" s="8"/>
+      <c r="I131" s="12"/>
       <c r="J131" s="9"/>
       <c r="K131" s="7"/>
       <c r="L131" s="10" t="str">
@@ -4714,7 +4810,7 @@
       <c r="F132" s="7"/>
       <c r="G132" s="7"/>
       <c r="H132" s="7"/>
-      <c r="I132" s="8"/>
+      <c r="I132" s="12"/>
       <c r="J132" s="9"/>
       <c r="K132" s="7"/>
       <c r="L132" s="10" t="str">
@@ -4744,7 +4840,7 @@
       <c r="F133" s="7"/>
       <c r="G133" s="7"/>
       <c r="H133" s="7"/>
-      <c r="I133" s="8"/>
+      <c r="I133" s="12"/>
       <c r="J133" s="9"/>
       <c r="K133" s="7"/>
       <c r="L133" s="10" t="str">
@@ -4774,7 +4870,7 @@
       <c r="F134" s="7"/>
       <c r="G134" s="7"/>
       <c r="H134" s="7"/>
-      <c r="I134" s="8"/>
+      <c r="I134" s="12"/>
       <c r="J134" s="9"/>
       <c r="K134" s="7"/>
       <c r="L134" s="10" t="str">
@@ -4804,7 +4900,7 @@
       <c r="F135" s="7"/>
       <c r="G135" s="7"/>
       <c r="H135" s="7"/>
-      <c r="I135" s="8"/>
+      <c r="I135" s="12"/>
       <c r="J135" s="9"/>
       <c r="K135" s="7"/>
       <c r="L135" s="10" t="str">
@@ -4834,7 +4930,7 @@
       <c r="F136" s="7"/>
       <c r="G136" s="7"/>
       <c r="H136" s="7"/>
-      <c r="I136" s="8"/>
+      <c r="I136" s="12"/>
       <c r="J136" s="9"/>
       <c r="K136" s="7"/>
       <c r="L136" s="10" t="str">
@@ -4864,7 +4960,7 @@
       <c r="F137" s="7"/>
       <c r="G137" s="7"/>
       <c r="H137" s="7"/>
-      <c r="I137" s="8"/>
+      <c r="I137" s="12"/>
       <c r="J137" s="9"/>
       <c r="K137" s="7"/>
       <c r="L137" s="10" t="str">
@@ -4894,7 +4990,7 @@
       <c r="F138" s="7"/>
       <c r="G138" s="7"/>
       <c r="H138" s="7"/>
-      <c r="I138" s="8"/>
+      <c r="I138" s="12"/>
       <c r="J138" s="9"/>
       <c r="K138" s="7"/>
       <c r="L138" s="10" t="str">
@@ -4924,7 +5020,7 @@
       <c r="F139" s="7"/>
       <c r="G139" s="7"/>
       <c r="H139" s="7"/>
-      <c r="I139" s="8"/>
+      <c r="I139" s="12"/>
       <c r="J139" s="9"/>
       <c r="K139" s="7"/>
       <c r="L139" s="10" t="str">
@@ -4954,7 +5050,7 @@
       <c r="F140" s="7"/>
       <c r="G140" s="7"/>
       <c r="H140" s="7"/>
-      <c r="I140" s="8"/>
+      <c r="I140" s="12"/>
       <c r="J140" s="9"/>
       <c r="K140" s="7"/>
       <c r="L140" s="10" t="str">
@@ -4984,7 +5080,7 @@
       <c r="F141" s="7"/>
       <c r="G141" s="7"/>
       <c r="H141" s="7"/>
-      <c r="I141" s="8"/>
+      <c r="I141" s="12"/>
       <c r="J141" s="9"/>
       <c r="K141" s="7"/>
       <c r="L141" s="10" t="str">
@@ -5014,7 +5110,7 @@
       <c r="F142" s="7"/>
       <c r="G142" s="7"/>
       <c r="H142" s="7"/>
-      <c r="I142" s="8"/>
+      <c r="I142" s="12"/>
       <c r="J142" s="9"/>
       <c r="K142" s="7"/>
       <c r="L142" s="10" t="str">
@@ -5044,7 +5140,7 @@
       <c r="F143" s="7"/>
       <c r="G143" s="7"/>
       <c r="H143" s="7"/>
-      <c r="I143" s="8"/>
+      <c r="I143" s="12"/>
       <c r="J143" s="9"/>
       <c r="K143" s="7"/>
       <c r="L143" s="10" t="str">
@@ -5074,7 +5170,7 @@
       <c r="F144" s="7"/>
       <c r="G144" s="7"/>
       <c r="H144" s="7"/>
-      <c r="I144" s="8"/>
+      <c r="I144" s="12"/>
       <c r="J144" s="9"/>
       <c r="K144" s="7"/>
       <c r="L144" s="10" t="str">
@@ -5104,7 +5200,7 @@
       <c r="F145" s="7"/>
       <c r="G145" s="7"/>
       <c r="H145" s="7"/>
-      <c r="I145" s="8"/>
+      <c r="I145" s="12"/>
       <c r="J145" s="9"/>
       <c r="K145" s="7"/>
       <c r="L145" s="10" t="str">
@@ -5134,7 +5230,7 @@
       <c r="F146" s="7"/>
       <c r="G146" s="7"/>
       <c r="H146" s="7"/>
-      <c r="I146" s="8"/>
+      <c r="I146" s="12"/>
       <c r="J146" s="9"/>
       <c r="K146" s="7"/>
       <c r="L146" s="10" t="str">
@@ -5164,7 +5260,7 @@
       <c r="F147" s="7"/>
       <c r="G147" s="7"/>
       <c r="H147" s="7"/>
-      <c r="I147" s="8"/>
+      <c r="I147" s="12"/>
       <c r="J147" s="9"/>
       <c r="K147" s="7"/>
       <c r="L147" s="10" t="str">
@@ -5194,7 +5290,7 @@
       <c r="F148" s="7"/>
       <c r="G148" s="7"/>
       <c r="H148" s="7"/>
-      <c r="I148" s="8"/>
+      <c r="I148" s="12"/>
       <c r="J148" s="9"/>
       <c r="K148" s="7"/>
       <c r="L148" s="10" t="str">
@@ -5224,7 +5320,7 @@
       <c r="F149" s="7"/>
       <c r="G149" s="7"/>
       <c r="H149" s="7"/>
-      <c r="I149" s="8"/>
+      <c r="I149" s="12"/>
       <c r="J149" s="9"/>
       <c r="K149" s="7"/>
       <c r="L149" s="10" t="str">
@@ -5254,7 +5350,7 @@
       <c r="F150" s="7"/>
       <c r="G150" s="7"/>
       <c r="H150" s="7"/>
-      <c r="I150" s="8"/>
+      <c r="I150" s="12"/>
       <c r="J150" s="9"/>
       <c r="K150" s="7"/>
       <c r="L150" s="10" t="str">
@@ -5284,7 +5380,7 @@
       <c r="F151" s="7"/>
       <c r="G151" s="7"/>
       <c r="H151" s="7"/>
-      <c r="I151" s="8"/>
+      <c r="I151" s="12"/>
       <c r="J151" s="9"/>
       <c r="K151" s="7"/>
       <c r="L151" s="10" t="str">
@@ -5314,7 +5410,7 @@
       <c r="F152" s="7"/>
       <c r="G152" s="7"/>
       <c r="H152" s="7"/>
-      <c r="I152" s="8"/>
+      <c r="I152" s="12"/>
       <c r="J152" s="9"/>
       <c r="K152" s="7"/>
       <c r="L152" s="10" t="str">
@@ -5344,7 +5440,7 @@
       <c r="F153" s="7"/>
       <c r="G153" s="7"/>
       <c r="H153" s="7"/>
-      <c r="I153" s="8"/>
+      <c r="I153" s="12"/>
       <c r="J153" s="9"/>
       <c r="K153" s="7"/>
       <c r="L153" s="10" t="str">
@@ -5374,7 +5470,7 @@
       <c r="F154" s="7"/>
       <c r="G154" s="7"/>
       <c r="H154" s="7"/>
-      <c r="I154" s="8"/>
+      <c r="I154" s="12"/>
       <c r="J154" s="9"/>
       <c r="K154" s="7"/>
       <c r="L154" s="10" t="str">
@@ -5404,7 +5500,7 @@
       <c r="F155" s="7"/>
       <c r="G155" s="7"/>
       <c r="H155" s="7"/>
-      <c r="I155" s="8"/>
+      <c r="I155" s="12"/>
       <c r="J155" s="9"/>
       <c r="K155" s="7"/>
       <c r="L155" s="10" t="str">
@@ -5434,7 +5530,7 @@
       <c r="F156" s="7"/>
       <c r="G156" s="7"/>
       <c r="H156" s="7"/>
-      <c r="I156" s="8"/>
+      <c r="I156" s="12"/>
       <c r="J156" s="9"/>
       <c r="K156" s="7"/>
       <c r="L156" s="10" t="str">
@@ -5464,7 +5560,7 @@
       <c r="F157" s="7"/>
       <c r="G157" s="7"/>
       <c r="H157" s="7"/>
-      <c r="I157" s="8"/>
+      <c r="I157" s="12"/>
       <c r="J157" s="9"/>
       <c r="K157" s="7"/>
       <c r="L157" s="10" t="str">
@@ -5494,7 +5590,7 @@
       <c r="F158" s="7"/>
       <c r="G158" s="7"/>
       <c r="H158" s="7"/>
-      <c r="I158" s="8"/>
+      <c r="I158" s="12"/>
       <c r="J158" s="9"/>
       <c r="K158" s="7"/>
       <c r="L158" s="10" t="str">
@@ -5524,7 +5620,7 @@
       <c r="F159" s="7"/>
       <c r="G159" s="7"/>
       <c r="H159" s="7"/>
-      <c r="I159" s="8"/>
+      <c r="I159" s="12"/>
       <c r="J159" s="9"/>
       <c r="K159" s="7"/>
       <c r="L159" s="10" t="str">
@@ -5554,7 +5650,7 @@
       <c r="F160" s="7"/>
       <c r="G160" s="7"/>
       <c r="H160" s="7"/>
-      <c r="I160" s="8"/>
+      <c r="I160" s="12"/>
       <c r="J160" s="9"/>
       <c r="K160" s="7"/>
       <c r="L160" s="10" t="str">
@@ -5584,7 +5680,7 @@
       <c r="F161" s="7"/>
       <c r="G161" s="7"/>
       <c r="H161" s="7"/>
-      <c r="I161" s="8"/>
+      <c r="I161" s="12"/>
       <c r="J161" s="9"/>
       <c r="K161" s="7"/>
       <c r="L161" s="10" t="str">
@@ -5614,7 +5710,7 @@
       <c r="F162" s="7"/>
       <c r="G162" s="7"/>
       <c r="H162" s="7"/>
-      <c r="I162" s="8"/>
+      <c r="I162" s="12"/>
       <c r="J162" s="9"/>
       <c r="K162" s="7"/>
       <c r="L162" s="10" t="str">
@@ -5644,7 +5740,7 @@
       <c r="F163" s="7"/>
       <c r="G163" s="7"/>
       <c r="H163" s="7"/>
-      <c r="I163" s="8"/>
+      <c r="I163" s="12"/>
       <c r="J163" s="9"/>
       <c r="K163" s="7"/>
       <c r="L163" s="10" t="str">
@@ -5674,7 +5770,7 @@
       <c r="F164" s="7"/>
       <c r="G164" s="7"/>
       <c r="H164" s="7"/>
-      <c r="I164" s="8"/>
+      <c r="I164" s="12"/>
       <c r="J164" s="9"/>
       <c r="K164" s="7"/>
       <c r="L164" s="10" t="str">
@@ -5704,7 +5800,7 @@
       <c r="F165" s="7"/>
       <c r="G165" s="7"/>
       <c r="H165" s="7"/>
-      <c r="I165" s="8"/>
+      <c r="I165" s="12"/>
       <c r="J165" s="9"/>
       <c r="K165" s="7"/>
       <c r="L165" s="10" t="str">
@@ -5734,7 +5830,7 @@
       <c r="F166" s="7"/>
       <c r="G166" s="7"/>
       <c r="H166" s="7"/>
-      <c r="I166" s="8"/>
+      <c r="I166" s="12"/>
       <c r="J166" s="9"/>
       <c r="K166" s="7"/>
       <c r="L166" s="10" t="str">
@@ -5764,7 +5860,7 @@
       <c r="F167" s="7"/>
       <c r="G167" s="7"/>
       <c r="H167" s="7"/>
-      <c r="I167" s="8"/>
+      <c r="I167" s="12"/>
       <c r="J167" s="9"/>
       <c r="K167" s="7"/>
       <c r="L167" s="10" t="str">
@@ -5794,7 +5890,7 @@
       <c r="F168" s="7"/>
       <c r="G168" s="7"/>
       <c r="H168" s="7"/>
-      <c r="I168" s="8"/>
+      <c r="I168" s="12"/>
       <c r="J168" s="9"/>
       <c r="K168" s="7"/>
       <c r="L168" s="10" t="str">
@@ -5824,7 +5920,7 @@
       <c r="F169" s="7"/>
       <c r="G169" s="7"/>
       <c r="H169" s="7"/>
-      <c r="I169" s="8"/>
+      <c r="I169" s="12"/>
       <c r="J169" s="9"/>
       <c r="K169" s="7"/>
       <c r="L169" s="10" t="str">
@@ -5854,7 +5950,7 @@
       <c r="F170" s="7"/>
       <c r="G170" s="7"/>
       <c r="H170" s="7"/>
-      <c r="I170" s="8"/>
+      <c r="I170" s="12"/>
       <c r="J170" s="9"/>
       <c r="K170" s="7"/>
       <c r="L170" s="10" t="str">
@@ -5884,7 +5980,7 @@
       <c r="F171" s="7"/>
       <c r="G171" s="7"/>
       <c r="H171" s="7"/>
-      <c r="I171" s="8"/>
+      <c r="I171" s="12"/>
       <c r="J171" s="9"/>
       <c r="K171" s="7"/>
       <c r="L171" s="10" t="str">
@@ -5914,7 +6010,7 @@
       <c r="F172" s="7"/>
       <c r="G172" s="7"/>
       <c r="H172" s="7"/>
-      <c r="I172" s="8"/>
+      <c r="I172" s="12"/>
       <c r="J172" s="9"/>
       <c r="K172" s="7"/>
       <c r="L172" s="10" t="str">
@@ -5944,7 +6040,7 @@
       <c r="F173" s="7"/>
       <c r="G173" s="7"/>
       <c r="H173" s="7"/>
-      <c r="I173" s="8"/>
+      <c r="I173" s="12"/>
       <c r="J173" s="9"/>
       <c r="K173" s="7"/>
       <c r="L173" s="10" t="str">
@@ -5974,7 +6070,7 @@
       <c r="F174" s="7"/>
       <c r="G174" s="7"/>
       <c r="H174" s="7"/>
-      <c r="I174" s="8"/>
+      <c r="I174" s="12"/>
       <c r="J174" s="9"/>
       <c r="K174" s="7"/>
       <c r="L174" s="10" t="str">
@@ -6004,7 +6100,7 @@
       <c r="F175" s="7"/>
       <c r="G175" s="7"/>
       <c r="H175" s="7"/>
-      <c r="I175" s="8"/>
+      <c r="I175" s="12"/>
       <c r="J175" s="9"/>
       <c r="K175" s="7"/>
       <c r="L175" s="10" t="str">
@@ -6034,7 +6130,7 @@
       <c r="F176" s="7"/>
       <c r="G176" s="7"/>
       <c r="H176" s="7"/>
-      <c r="I176" s="8"/>
+      <c r="I176" s="12"/>
       <c r="J176" s="9"/>
       <c r="K176" s="7"/>
       <c r="L176" s="10" t="str">
@@ -6064,7 +6160,7 @@
       <c r="F177" s="7"/>
       <c r="G177" s="7"/>
       <c r="H177" s="7"/>
-      <c r="I177" s="8"/>
+      <c r="I177" s="12"/>
       <c r="J177" s="9"/>
       <c r="K177" s="7"/>
       <c r="L177" s="10" t="str">
@@ -6094,7 +6190,7 @@
       <c r="F178" s="7"/>
       <c r="G178" s="7"/>
       <c r="H178" s="7"/>
-      <c r="I178" s="8"/>
+      <c r="I178" s="12"/>
       <c r="J178" s="9"/>
       <c r="K178" s="7"/>
       <c r="L178" s="10" t="str">
@@ -6124,7 +6220,7 @@
       <c r="F179" s="7"/>
       <c r="G179" s="7"/>
       <c r="H179" s="7"/>
-      <c r="I179" s="8"/>
+      <c r="I179" s="12"/>
       <c r="J179" s="9"/>
       <c r="K179" s="7"/>
       <c r="L179" s="10" t="str">
@@ -6154,7 +6250,7 @@
       <c r="F180" s="7"/>
       <c r="G180" s="7"/>
       <c r="H180" s="7"/>
-      <c r="I180" s="8"/>
+      <c r="I180" s="12"/>
       <c r="J180" s="9"/>
       <c r="K180" s="7"/>
       <c r="L180" s="10" t="str">
@@ -6184,7 +6280,7 @@
       <c r="F181" s="7"/>
       <c r="G181" s="7"/>
       <c r="H181" s="7"/>
-      <c r="I181" s="8"/>
+      <c r="I181" s="12"/>
       <c r="J181" s="9"/>
       <c r="K181" s="7"/>
       <c r="L181" s="10" t="str">
@@ -6214,7 +6310,7 @@
       <c r="F182" s="7"/>
       <c r="G182" s="7"/>
       <c r="H182" s="7"/>
-      <c r="I182" s="8"/>
+      <c r="I182" s="12"/>
       <c r="J182" s="9"/>
       <c r="K182" s="7"/>
       <c r="L182" s="10" t="str">
@@ -6244,7 +6340,7 @@
       <c r="F183" s="7"/>
       <c r="G183" s="7"/>
       <c r="H183" s="7"/>
-      <c r="I183" s="8"/>
+      <c r="I183" s="12"/>
       <c r="J183" s="9"/>
       <c r="K183" s="7"/>
       <c r="L183" s="10" t="str">
@@ -6274,7 +6370,7 @@
       <c r="F184" s="7"/>
       <c r="G184" s="7"/>
       <c r="H184" s="7"/>
-      <c r="I184" s="8"/>
+      <c r="I184" s="12"/>
       <c r="J184" s="9"/>
       <c r="K184" s="7"/>
       <c r="L184" s="10" t="str">
@@ -6304,7 +6400,7 @@
       <c r="F185" s="7"/>
       <c r="G185" s="7"/>
       <c r="H185" s="7"/>
-      <c r="I185" s="8"/>
+      <c r="I185" s="12"/>
       <c r="J185" s="9"/>
       <c r="K185" s="7"/>
       <c r="L185" s="10" t="str">
@@ -6334,7 +6430,7 @@
       <c r="F186" s="7"/>
       <c r="G186" s="7"/>
       <c r="H186" s="7"/>
-      <c r="I186" s="8"/>
+      <c r="I186" s="12"/>
       <c r="J186" s="9"/>
       <c r="K186" s="7"/>
       <c r="L186" s="10" t="str">
@@ -6364,7 +6460,7 @@
       <c r="F187" s="7"/>
       <c r="G187" s="7"/>
       <c r="H187" s="7"/>
-      <c r="I187" s="8"/>
+      <c r="I187" s="12"/>
       <c r="J187" s="9"/>
       <c r="K187" s="7"/>
       <c r="L187" s="10" t="str">
@@ -6394,7 +6490,7 @@
       <c r="F188" s="7"/>
       <c r="G188" s="7"/>
       <c r="H188" s="7"/>
-      <c r="I188" s="8"/>
+      <c r="I188" s="12"/>
       <c r="J188" s="9"/>
       <c r="K188" s="7"/>
       <c r="L188" s="10" t="str">
@@ -6424,7 +6520,7 @@
       <c r="F189" s="7"/>
       <c r="G189" s="7"/>
       <c r="H189" s="7"/>
-      <c r="I189" s="8"/>
+      <c r="I189" s="12"/>
       <c r="J189" s="9"/>
       <c r="K189" s="7"/>
       <c r="L189" s="10" t="str">
@@ -6454,7 +6550,7 @@
       <c r="F190" s="7"/>
       <c r="G190" s="7"/>
       <c r="H190" s="7"/>
-      <c r="I190" s="8"/>
+      <c r="I190" s="12"/>
       <c r="J190" s="9"/>
       <c r="K190" s="7"/>
       <c r="L190" s="10" t="str">
@@ -6484,7 +6580,7 @@
       <c r="F191" s="7"/>
       <c r="G191" s="7"/>
       <c r="H191" s="7"/>
-      <c r="I191" s="8"/>
+      <c r="I191" s="12"/>
       <c r="J191" s="9"/>
       <c r="K191" s="7"/>
       <c r="L191" s="10" t="str">
@@ -6514,7 +6610,7 @@
       <c r="F192" s="7"/>
       <c r="G192" s="7"/>
       <c r="H192" s="7"/>
-      <c r="I192" s="8"/>
+      <c r="I192" s="12"/>
       <c r="J192" s="9"/>
       <c r="K192" s="7"/>
       <c r="L192" s="10" t="str">
@@ -6544,7 +6640,7 @@
       <c r="F193" s="7"/>
       <c r="G193" s="7"/>
       <c r="H193" s="7"/>
-      <c r="I193" s="8"/>
+      <c r="I193" s="12"/>
       <c r="J193" s="9"/>
       <c r="K193" s="7"/>
       <c r="L193" s="10" t="str">
@@ -6574,7 +6670,7 @@
       <c r="F194" s="7"/>
       <c r="G194" s="7"/>
       <c r="H194" s="7"/>
-      <c r="I194" s="8"/>
+      <c r="I194" s="12"/>
       <c r="J194" s="9"/>
       <c r="K194" s="7"/>
       <c r="L194" s="10" t="str">
@@ -6604,7 +6700,7 @@
       <c r="F195" s="7"/>
       <c r="G195" s="7"/>
       <c r="H195" s="7"/>
-      <c r="I195" s="8"/>
+      <c r="I195" s="12"/>
       <c r="J195" s="9"/>
       <c r="K195" s="7"/>
       <c r="L195" s="10" t="str">
@@ -6634,7 +6730,7 @@
       <c r="F196" s="7"/>
       <c r="G196" s="7"/>
       <c r="H196" s="7"/>
-      <c r="I196" s="8"/>
+      <c r="I196" s="12"/>
       <c r="J196" s="9"/>
       <c r="K196" s="7"/>
       <c r="L196" s="10" t="str">
@@ -6664,7 +6760,7 @@
       <c r="F197" s="7"/>
       <c r="G197" s="7"/>
       <c r="H197" s="7"/>
-      <c r="I197" s="8"/>
+      <c r="I197" s="12"/>
       <c r="J197" s="9"/>
       <c r="K197" s="7"/>
       <c r="L197" s="10" t="str">
@@ -6694,7 +6790,7 @@
       <c r="F198" s="7"/>
       <c r="G198" s="7"/>
       <c r="H198" s="7"/>
-      <c r="I198" s="8"/>
+      <c r="I198" s="12"/>
       <c r="J198" s="9"/>
       <c r="K198" s="7"/>
       <c r="L198" s="10" t="str">
@@ -6724,7 +6820,7 @@
       <c r="F199" s="7"/>
       <c r="G199" s="7"/>
       <c r="H199" s="7"/>
-      <c r="I199" s="8"/>
+      <c r="I199" s="12"/>
       <c r="J199" s="9"/>
       <c r="K199" s="7"/>
       <c r="L199" s="10" t="str">
@@ -6754,7 +6850,7 @@
       <c r="F200" s="7"/>
       <c r="G200" s="7"/>
       <c r="H200" s="7"/>
-      <c r="I200" s="8"/>
+      <c r="I200" s="12"/>
       <c r="J200" s="9"/>
       <c r="K200" s="7"/>
       <c r="L200" s="10" t="str">
@@ -6784,7 +6880,7 @@
       <c r="F201" s="7"/>
       <c r="G201" s="7"/>
       <c r="H201" s="7"/>
-      <c r="I201" s="8"/>
+      <c r="I201" s="12"/>
       <c r="J201" s="9"/>
       <c r="K201" s="7"/>
       <c r="L201" s="10" t="str">
@@ -6814,7 +6910,7 @@
       <c r="F202" s="7"/>
       <c r="G202" s="7"/>
       <c r="H202" s="7"/>
-      <c r="I202" s="8"/>
+      <c r="I202" s="12"/>
       <c r="J202" s="9"/>
       <c r="K202" s="7"/>
       <c r="L202" s="10" t="str">
@@ -6844,7 +6940,7 @@
       <c r="F203" s="7"/>
       <c r="G203" s="7"/>
       <c r="H203" s="7"/>
-      <c r="I203" s="8"/>
+      <c r="I203" s="12"/>
       <c r="J203" s="9"/>
       <c r="K203" s="7"/>
       <c r="L203" s="10" t="str">
@@ -6874,7 +6970,7 @@
       <c r="F204" s="7"/>
       <c r="G204" s="7"/>
       <c r="H204" s="7"/>
-      <c r="I204" s="8"/>
+      <c r="I204" s="12"/>
       <c r="J204" s="9"/>
       <c r="K204" s="7"/>
       <c r="L204" s="10" t="str">
@@ -6904,7 +7000,7 @@
       <c r="F205" s="7"/>
       <c r="G205" s="7"/>
       <c r="H205" s="7"/>
-      <c r="I205" s="8"/>
+      <c r="I205" s="12"/>
       <c r="J205" s="9"/>
       <c r="K205" s="7"/>
       <c r="L205" s="10" t="str">
@@ -6934,7 +7030,7 @@
       <c r="F206" s="7"/>
       <c r="G206" s="7"/>
       <c r="H206" s="7"/>
-      <c r="I206" s="8"/>
+      <c r="I206" s="12"/>
       <c r="J206" s="9"/>
       <c r="K206" s="7"/>
       <c r="L206" s="10" t="str">
@@ -6964,7 +7060,7 @@
       <c r="F207" s="7"/>
       <c r="G207" s="7"/>
       <c r="H207" s="7"/>
-      <c r="I207" s="8"/>
+      <c r="I207" s="12"/>
       <c r="J207" s="9"/>
       <c r="K207" s="7"/>
       <c r="L207" s="10" t="str">
@@ -6994,7 +7090,7 @@
       <c r="F208" s="7"/>
       <c r="G208" s="7"/>
       <c r="H208" s="7"/>
-      <c r="I208" s="8"/>
+      <c r="I208" s="12"/>
       <c r="J208" s="9"/>
       <c r="K208" s="7"/>
       <c r="L208" s="10" t="str">
@@ -7024,7 +7120,7 @@
       <c r="F209" s="7"/>
       <c r="G209" s="7"/>
       <c r="H209" s="7"/>
-      <c r="I209" s="8"/>
+      <c r="I209" s="12"/>
       <c r="J209" s="9"/>
       <c r="K209" s="7"/>
       <c r="L209" s="10" t="str">
@@ -7054,7 +7150,7 @@
       <c r="F210" s="7"/>
       <c r="G210" s="7"/>
       <c r="H210" s="7"/>
-      <c r="I210" s="8"/>
+      <c r="I210" s="12"/>
       <c r="J210" s="9"/>
       <c r="K210" s="7"/>
       <c r="L210" s="10" t="str">
@@ -7084,7 +7180,7 @@
       <c r="F211" s="7"/>
       <c r="G211" s="7"/>
       <c r="H211" s="7"/>
-      <c r="I211" s="8"/>
+      <c r="I211" s="12"/>
       <c r="J211" s="9"/>
       <c r="K211" s="7"/>
       <c r="L211" s="10" t="str">
@@ -7114,7 +7210,7 @@
       <c r="F212" s="7"/>
       <c r="G212" s="7"/>
       <c r="H212" s="7"/>
-      <c r="I212" s="8"/>
+      <c r="I212" s="12"/>
       <c r="J212" s="9"/>
       <c r="K212" s="7"/>
       <c r="L212" s="10" t="str">
@@ -7144,7 +7240,7 @@
       <c r="F213" s="7"/>
       <c r="G213" s="7"/>
       <c r="H213" s="7"/>
-      <c r="I213" s="8"/>
+      <c r="I213" s="12"/>
       <c r="J213" s="9"/>
       <c r="K213" s="7"/>
       <c r="L213" s="10" t="str">
@@ -7174,7 +7270,7 @@
       <c r="F214" s="7"/>
       <c r="G214" s="7"/>
       <c r="H214" s="7"/>
-      <c r="I214" s="8"/>
+      <c r="I214" s="12"/>
       <c r="J214" s="9"/>
       <c r="K214" s="7"/>
       <c r="L214" s="10" t="str">
@@ -7204,7 +7300,7 @@
       <c r="F215" s="7"/>
       <c r="G215" s="7"/>
       <c r="H215" s="7"/>
-      <c r="I215" s="8"/>
+      <c r="I215" s="12"/>
       <c r="J215" s="9"/>
       <c r="K215" s="7"/>
       <c r="L215" s="10" t="str">
@@ -7234,7 +7330,7 @@
       <c r="F216" s="7"/>
       <c r="G216" s="7"/>
       <c r="H216" s="7"/>
-      <c r="I216" s="8"/>
+      <c r="I216" s="12"/>
       <c r="J216" s="9"/>
       <c r="K216" s="7"/>
       <c r="L216" s="10" t="str">
@@ -7264,7 +7360,7 @@
       <c r="F217" s="7"/>
       <c r="G217" s="7"/>
       <c r="H217" s="7"/>
-      <c r="I217" s="8"/>
+      <c r="I217" s="12"/>
       <c r="J217" s="9"/>
       <c r="K217" s="7"/>
       <c r="L217" s="10" t="str">
@@ -7294,7 +7390,7 @@
       <c r="F218" s="7"/>
       <c r="G218" s="7"/>
       <c r="H218" s="7"/>
-      <c r="I218" s="8"/>
+      <c r="I218" s="12"/>
       <c r="J218" s="9"/>
       <c r="K218" s="7"/>
       <c r="L218" s="10" t="str">
@@ -7324,7 +7420,7 @@
       <c r="F219" s="7"/>
       <c r="G219" s="7"/>
       <c r="H219" s="7"/>
-      <c r="I219" s="8"/>
+      <c r="I219" s="12"/>
       <c r="J219" s="9"/>
       <c r="K219" s="7"/>
       <c r="L219" s="10" t="str">
@@ -7354,7 +7450,7 @@
       <c r="F220" s="7"/>
       <c r="G220" s="7"/>
       <c r="H220" s="7"/>
-      <c r="I220" s="8"/>
+      <c r="I220" s="12"/>
       <c r="J220" s="9"/>
       <c r="K220" s="7"/>
       <c r="L220" s="10" t="str">
@@ -7384,7 +7480,7 @@
       <c r="F221" s="7"/>
       <c r="G221" s="7"/>
       <c r="H221" s="7"/>
-      <c r="I221" s="8"/>
+      <c r="I221" s="12"/>
       <c r="J221" s="9"/>
       <c r="K221" s="7"/>
       <c r="L221" s="10" t="str">
@@ -7414,7 +7510,7 @@
       <c r="F222" s="7"/>
       <c r="G222" s="7"/>
       <c r="H222" s="7"/>
-      <c r="I222" s="8"/>
+      <c r="I222" s="12"/>
       <c r="J222" s="9"/>
       <c r="K222" s="7"/>
       <c r="L222" s="10" t="str">
@@ -7444,7 +7540,7 @@
       <c r="F223" s="7"/>
       <c r="G223" s="7"/>
       <c r="H223" s="7"/>
-      <c r="I223" s="8"/>
+      <c r="I223" s="12"/>
       <c r="J223" s="9"/>
       <c r="K223" s="7"/>
       <c r="L223" s="10" t="str">
@@ -7474,7 +7570,7 @@
       <c r="F224" s="7"/>
       <c r="G224" s="7"/>
       <c r="H224" s="7"/>
-      <c r="I224" s="8"/>
+      <c r="I224" s="12"/>
       <c r="J224" s="9"/>
       <c r="K224" s="7"/>
       <c r="L224" s="10" t="str">
@@ -7504,7 +7600,7 @@
       <c r="F225" s="7"/>
       <c r="G225" s="7"/>
       <c r="H225" s="7"/>
-      <c r="I225" s="8"/>
+      <c r="I225" s="12"/>
       <c r="J225" s="9"/>
       <c r="K225" s="7"/>
       <c r="L225" s="10" t="str">
@@ -7534,7 +7630,7 @@
       <c r="F226" s="7"/>
       <c r="G226" s="7"/>
       <c r="H226" s="7"/>
-      <c r="I226" s="8"/>
+      <c r="I226" s="12"/>
       <c r="J226" s="9"/>
       <c r="K226" s="7"/>
       <c r="L226" s="10" t="str">
@@ -7564,7 +7660,7 @@
       <c r="F227" s="7"/>
       <c r="G227" s="7"/>
       <c r="H227" s="7"/>
-      <c r="I227" s="8"/>
+      <c r="I227" s="12"/>
       <c r="J227" s="9"/>
       <c r="K227" s="7"/>
       <c r="L227" s="10" t="str">
@@ -7594,7 +7690,7 @@
       <c r="F228" s="7"/>
       <c r="G228" s="7"/>
       <c r="H228" s="7"/>
-      <c r="I228" s="8"/>
+      <c r="I228" s="12"/>
       <c r="J228" s="9"/>
       <c r="K228" s="7"/>
       <c r="L228" s="10" t="str">
@@ -7624,7 +7720,7 @@
       <c r="F229" s="7"/>
       <c r="G229" s="7"/>
       <c r="H229" s="7"/>
-      <c r="I229" s="8"/>
+      <c r="I229" s="12"/>
       <c r="J229" s="9"/>
       <c r="K229" s="7"/>
       <c r="L229" s="10" t="str">
@@ -7654,7 +7750,7 @@
       <c r="F230" s="7"/>
       <c r="G230" s="7"/>
       <c r="H230" s="7"/>
-      <c r="I230" s="8"/>
+      <c r="I230" s="12"/>
       <c r="J230" s="9"/>
       <c r="K230" s="7"/>
       <c r="L230" s="10" t="str">
@@ -7684,7 +7780,7 @@
       <c r="F231" s="7"/>
       <c r="G231" s="7"/>
       <c r="H231" s="7"/>
-      <c r="I231" s="8"/>
+      <c r="I231" s="12"/>
       <c r="J231" s="9"/>
       <c r="K231" s="7"/>
       <c r="L231" s="10" t="str">
@@ -7714,7 +7810,7 @@
       <c r="F232" s="7"/>
       <c r="G232" s="7"/>
       <c r="H232" s="7"/>
-      <c r="I232" s="8"/>
+      <c r="I232" s="12"/>
       <c r="J232" s="9"/>
       <c r="K232" s="7"/>
       <c r="L232" s="10" t="str">
@@ -7744,7 +7840,7 @@
       <c r="F233" s="7"/>
       <c r="G233" s="7"/>
       <c r="H233" s="7"/>
-      <c r="I233" s="8"/>
+      <c r="I233" s="12"/>
       <c r="J233" s="9"/>
       <c r="K233" s="7"/>
       <c r="L233" s="10" t="str">
@@ -7774,7 +7870,7 @@
       <c r="F234" s="7"/>
       <c r="G234" s="7"/>
       <c r="H234" s="7"/>
-      <c r="I234" s="8"/>
+      <c r="I234" s="12"/>
       <c r="J234" s="9"/>
       <c r="K234" s="7"/>
       <c r="L234" s="10" t="str">
@@ -7804,7 +7900,7 @@
       <c r="F235" s="7"/>
       <c r="G235" s="7"/>
       <c r="H235" s="7"/>
-      <c r="I235" s="8"/>
+      <c r="I235" s="12"/>
       <c r="J235" s="9"/>
       <c r="K235" s="7"/>
       <c r="L235" s="10" t="str">
@@ -7834,7 +7930,7 @@
       <c r="F236" s="7"/>
       <c r="G236" s="7"/>
       <c r="H236" s="7"/>
-      <c r="I236" s="8"/>
+      <c r="I236" s="12"/>
       <c r="J236" s="9"/>
       <c r="K236" s="7"/>
       <c r="L236" s="10" t="str">
@@ -7864,7 +7960,7 @@
       <c r="F237" s="7"/>
       <c r="G237" s="7"/>
       <c r="H237" s="7"/>
-      <c r="I237" s="8"/>
+      <c r="I237" s="12"/>
       <c r="J237" s="9"/>
       <c r="K237" s="7"/>
       <c r="L237" s="10" t="str">
@@ -7894,7 +7990,7 @@
       <c r="F238" s="7"/>
       <c r="G238" s="7"/>
       <c r="H238" s="7"/>
-      <c r="I238" s="8"/>
+      <c r="I238" s="12"/>
       <c r="J238" s="9"/>
       <c r="K238" s="7"/>
       <c r="L238" s="10" t="str">
@@ -7924,7 +8020,7 @@
       <c r="F239" s="7"/>
       <c r="G239" s="7"/>
       <c r="H239" s="7"/>
-      <c r="I239" s="8"/>
+      <c r="I239" s="12"/>
       <c r="J239" s="9"/>
       <c r="K239" s="7"/>
       <c r="L239" s="10" t="str">
@@ -7954,7 +8050,7 @@
       <c r="F240" s="7"/>
       <c r="G240" s="7"/>
       <c r="H240" s="7"/>
-      <c r="I240" s="8"/>
+      <c r="I240" s="12"/>
       <c r="J240" s="9"/>
       <c r="K240" s="7"/>
       <c r="L240" s="10" t="str">
@@ -7984,7 +8080,7 @@
       <c r="F241" s="7"/>
       <c r="G241" s="7"/>
       <c r="H241" s="7"/>
-      <c r="I241" s="8"/>
+      <c r="I241" s="12"/>
       <c r="J241" s="9"/>
       <c r="K241" s="7"/>
       <c r="L241" s="10" t="str">
@@ -8014,7 +8110,7 @@
       <c r="F242" s="7"/>
       <c r="G242" s="7"/>
       <c r="H242" s="7"/>
-      <c r="I242" s="8"/>
+      <c r="I242" s="12"/>
       <c r="J242" s="9"/>
       <c r="K242" s="7"/>
       <c r="L242" s="10" t="str">
@@ -8044,7 +8140,7 @@
       <c r="F243" s="7"/>
       <c r="G243" s="7"/>
       <c r="H243" s="7"/>
-      <c r="I243" s="8"/>
+      <c r="I243" s="12"/>
       <c r="J243" s="9"/>
       <c r="K243" s="7"/>
       <c r="L243" s="10" t="str">
@@ -8074,7 +8170,7 @@
       <c r="F244" s="7"/>
       <c r="G244" s="7"/>
       <c r="H244" s="7"/>
-      <c r="I244" s="8"/>
+      <c r="I244" s="12"/>
       <c r="J244" s="9"/>
       <c r="K244" s="7"/>
       <c r="L244" s="10" t="str">
@@ -8104,7 +8200,7 @@
       <c r="F245" s="7"/>
       <c r="G245" s="7"/>
       <c r="H245" s="7"/>
-      <c r="I245" s="8"/>
+      <c r="I245" s="12"/>
       <c r="J245" s="9"/>
       <c r="K245" s="7"/>
       <c r="L245" s="10" t="str">
@@ -8134,7 +8230,7 @@
       <c r="F246" s="7"/>
       <c r="G246" s="7"/>
       <c r="H246" s="7"/>
-      <c r="I246" s="8"/>
+      <c r="I246" s="12"/>
       <c r="J246" s="9"/>
       <c r="K246" s="7"/>
       <c r="L246" s="10" t="str">
@@ -8164,7 +8260,7 @@
       <c r="F247" s="7"/>
       <c r="G247" s="7"/>
       <c r="H247" s="7"/>
-      <c r="I247" s="8"/>
+      <c r="I247" s="12"/>
       <c r="J247" s="9"/>
       <c r="K247" s="7"/>
       <c r="L247" s="10" t="str">
@@ -8194,7 +8290,7 @@
       <c r="F248" s="7"/>
       <c r="G248" s="7"/>
       <c r="H248" s="7"/>
-      <c r="I248" s="8"/>
+      <c r="I248" s="12"/>
       <c r="J248" s="9"/>
       <c r="K248" s="7"/>
       <c r="L248" s="10" t="str">
@@ -8224,7 +8320,7 @@
       <c r="F249" s="7"/>
       <c r="G249" s="7"/>
       <c r="H249" s="7"/>
-      <c r="I249" s="8"/>
+      <c r="I249" s="12"/>
       <c r="J249" s="9"/>
       <c r="K249" s="7"/>
       <c r="L249" s="10" t="str">
@@ -8254,7 +8350,7 @@
       <c r="F250" s="7"/>
       <c r="G250" s="7"/>
       <c r="H250" s="7"/>
-      <c r="I250" s="8"/>
+      <c r="I250" s="12"/>
       <c r="J250" s="9"/>
       <c r="K250" s="7"/>
       <c r="L250" s="10" t="str">
@@ -8284,7 +8380,7 @@
       <c r="F251" s="7"/>
       <c r="G251" s="7"/>
       <c r="H251" s="7"/>
-      <c r="I251" s="8"/>
+      <c r="I251" s="12"/>
       <c r="J251" s="9"/>
       <c r="K251" s="7"/>
       <c r="L251" s="10" t="str">
@@ -8314,7 +8410,7 @@
       <c r="F252" s="7"/>
       <c r="G252" s="7"/>
       <c r="H252" s="7"/>
-      <c r="I252" s="8"/>
+      <c r="I252" s="12"/>
       <c r="J252" s="9"/>
       <c r="K252" s="7"/>
       <c r="L252" s="10" t="str">
@@ -8344,7 +8440,7 @@
       <c r="F253" s="7"/>
       <c r="G253" s="7"/>
       <c r="H253" s="7"/>
-      <c r="I253" s="8"/>
+      <c r="I253" s="12"/>
       <c r="J253" s="9"/>
       <c r="K253" s="7"/>
       <c r="L253" s="10" t="str">
@@ -8374,7 +8470,7 @@
       <c r="F254" s="7"/>
       <c r="G254" s="7"/>
       <c r="H254" s="7"/>
-      <c r="I254" s="8"/>
+      <c r="I254" s="12"/>
       <c r="J254" s="9"/>
       <c r="K254" s="7"/>
       <c r="L254" s="10" t="str">
@@ -8404,7 +8500,7 @@
       <c r="F255" s="7"/>
       <c r="G255" s="7"/>
       <c r="H255" s="7"/>
-      <c r="I255" s="8"/>
+      <c r="I255" s="12"/>
       <c r="J255" s="9"/>
       <c r="K255" s="7"/>
       <c r="L255" s="10" t="str">
@@ -8434,7 +8530,7 @@
       <c r="F256" s="7"/>
       <c r="G256" s="7"/>
       <c r="H256" s="7"/>
-      <c r="I256" s="8"/>
+      <c r="I256" s="12"/>
       <c r="J256" s="9"/>
       <c r="K256" s="7"/>
       <c r="L256" s="10" t="str">
@@ -8464,7 +8560,7 @@
       <c r="F257" s="7"/>
       <c r="G257" s="7"/>
       <c r="H257" s="7"/>
-      <c r="I257" s="8"/>
+      <c r="I257" s="12"/>
       <c r="J257" s="9"/>
       <c r="K257" s="7"/>
       <c r="L257" s="10" t="str">
@@ -8494,7 +8590,7 @@
       <c r="F258" s="7"/>
       <c r="G258" s="7"/>
       <c r="H258" s="7"/>
-      <c r="I258" s="8"/>
+      <c r="I258" s="12"/>
       <c r="J258" s="9"/>
       <c r="K258" s="7"/>
       <c r="L258" s="10" t="str">
@@ -8524,7 +8620,7 @@
       <c r="F259" s="7"/>
       <c r="G259" s="7"/>
       <c r="H259" s="7"/>
-      <c r="I259" s="8"/>
+      <c r="I259" s="12"/>
       <c r="J259" s="9"/>
       <c r="K259" s="7"/>
       <c r="L259" s="10" t="str">
@@ -8554,7 +8650,7 @@
       <c r="F260" s="7"/>
       <c r="G260" s="7"/>
       <c r="H260" s="7"/>
-      <c r="I260" s="8"/>
+      <c r="I260" s="12"/>
       <c r="J260" s="9"/>
       <c r="K260" s="7"/>
       <c r="L260" s="10" t="str">
@@ -8584,7 +8680,7 @@
       <c r="F261" s="7"/>
       <c r="G261" s="7"/>
       <c r="H261" s="7"/>
-      <c r="I261" s="8"/>
+      <c r="I261" s="12"/>
       <c r="J261" s="9"/>
       <c r="K261" s="7"/>
       <c r="L261" s="10" t="str">
@@ -8614,7 +8710,7 @@
       <c r="F262" s="7"/>
       <c r="G262" s="7"/>
       <c r="H262" s="7"/>
-      <c r="I262" s="8"/>
+      <c r="I262" s="12"/>
       <c r="J262" s="9"/>
       <c r="K262" s="7"/>
       <c r="L262" s="10" t="str">
@@ -8644,7 +8740,7 @@
       <c r="F263" s="7"/>
       <c r="G263" s="7"/>
       <c r="H263" s="7"/>
-      <c r="I263" s="8"/>
+      <c r="I263" s="12"/>
       <c r="J263" s="9"/>
       <c r="K263" s="7"/>
       <c r="L263" s="10" t="str">
@@ -8674,7 +8770,7 @@
       <c r="F264" s="7"/>
       <c r="G264" s="7"/>
       <c r="H264" s="7"/>
-      <c r="I264" s="8"/>
+      <c r="I264" s="12"/>
       <c r="J264" s="9"/>
       <c r="K264" s="7"/>
       <c r="L264" s="10" t="str">
@@ -8704,7 +8800,7 @@
       <c r="F265" s="7"/>
       <c r="G265" s="7"/>
       <c r="H265" s="7"/>
-      <c r="I265" s="8"/>
+      <c r="I265" s="12"/>
       <c r="J265" s="9"/>
       <c r="K265" s="7"/>
       <c r="L265" s="10" t="str">
@@ -8734,7 +8830,7 @@
       <c r="F266" s="7"/>
       <c r="G266" s="7"/>
       <c r="H266" s="7"/>
-      <c r="I266" s="8"/>
+      <c r="I266" s="12"/>
       <c r="J266" s="9"/>
       <c r="K266" s="7"/>
       <c r="L266" s="10" t="str">
@@ -8764,7 +8860,7 @@
       <c r="F267" s="7"/>
       <c r="G267" s="7"/>
       <c r="H267" s="7"/>
-      <c r="I267" s="8"/>
+      <c r="I267" s="12"/>
       <c r="J267" s="9"/>
       <c r="K267" s="7"/>
       <c r="L267" s="10" t="str">
@@ -8794,7 +8890,7 @@
       <c r="F268" s="7"/>
       <c r="G268" s="7"/>
       <c r="H268" s="7"/>
-      <c r="I268" s="8"/>
+      <c r="I268" s="12"/>
       <c r="J268" s="9"/>
       <c r="K268" s="7"/>
       <c r="L268" s="10" t="str">
@@ -8824,7 +8920,7 @@
       <c r="F269" s="7"/>
       <c r="G269" s="7"/>
       <c r="H269" s="7"/>
-      <c r="I269" s="8"/>
+      <c r="I269" s="12"/>
       <c r="J269" s="9"/>
       <c r="K269" s="7"/>
       <c r="L269" s="10" t="str">
@@ -8854,7 +8950,7 @@
       <c r="F270" s="7"/>
       <c r="G270" s="7"/>
       <c r="H270" s="7"/>
-      <c r="I270" s="8"/>
+      <c r="I270" s="12"/>
       <c r="J270" s="9"/>
       <c r="K270" s="7"/>
       <c r="L270" s="10" t="str">
@@ -8884,7 +8980,7 @@
       <c r="F271" s="7"/>
       <c r="G271" s="7"/>
       <c r="H271" s="7"/>
-      <c r="I271" s="8"/>
+      <c r="I271" s="12"/>
       <c r="J271" s="9"/>
       <c r="K271" s="7"/>
       <c r="L271" s="10" t="str">
@@ -8914,7 +9010,7 @@
       <c r="F272" s="7"/>
       <c r="G272" s="7"/>
       <c r="H272" s="7"/>
-      <c r="I272" s="8"/>
+      <c r="I272" s="12"/>
       <c r="J272" s="9"/>
       <c r="K272" s="7"/>
       <c r="L272" s="10" t="str">
@@ -8944,7 +9040,7 @@
       <c r="F273" s="7"/>
       <c r="G273" s="7"/>
       <c r="H273" s="7"/>
-      <c r="I273" s="8"/>
+      <c r="I273" s="12"/>
       <c r="J273" s="9"/>
       <c r="K273" s="7"/>
       <c r="L273" s="10" t="str">
@@ -8974,7 +9070,7 @@
       <c r="F274" s="7"/>
       <c r="G274" s="7"/>
       <c r="H274" s="7"/>
-      <c r="I274" s="8"/>
+      <c r="I274" s="12"/>
       <c r="J274" s="9"/>
       <c r="K274" s="7"/>
       <c r="L274" s="10" t="str">
@@ -9004,7 +9100,7 @@
       <c r="F275" s="7"/>
       <c r="G275" s="7"/>
       <c r="H275" s="7"/>
-      <c r="I275" s="8"/>
+      <c r="I275" s="12"/>
       <c r="J275" s="9"/>
       <c r="K275" s="7"/>
       <c r="L275" s="10" t="str">
@@ -9034,7 +9130,7 @@
       <c r="F276" s="7"/>
       <c r="G276" s="7"/>
       <c r="H276" s="7"/>
-      <c r="I276" s="8"/>
+      <c r="I276" s="12"/>
       <c r="J276" s="9"/>
       <c r="K276" s="7"/>
       <c r="L276" s="10" t="str">
@@ -9064,7 +9160,7 @@
       <c r="F277" s="7"/>
       <c r="G277" s="7"/>
       <c r="H277" s="7"/>
-      <c r="I277" s="8"/>
+      <c r="I277" s="12"/>
       <c r="J277" s="9"/>
       <c r="K277" s="7"/>
       <c r="L277" s="10" t="str">
@@ -9094,7 +9190,7 @@
       <c r="F278" s="7"/>
       <c r="G278" s="7"/>
       <c r="H278" s="7"/>
-      <c r="I278" s="8"/>
+      <c r="I278" s="12"/>
       <c r="J278" s="9"/>
       <c r="K278" s="7"/>
       <c r="L278" s="10" t="str">
@@ -9124,7 +9220,7 @@
       <c r="F279" s="7"/>
       <c r="G279" s="7"/>
       <c r="H279" s="7"/>
-      <c r="I279" s="8"/>
+      <c r="I279" s="12"/>
       <c r="J279" s="9"/>
       <c r="K279" s="7"/>
       <c r="L279" s="10" t="str">
@@ -9154,7 +9250,7 @@
       <c r="F280" s="7"/>
       <c r="G280" s="7"/>
       <c r="H280" s="7"/>
-      <c r="I280" s="8"/>
+      <c r="I280" s="12"/>
       <c r="J280" s="9"/>
       <c r="K280" s="7"/>
       <c r="L280" s="10" t="str">
@@ -9184,7 +9280,7 @@
       <c r="F281" s="7"/>
       <c r="G281" s="7"/>
       <c r="H281" s="7"/>
-      <c r="I281" s="8"/>
+      <c r="I281" s="12"/>
       <c r="J281" s="9"/>
       <c r="K281" s="7"/>
       <c r="L281" s="10" t="str">
@@ -9214,7 +9310,7 @@
       <c r="F282" s="7"/>
       <c r="G282" s="7"/>
       <c r="H282" s="7"/>
-      <c r="I282" s="8"/>
+      <c r="I282" s="12"/>
       <c r="J282" s="9"/>
       <c r="K282" s="7"/>
       <c r="L282" s="10" t="str">
@@ -9244,7 +9340,7 @@
       <c r="F283" s="7"/>
       <c r="G283" s="7"/>
       <c r="H283" s="7"/>
-      <c r="I283" s="8"/>
+      <c r="I283" s="12"/>
       <c r="J283" s="9"/>
       <c r="K283" s="7"/>
       <c r="L283" s="10" t="str">
@@ -9274,7 +9370,7 @@
       <c r="F284" s="7"/>
       <c r="G284" s="7"/>
       <c r="H284" s="7"/>
-      <c r="I284" s="8"/>
+      <c r="I284" s="12"/>
       <c r="J284" s="9"/>
       <c r="K284" s="7"/>
       <c r="L284" s="10" t="str">
@@ -9304,7 +9400,7 @@
       <c r="F285" s="7"/>
       <c r="G285" s="7"/>
       <c r="H285" s="7"/>
-      <c r="I285" s="8"/>
+      <c r="I285" s="12"/>
       <c r="J285" s="9"/>
       <c r="K285" s="7"/>
       <c r="L285" s="10" t="str">
@@ -9334,7 +9430,7 @@
       <c r="F286" s="7"/>
       <c r="G286" s="7"/>
       <c r="H286" s="7"/>
-      <c r="I286" s="8"/>
+      <c r="I286" s="12"/>
       <c r="J286" s="9"/>
       <c r="K286" s="7"/>
       <c r="L286" s="10" t="str">
@@ -9364,7 +9460,7 @@
       <c r="F287" s="7"/>
       <c r="G287" s="7"/>
       <c r="H287" s="7"/>
-      <c r="I287" s="8"/>
+      <c r="I287" s="12"/>
       <c r="J287" s="9"/>
       <c r="K287" s="7"/>
       <c r="L287" s="10" t="str">
@@ -9394,7 +9490,7 @@
       <c r="F288" s="7"/>
       <c r="G288" s="7"/>
       <c r="H288" s="7"/>
-      <c r="I288" s="8"/>
+      <c r="I288" s="12"/>
       <c r="J288" s="9"/>
       <c r="K288" s="7"/>
       <c r="L288" s="10" t="str">
@@ -9424,7 +9520,7 @@
       <c r="F289" s="7"/>
       <c r="G289" s="7"/>
       <c r="H289" s="7"/>
-      <c r="I289" s="8"/>
+      <c r="I289" s="12"/>
       <c r="J289" s="9"/>
       <c r="K289" s="7"/>
       <c r="L289" s="10" t="str">
@@ -9454,7 +9550,7 @@
       <c r="F290" s="7"/>
       <c r="G290" s="7"/>
       <c r="H290" s="7"/>
-      <c r="I290" s="8"/>
+      <c r="I290" s="12"/>
       <c r="J290" s="9"/>
       <c r="K290" s="7"/>
       <c r="L290" s="10" t="str">
@@ -9484,7 +9580,7 @@
       <c r="F291" s="7"/>
       <c r="G291" s="7"/>
       <c r="H291" s="7"/>
-      <c r="I291" s="8"/>
+      <c r="I291" s="12"/>
       <c r="J291" s="9"/>
       <c r="K291" s="7"/>
       <c r="L291" s="10" t="str">
@@ -9514,7 +9610,7 @@
       <c r="F292" s="7"/>
       <c r="G292" s="7"/>
       <c r="H292" s="7"/>
-      <c r="I292" s="8"/>
+      <c r="I292" s="12"/>
       <c r="J292" s="9"/>
       <c r="K292" s="7"/>
       <c r="L292" s="10" t="str">
@@ -9544,7 +9640,7 @@
       <c r="F293" s="7"/>
       <c r="G293" s="7"/>
       <c r="H293" s="7"/>
-      <c r="I293" s="8"/>
+      <c r="I293" s="12"/>
       <c r="J293" s="9"/>
       <c r="K293" s="7"/>
       <c r="L293" s="10" t="str">
@@ -9574,7 +9670,7 @@
       <c r="F294" s="7"/>
       <c r="G294" s="7"/>
       <c r="H294" s="7"/>
-      <c r="I294" s="8"/>
+      <c r="I294" s="12"/>
       <c r="J294" s="9"/>
       <c r="K294" s="7"/>
       <c r="L294" s="10" t="str">
@@ -9604,7 +9700,7 @@
       <c r="F295" s="7"/>
       <c r="G295" s="7"/>
       <c r="H295" s="7"/>
-      <c r="I295" s="8"/>
+      <c r="I295" s="12"/>
       <c r="J295" s="9"/>
       <c r="K295" s="7"/>
       <c r="L295" s="10" t="str">
@@ -9634,7 +9730,7 @@
       <c r="F296" s="7"/>
       <c r="G296" s="7"/>
       <c r="H296" s="7"/>
-      <c r="I296" s="8"/>
+      <c r="I296" s="12"/>
       <c r="J296" s="9"/>
       <c r="K296" s="7"/>
       <c r="L296" s="10" t="str">
@@ -9664,7 +9760,7 @@
       <c r="F297" s="7"/>
       <c r="G297" s="7"/>
       <c r="H297" s="7"/>
-      <c r="I297" s="8"/>
+      <c r="I297" s="12"/>
       <c r="J297" s="9"/>
       <c r="K297" s="7"/>
       <c r="L297" s="10" t="str">
@@ -9694,7 +9790,7 @@
       <c r="F298" s="7"/>
       <c r="G298" s="7"/>
       <c r="H298" s="7"/>
-      <c r="I298" s="8"/>
+      <c r="I298" s="12"/>
       <c r="J298" s="9"/>
       <c r="K298" s="7"/>
       <c r="L298" s="10" t="str">
@@ -9724,7 +9820,7 @@
       <c r="F299" s="7"/>
       <c r="G299" s="7"/>
       <c r="H299" s="7"/>
-      <c r="I299" s="8"/>
+      <c r="I299" s="12"/>
       <c r="J299" s="9"/>
       <c r="K299" s="7"/>
       <c r="L299" s="10" t="str">
@@ -9754,7 +9850,7 @@
       <c r="F300" s="7"/>
       <c r="G300" s="7"/>
       <c r="H300" s="7"/>
-      <c r="I300" s="8"/>
+      <c r="I300" s="12"/>
       <c r="J300" s="9"/>
       <c r="K300" s="7"/>
       <c r="L300" s="10" t="str">
@@ -9784,7 +9880,7 @@
       <c r="F301" s="7"/>
       <c r="G301" s="7"/>
       <c r="H301" s="7"/>
-      <c r="I301" s="8"/>
+      <c r="I301" s="12"/>
       <c r="J301" s="9"/>
       <c r="K301" s="7"/>
       <c r="L301" s="10" t="str">
@@ -9814,7 +9910,7 @@
       <c r="F302" s="7"/>
       <c r="G302" s="7"/>
       <c r="H302" s="7"/>
-      <c r="I302" s="8"/>
+      <c r="I302" s="12"/>
       <c r="J302" s="9"/>
       <c r="K302" s="7"/>
       <c r="L302" s="10" t="str">
@@ -9844,7 +9940,7 @@
       <c r="F303" s="7"/>
       <c r="G303" s="7"/>
       <c r="H303" s="7"/>
-      <c r="I303" s="8"/>
+      <c r="I303" s="12"/>
       <c r="J303" s="9"/>
       <c r="K303" s="7"/>
       <c r="L303" s="10" t="str">
@@ -9874,7 +9970,7 @@
       <c r="F304" s="7"/>
       <c r="G304" s="7"/>
       <c r="H304" s="7"/>
-      <c r="I304" s="8"/>
+      <c r="I304" s="12"/>
       <c r="J304" s="9"/>
       <c r="K304" s="7"/>
       <c r="L304" s="10" t="str">
@@ -9904,7 +10000,7 @@
       <c r="F305" s="7"/>
       <c r="G305" s="7"/>
       <c r="H305" s="7"/>
-      <c r="I305" s="8"/>
+      <c r="I305" s="12"/>
       <c r="J305" s="9"/>
       <c r="K305" s="7"/>
       <c r="L305" s="10" t="str">
@@ -9934,7 +10030,7 @@
       <c r="F306" s="7"/>
       <c r="G306" s="7"/>
       <c r="H306" s="7"/>
-      <c r="I306" s="8"/>
+      <c r="I306" s="12"/>
       <c r="J306" s="9"/>
       <c r="K306" s="7"/>
       <c r="L306" s="10" t="str">
@@ -9964,7 +10060,7 @@
       <c r="F307" s="7"/>
       <c r="G307" s="7"/>
       <c r="H307" s="7"/>
-      <c r="I307" s="8"/>
+      <c r="I307" s="12"/>
       <c r="J307" s="9"/>
       <c r="K307" s="7"/>
       <c r="L307" s="10" t="str">
@@ -9994,7 +10090,7 @@
       <c r="F308" s="7"/>
       <c r="G308" s="7"/>
       <c r="H308" s="7"/>
-      <c r="I308" s="8"/>
+      <c r="I308" s="12"/>
       <c r="J308" s="9"/>
       <c r="K308" s="7"/>
       <c r="L308" s="10" t="str">
@@ -10024,7 +10120,7 @@
       <c r="F309" s="7"/>
       <c r="G309" s="7"/>
       <c r="H309" s="7"/>
-      <c r="I309" s="8"/>
+      <c r="I309" s="12"/>
       <c r="J309" s="9"/>
       <c r="K309" s="7"/>
       <c r="L309" s="10" t="str">
@@ -10054,7 +10150,7 @@
       <c r="F310" s="7"/>
       <c r="G310" s="7"/>
       <c r="H310" s="7"/>
-      <c r="I310" s="8"/>
+      <c r="I310" s="12"/>
       <c r="J310" s="9"/>
       <c r="K310" s="7"/>
       <c r="L310" s="10" t="str">
@@ -10084,7 +10180,7 @@
       <c r="F311" s="7"/>
       <c r="G311" s="7"/>
       <c r="H311" s="7"/>
-      <c r="I311" s="8"/>
+      <c r="I311" s="12"/>
       <c r="J311" s="9"/>
       <c r="K311" s="7"/>
       <c r="L311" s="10" t="str">
@@ -10114,7 +10210,7 @@
       <c r="F312" s="7"/>
       <c r="G312" s="7"/>
       <c r="H312" s="7"/>
-      <c r="I312" s="8"/>
+      <c r="I312" s="12"/>
       <c r="J312" s="9"/>
       <c r="K312" s="7"/>
       <c r="L312" s="10" t="str">
@@ -10144,7 +10240,7 @@
       <c r="F313" s="7"/>
       <c r="G313" s="7"/>
       <c r="H313" s="7"/>
-      <c r="I313" s="8"/>
+      <c r="I313" s="12"/>
       <c r="J313" s="9"/>
       <c r="K313" s="7"/>
       <c r="L313" s="10" t="str">
@@ -10174,7 +10270,7 @@
       <c r="F314" s="7"/>
       <c r="G314" s="7"/>
       <c r="H314" s="7"/>
-      <c r="I314" s="8"/>
+      <c r="I314" s="12"/>
       <c r="J314" s="9"/>
       <c r="K314" s="7"/>
       <c r="L314" s="10" t="str">
@@ -10204,7 +10300,7 @@
       <c r="F315" s="7"/>
       <c r="G315" s="7"/>
       <c r="H315" s="7"/>
-      <c r="I315" s="8"/>
+      <c r="I315" s="12"/>
       <c r="J315" s="9"/>
       <c r="K315" s="7"/>
       <c r="L315" s="10" t="str">
@@ -10234,7 +10330,7 @@
       <c r="F316" s="7"/>
       <c r="G316" s="7"/>
       <c r="H316" s="7"/>
-      <c r="I316" s="8"/>
+      <c r="I316" s="12"/>
       <c r="J316" s="9"/>
       <c r="K316" s="7"/>
       <c r="L316" s="10" t="str">
@@ -10264,7 +10360,7 @@
       <c r="F317" s="7"/>
       <c r="G317" s="7"/>
       <c r="H317" s="7"/>
-      <c r="I317" s="8"/>
+      <c r="I317" s="12"/>
       <c r="J317" s="9"/>
       <c r="K317" s="7"/>
       <c r="L317" s="10" t="str">
@@ -10294,7 +10390,7 @@
       <c r="F318" s="7"/>
       <c r="G318" s="7"/>
       <c r="H318" s="7"/>
-      <c r="I318" s="8"/>
+      <c r="I318" s="12"/>
       <c r="J318" s="9"/>
       <c r="K318" s="7"/>
       <c r="L318" s="10" t="str">
@@ -10324,7 +10420,7 @@
       <c r="F319" s="7"/>
       <c r="G319" s="7"/>
       <c r="H319" s="7"/>
-      <c r="I319" s="8"/>
+      <c r="I319" s="12"/>
       <c r="J319" s="9"/>
       <c r="K319" s="7"/>
       <c r="L319" s="10" t="str">
@@ -10354,7 +10450,7 @@
       <c r="F320" s="7"/>
       <c r="G320" s="7"/>
       <c r="H320" s="7"/>
-      <c r="I320" s="8"/>
+      <c r="I320" s="12"/>
       <c r="J320" s="9"/>
       <c r="K320" s="7"/>
       <c r="L320" s="10" t="str">
@@ -10384,7 +10480,7 @@
       <c r="F321" s="7"/>
       <c r="G321" s="7"/>
       <c r="H321" s="7"/>
-      <c r="I321" s="8"/>
+      <c r="I321" s="12"/>
       <c r="J321" s="9"/>
       <c r="K321" s="7"/>
       <c r="L321" s="10" t="str">
@@ -10414,7 +10510,7 @@
       <c r="F322" s="7"/>
       <c r="G322" s="7"/>
       <c r="H322" s="7"/>
-      <c r="I322" s="8"/>
+      <c r="I322" s="12"/>
       <c r="J322" s="9"/>
       <c r="K322" s="7"/>
       <c r="L322" s="10" t="str">
@@ -10444,7 +10540,7 @@
       <c r="F323" s="7"/>
       <c r="G323" s="7"/>
       <c r="H323" s="7"/>
-      <c r="I323" s="8"/>
+      <c r="I323" s="12"/>
       <c r="J323" s="9"/>
       <c r="K323" s="7"/>
       <c r="L323" s="10" t="str">
@@ -10474,7 +10570,7 @@
       <c r="F324" s="7"/>
       <c r="G324" s="7"/>
       <c r="H324" s="7"/>
-      <c r="I324" s="8"/>
+      <c r="I324" s="12"/>
       <c r="J324" s="9"/>
       <c r="K324" s="7"/>
       <c r="L324" s="10" t="str">
@@ -10504,7 +10600,7 @@
       <c r="F325" s="7"/>
       <c r="G325" s="7"/>
       <c r="H325" s="7"/>
-      <c r="I325" s="8"/>
+      <c r="I325" s="12"/>
       <c r="J325" s="9"/>
       <c r="K325" s="7"/>
       <c r="L325" s="10" t="str">
@@ -10534,7 +10630,7 @@
       <c r="F326" s="7"/>
       <c r="G326" s="7"/>
       <c r="H326" s="7"/>
-      <c r="I326" s="8"/>
+      <c r="I326" s="12"/>
       <c r="J326" s="9"/>
       <c r="K326" s="7"/>
       <c r="L326" s="10" t="str">
@@ -10564,7 +10660,7 @@
       <c r="F327" s="7"/>
       <c r="G327" s="7"/>
       <c r="H327" s="7"/>
-      <c r="I327" s="8"/>
+      <c r="I327" s="12"/>
       <c r="J327" s="9"/>
       <c r="K327" s="7"/>
       <c r="L327" s="10" t="str">
@@ -10594,7 +10690,7 @@
       <c r="F328" s="7"/>
       <c r="G328" s="7"/>
       <c r="H328" s="7"/>
-      <c r="I328" s="8"/>
+      <c r="I328" s="12"/>
       <c r="J328" s="9"/>
       <c r="K328" s="7"/>
       <c r="L328" s="10" t="str">
@@ -10624,7 +10720,7 @@
       <c r="F329" s="7"/>
       <c r="G329" s="7"/>
       <c r="H329" s="7"/>
-      <c r="I329" s="8"/>
+      <c r="I329" s="12"/>
       <c r="J329" s="9"/>
       <c r="K329" s="7"/>
       <c r="L329" s="10" t="str">
@@ -10654,7 +10750,7 @@
       <c r="F330" s="7"/>
       <c r="G330" s="7"/>
       <c r="H330" s="7"/>
-      <c r="I330" s="8"/>
+      <c r="I330" s="12"/>
       <c r="J330" s="9"/>
       <c r="K330" s="7"/>
       <c r="L330" s="10" t="str">
@@ -10684,7 +10780,7 @@
       <c r="F331" s="7"/>
       <c r="G331" s="7"/>
       <c r="H331" s="7"/>
-      <c r="I331" s="8"/>
+      <c r="I331" s="12"/>
       <c r="J331" s="9"/>
       <c r="K331" s="7"/>
       <c r="L331" s="10" t="str">
@@ -10714,7 +10810,7 @@
       <c r="F332" s="7"/>
       <c r="G332" s="7"/>
       <c r="H332" s="7"/>
-      <c r="I332" s="8"/>
+      <c r="I332" s="12"/>
       <c r="J332" s="9"/>
       <c r="K332" s="7"/>
       <c r="L332" s="10" t="str">
@@ -10744,7 +10840,7 @@
       <c r="F333" s="7"/>
       <c r="G333" s="7"/>
       <c r="H333" s="7"/>
-      <c r="I333" s="8"/>
+      <c r="I333" s="12"/>
       <c r="J333" s="9"/>
       <c r="K333" s="7"/>
       <c r="L333" s="10" t="str">
@@ -10774,7 +10870,7 @@
       <c r="F334" s="7"/>
       <c r="G334" s="7"/>
       <c r="H334" s="7"/>
-      <c r="I334" s="8"/>
+      <c r="I334" s="12"/>
       <c r="J334" s="9"/>
       <c r="K334" s="7"/>
       <c r="L334" s="10" t="str">
@@ -10804,7 +10900,7 @@
       <c r="F335" s="7"/>
       <c r="G335" s="7"/>
       <c r="H335" s="7"/>
-      <c r="I335" s="8"/>
+      <c r="I335" s="12"/>
       <c r="J335" s="9"/>
       <c r="K335" s="7"/>
       <c r="L335" s="10" t="str">
@@ -10834,7 +10930,7 @@
       <c r="F336" s="7"/>
       <c r="G336" s="7"/>
       <c r="H336" s="7"/>
-      <c r="I336" s="8"/>
+      <c r="I336" s="12"/>
       <c r="J336" s="9"/>
       <c r="K336" s="7"/>
       <c r="L336" s="10" t="str">
@@ -10864,7 +10960,7 @@
       <c r="F337" s="7"/>
       <c r="G337" s="7"/>
       <c r="H337" s="7"/>
-      <c r="I337" s="8"/>
+      <c r="I337" s="12"/>
       <c r="J337" s="9"/>
       <c r="K337" s="7"/>
       <c r="L337" s="10" t="str">
@@ -10894,7 +10990,7 @@
       <c r="F338" s="7"/>
       <c r="G338" s="7"/>
       <c r="H338" s="7"/>
-      <c r="I338" s="8"/>
+      <c r="I338" s="12"/>
       <c r="J338" s="9"/>
       <c r="K338" s="7"/>
       <c r="L338" s="10" t="str">
@@ -10924,7 +11020,7 @@
       <c r="F339" s="7"/>
       <c r="G339" s="7"/>
       <c r="H339" s="7"/>
-      <c r="I339" s="8"/>
+      <c r="I339" s="12"/>
       <c r="J339" s="9"/>
       <c r="K339" s="7"/>
       <c r="L339" s="10" t="str">
@@ -10954,7 +11050,7 @@
       <c r="F340" s="7"/>
       <c r="G340" s="7"/>
       <c r="H340" s="7"/>
-      <c r="I340" s="8"/>
+      <c r="I340" s="12"/>
       <c r="J340" s="9"/>
       <c r="K340" s="7"/>
       <c r="L340" s="10" t="str">
@@ -10984,7 +11080,7 @@
       <c r="F341" s="7"/>
       <c r="G341" s="7"/>
       <c r="H341" s="7"/>
-      <c r="I341" s="8"/>
+      <c r="I341" s="12"/>
       <c r="J341" s="9"/>
       <c r="K341" s="7"/>
       <c r="L341" s="10" t="str">
@@ -11014,7 +11110,7 @@
       <c r="F342" s="7"/>
       <c r="G342" s="7"/>
       <c r="H342" s="7"/>
-      <c r="I342" s="8"/>
+      <c r="I342" s="12"/>
       <c r="J342" s="9"/>
       <c r="K342" s="7"/>
       <c r="L342" s="10" t="str">
@@ -11044,7 +11140,7 @@
       <c r="F343" s="7"/>
       <c r="G343" s="7"/>
       <c r="H343" s="7"/>
-      <c r="I343" s="8"/>
+      <c r="I343" s="12"/>
       <c r="J343" s="9"/>
       <c r="K343" s="7"/>
       <c r="L343" s="10" t="str">
@@ -11074,7 +11170,7 @@
       <c r="F344" s="7"/>
       <c r="G344" s="7"/>
       <c r="H344" s="7"/>
-      <c r="I344" s="8"/>
+      <c r="I344" s="12"/>
       <c r="J344" s="9"/>
       <c r="K344" s="7"/>
       <c r="L344" s="10" t="str">
@@ -11104,7 +11200,7 @@
       <c r="F345" s="7"/>
       <c r="G345" s="7"/>
       <c r="H345" s="7"/>
-      <c r="I345" s="8"/>
+      <c r="I345" s="12"/>
       <c r="J345" s="9"/>
       <c r="K345" s="7"/>
       <c r="L345" s="10" t="str">
@@ -11134,7 +11230,7 @@
       <c r="F346" s="7"/>
       <c r="G346" s="7"/>
       <c r="H346" s="7"/>
-      <c r="I346" s="8"/>
+      <c r="I346" s="12"/>
       <c r="J346" s="9"/>
       <c r="K346" s="7"/>
       <c r="L346" s="10" t="str">
@@ -11164,7 +11260,7 @@
       <c r="F347" s="7"/>
       <c r="G347" s="7"/>
       <c r="H347" s="7"/>
-      <c r="I347" s="8"/>
+      <c r="I347" s="12"/>
       <c r="J347" s="9"/>
       <c r="K347" s="7"/>
       <c r="L347" s="10" t="str">
@@ -11194,7 +11290,7 @@
       <c r="F348" s="7"/>
       <c r="G348" s="7"/>
       <c r="H348" s="7"/>
-      <c r="I348" s="8"/>
+      <c r="I348" s="12"/>
       <c r="J348" s="9"/>
       <c r="K348" s="7"/>
       <c r="L348" s="10" t="str">
@@ -11224,7 +11320,7 @@
       <c r="F349" s="7"/>
       <c r="G349" s="7"/>
       <c r="H349" s="7"/>
-      <c r="I349" s="8"/>
+      <c r="I349" s="12"/>
       <c r="J349" s="9"/>
       <c r="K349" s="7"/>
       <c r="L349" s="10" t="str">
@@ -11254,7 +11350,7 @@
       <c r="F350" s="7"/>
       <c r="G350" s="7"/>
       <c r="H350" s="7"/>
-      <c r="I350" s="8"/>
+      <c r="I350" s="12"/>
       <c r="J350" s="9"/>
       <c r="K350" s="7"/>
       <c r="L350" s="10" t="str">
@@ -11284,7 +11380,7 @@
       <c r="F351" s="7"/>
       <c r="G351" s="7"/>
       <c r="H351" s="7"/>
-      <c r="I351" s="8"/>
+      <c r="I351" s="12"/>
       <c r="J351" s="9"/>
       <c r="K351" s="7"/>
       <c r="L351" s="10" t="str">
@@ -11314,7 +11410,7 @@
       <c r="F352" s="7"/>
       <c r="G352" s="7"/>
       <c r="H352" s="7"/>
-      <c r="I352" s="8"/>
+      <c r="I352" s="12"/>
       <c r="J352" s="9"/>
       <c r="K352" s="7"/>
       <c r="L352" s="10" t="str">
@@ -11344,7 +11440,7 @@
       <c r="F353" s="7"/>
       <c r="G353" s="7"/>
       <c r="H353" s="7"/>
-      <c r="I353" s="8"/>
+      <c r="I353" s="12"/>
       <c r="J353" s="9"/>
       <c r="K353" s="7"/>
       <c r="L353" s="10" t="str">
@@ -11374,7 +11470,7 @@
       <c r="F354" s="7"/>
       <c r="G354" s="7"/>
       <c r="H354" s="7"/>
-      <c r="I354" s="8"/>
+      <c r="I354" s="12"/>
       <c r="J354" s="9"/>
       <c r="K354" s="7"/>
       <c r="L354" s="10" t="str">
@@ -11404,7 +11500,7 @@
       <c r="F355" s="7"/>
       <c r="G355" s="7"/>
       <c r="H355" s="7"/>
-      <c r="I355" s="8"/>
+      <c r="I355" s="12"/>
       <c r="J355" s="9"/>
       <c r="K355" s="7"/>
       <c r="L355" s="10" t="str">
@@ -11434,7 +11530,7 @@
       <c r="F356" s="7"/>
       <c r="G356" s="7"/>
       <c r="H356" s="7"/>
-      <c r="I356" s="8"/>
+      <c r="I356" s="12"/>
       <c r="J356" s="9"/>
       <c r="K356" s="7"/>
       <c r="L356" s="10" t="str">
@@ -11464,7 +11560,7 @@
       <c r="F357" s="7"/>
       <c r="G357" s="7"/>
       <c r="H357" s="7"/>
-      <c r="I357" s="8"/>
+      <c r="I357" s="12"/>
       <c r="J357" s="9"/>
       <c r="K357" s="7"/>
       <c r="L357" s="10" t="str">
@@ -11494,7 +11590,7 @@
       <c r="F358" s="7"/>
       <c r="G358" s="7"/>
       <c r="H358" s="7"/>
-      <c r="I358" s="8"/>
+      <c r="I358" s="12"/>
       <c r="J358" s="9"/>
       <c r="K358" s="7"/>
       <c r="L358" s="10" t="str">
@@ -11524,7 +11620,7 @@
       <c r="F359" s="7"/>
       <c r="G359" s="7"/>
       <c r="H359" s="7"/>
-      <c r="I359" s="8"/>
+      <c r="I359" s="12"/>
       <c r="J359" s="9"/>
       <c r="K359" s="7"/>
       <c r="L359" s="10" t="str">
@@ -11554,7 +11650,7 @@
       <c r="F360" s="7"/>
       <c r="G360" s="7"/>
       <c r="H360" s="7"/>
-      <c r="I360" s="8"/>
+      <c r="I360" s="12"/>
       <c r="J360" s="9"/>
       <c r="K360" s="7"/>
       <c r="L360" s="10" t="str">
@@ -11584,7 +11680,7 @@
       <c r="F361" s="7"/>
       <c r="G361" s="7"/>
       <c r="H361" s="7"/>
-      <c r="I361" s="8"/>
+      <c r="I361" s="12"/>
       <c r="J361" s="9"/>
       <c r="K361" s="7"/>
       <c r="L361" s="10" t="str">
@@ -11614,7 +11710,7 @@
       <c r="F362" s="7"/>
       <c r="G362" s="7"/>
       <c r="H362" s="7"/>
-      <c r="I362" s="8"/>
+      <c r="I362" s="12"/>
       <c r="J362" s="9"/>
       <c r="K362" s="7"/>
       <c r="L362" s="10" t="str">
@@ -11644,7 +11740,7 @@
       <c r="F363" s="7"/>
       <c r="G363" s="7"/>
       <c r="H363" s="7"/>
-      <c r="I363" s="8"/>
+      <c r="I363" s="12"/>
       <c r="J363" s="9"/>
       <c r="K363" s="7"/>
       <c r="L363" s="10" t="str">
@@ -11674,7 +11770,7 @@
       <c r="F364" s="7"/>
       <c r="G364" s="7"/>
       <c r="H364" s="7"/>
-      <c r="I364" s="8"/>
+      <c r="I364" s="12"/>
       <c r="J364" s="9"/>
       <c r="K364" s="7"/>
       <c r="L364" s="10" t="str">
@@ -11704,7 +11800,7 @@
       <c r="F365" s="7"/>
       <c r="G365" s="7"/>
       <c r="H365" s="7"/>
-      <c r="I365" s="8"/>
+      <c r="I365" s="12"/>
       <c r="J365" s="9"/>
       <c r="K365" s="7"/>
       <c r="L365" s="10" t="str">
@@ -11734,7 +11830,7 @@
       <c r="F366" s="7"/>
       <c r="G366" s="7"/>
       <c r="H366" s="7"/>
-      <c r="I366" s="8"/>
+      <c r="I366" s="12"/>
       <c r="J366" s="9"/>
       <c r="K366" s="7"/>
       <c r="L366" s="10" t="str">
@@ -11764,7 +11860,7 @@
       <c r="F367" s="7"/>
       <c r="G367" s="7"/>
       <c r="H367" s="7"/>
-      <c r="I367" s="8"/>
+      <c r="I367" s="12"/>
       <c r="J367" s="9"/>
       <c r="K367" s="7"/>
       <c r="L367" s="10" t="str">
@@ -11794,7 +11890,7 @@
       <c r="F368" s="7"/>
       <c r="G368" s="7"/>
       <c r="H368" s="7"/>
-      <c r="I368" s="8"/>
+      <c r="I368" s="12"/>
       <c r="J368" s="9"/>
       <c r="K368" s="7"/>
       <c r="L368" s="10" t="str">
@@ -11824,7 +11920,7 @@
       <c r="F369" s="7"/>
       <c r="G369" s="7"/>
       <c r="H369" s="7"/>
-      <c r="I369" s="8"/>
+      <c r="I369" s="12"/>
       <c r="J369" s="9"/>
       <c r="K369" s="7"/>
       <c r="L369" s="10" t="str">
@@ -11854,7 +11950,7 @@
       <c r="F370" s="7"/>
       <c r="G370" s="7"/>
       <c r="H370" s="7"/>
-      <c r="I370" s="8"/>
+      <c r="I370" s="12"/>
       <c r="J370" s="9"/>
       <c r="K370" s="7"/>
       <c r="L370" s="10" t="str">
@@ -11884,7 +11980,7 @@
       <c r="F371" s="7"/>
       <c r="G371" s="7"/>
       <c r="H371" s="7"/>
-      <c r="I371" s="8"/>
+      <c r="I371" s="12"/>
       <c r="J371" s="9"/>
       <c r="K371" s="7"/>
       <c r="L371" s="10" t="str">
@@ -11914,7 +12010,7 @@
       <c r="F372" s="7"/>
       <c r="G372" s="7"/>
       <c r="H372" s="7"/>
-      <c r="I372" s="8"/>
+      <c r="I372" s="12"/>
       <c r="J372" s="9"/>
       <c r="K372" s="7"/>
       <c r="L372" s="10" t="str">
@@ -11944,7 +12040,7 @@
       <c r="F373" s="7"/>
       <c r="G373" s="7"/>
       <c r="H373" s="7"/>
-      <c r="I373" s="8"/>
+      <c r="I373" s="12"/>
       <c r="J373" s="9"/>
       <c r="K373" s="7"/>
       <c r="L373" s="10" t="str">
@@ -11974,7 +12070,7 @@
       <c r="F374" s="7"/>
       <c r="G374" s="7"/>
       <c r="H374" s="7"/>
-      <c r="I374" s="8"/>
+      <c r="I374" s="12"/>
       <c r="J374" s="9"/>
       <c r="K374" s="7"/>
       <c r="L374" s="10" t="str">
@@ -12004,7 +12100,7 @@
       <c r="F375" s="7"/>
       <c r="G375" s="7"/>
       <c r="H375" s="7"/>
-      <c r="I375" s="8"/>
+      <c r="I375" s="12"/>
       <c r="J375" s="9"/>
       <c r="K375" s="7"/>
       <c r="L375" s="10" t="str">
@@ -12034,7 +12130,7 @@
       <c r="F376" s="7"/>
       <c r="G376" s="7"/>
       <c r="H376" s="7"/>
-      <c r="I376" s="8"/>
+      <c r="I376" s="12"/>
       <c r="J376" s="9"/>
       <c r="K376" s="7"/>
       <c r="L376" s="10" t="str">
@@ -12064,7 +12160,7 @@
       <c r="F377" s="7"/>
       <c r="G377" s="7"/>
       <c r="H377" s="7"/>
-      <c r="I377" s="8"/>
+      <c r="I377" s="12"/>
       <c r="J377" s="9"/>
       <c r="K377" s="7"/>
       <c r="L377" s="10" t="str">
@@ -12094,7 +12190,7 @@
       <c r="F378" s="7"/>
       <c r="G378" s="7"/>
       <c r="H378" s="7"/>
-      <c r="I378" s="8"/>
+      <c r="I378" s="12"/>
       <c r="J378" s="9"/>
       <c r="K378" s="7"/>
       <c r="L378" s="10" t="str">
@@ -12124,7 +12220,7 @@
       <c r="F379" s="7"/>
       <c r="G379" s="7"/>
       <c r="H379" s="7"/>
-      <c r="I379" s="8"/>
+      <c r="I379" s="12"/>
       <c r="J379" s="9"/>
       <c r="K379" s="7"/>
       <c r="L379" s="10" t="str">
@@ -12154,7 +12250,7 @@
       <c r="F380" s="7"/>
       <c r="G380" s="7"/>
       <c r="H380" s="7"/>
-      <c r="I380" s="8"/>
+      <c r="I380" s="12"/>
       <c r="J380" s="9"/>
       <c r="K380" s="7"/>
       <c r="L380" s="10" t="str">
@@ -12184,7 +12280,7 @@
       <c r="F381" s="7"/>
       <c r="G381" s="7"/>
       <c r="H381" s="7"/>
-      <c r="I381" s="8"/>
+      <c r="I381" s="12"/>
       <c r="J381" s="9"/>
       <c r="K381" s="7"/>
       <c r="L381" s="10" t="str">
@@ -12214,7 +12310,7 @@
       <c r="F382" s="7"/>
       <c r="G382" s="7"/>
       <c r="H382" s="7"/>
-      <c r="I382" s="8"/>
+      <c r="I382" s="12"/>
       <c r="J382" s="9"/>
       <c r="K382" s="7"/>
       <c r="L382" s="10" t="str">
@@ -12244,7 +12340,7 @@
       <c r="F383" s="7"/>
       <c r="G383" s="7"/>
       <c r="H383" s="7"/>
-      <c r="I383" s="8"/>
+      <c r="I383" s="12"/>
       <c r="J383" s="9"/>
       <c r="K383" s="7"/>
       <c r="L383" s="10" t="str">
@@ -12274,7 +12370,7 @@
       <c r="F384" s="7"/>
       <c r="G384" s="7"/>
       <c r="H384" s="7"/>
-      <c r="I384" s="8"/>
+      <c r="I384" s="12"/>
       <c r="J384" s="9"/>
       <c r="K384" s="7"/>
       <c r="L384" s="10" t="str">
@@ -12304,7 +12400,7 @@
       <c r="F385" s="7"/>
       <c r="G385" s="7"/>
       <c r="H385" s="7"/>
-      <c r="I385" s="8"/>
+      <c r="I385" s="12"/>
       <c r="J385" s="9"/>
       <c r="K385" s="7"/>
       <c r="L385" s="10" t="str">
@@ -12334,7 +12430,7 @@
       <c r="F386" s="7"/>
       <c r="G386" s="7"/>
       <c r="H386" s="7"/>
-      <c r="I386" s="8"/>
+      <c r="I386" s="12"/>
       <c r="J386" s="9"/>
       <c r="K386" s="7"/>
       <c r="L386" s="10" t="str">
@@ -12364,7 +12460,7 @@
       <c r="F387" s="7"/>
       <c r="G387" s="7"/>
       <c r="H387" s="7"/>
-      <c r="I387" s="8"/>
+      <c r="I387" s="12"/>
       <c r="J387" s="9"/>
       <c r="K387" s="7"/>
       <c r="L387" s="10" t="str">
@@ -12394,7 +12490,7 @@
       <c r="F388" s="7"/>
       <c r="G388" s="7"/>
       <c r="H388" s="7"/>
-      <c r="I388" s="8"/>
+      <c r="I388" s="12"/>
       <c r="J388" s="9"/>
       <c r="K388" s="7"/>
       <c r="L388" s="10" t="str">
@@ -12424,7 +12520,7 @@
       <c r="F389" s="7"/>
       <c r="G389" s="7"/>
       <c r="H389" s="7"/>
-      <c r="I389" s="8"/>
+      <c r="I389" s="12"/>
       <c r="J389" s="9"/>
       <c r="K389" s="7"/>
       <c r="L389" s="10" t="str">
@@ -12454,7 +12550,7 @@
       <c r="F390" s="7"/>
       <c r="G390" s="7"/>
       <c r="H390" s="7"/>
-      <c r="I390" s="8"/>
+      <c r="I390" s="12"/>
       <c r="J390" s="9"/>
       <c r="K390" s="7"/>
       <c r="L390" s="10" t="str">
@@ -12484,7 +12580,7 @@
       <c r="F391" s="7"/>
       <c r="G391" s="7"/>
       <c r="H391" s="7"/>
-      <c r="I391" s="8"/>
+      <c r="I391" s="12"/>
       <c r="J391" s="9"/>
       <c r="K391" s="7"/>
       <c r="L391" s="10" t="str">
@@ -12514,7 +12610,7 @@
       <c r="F392" s="7"/>
       <c r="G392" s="7"/>
       <c r="H392" s="7"/>
-      <c r="I392" s="8"/>
+      <c r="I392" s="12"/>
       <c r="J392" s="9"/>
       <c r="K392" s="7"/>
       <c r="L392" s="10" t="str">
@@ -12544,7 +12640,7 @@
       <c r="F393" s="7"/>
       <c r="G393" s="7"/>
       <c r="H393" s="7"/>
-      <c r="I393" s="8"/>
+      <c r="I393" s="12"/>
       <c r="J393" s="9"/>
       <c r="K393" s="7"/>
       <c r="L393" s="10" t="str">
@@ -12574,7 +12670,7 @@
       <c r="F394" s="7"/>
       <c r="G394" s="7"/>
       <c r="H394" s="7"/>
-      <c r="I394" s="8"/>
+      <c r="I394" s="12"/>
       <c r="J394" s="9"/>
       <c r="K394" s="7"/>
       <c r="L394" s="10" t="str">
@@ -12604,7 +12700,7 @@
       <c r="F395" s="7"/>
       <c r="G395" s="7"/>
       <c r="H395" s="7"/>
-      <c r="I395" s="8"/>
+      <c r="I395" s="12"/>
       <c r="J395" s="9"/>
       <c r="K395" s="7"/>
       <c r="L395" s="10" t="str">
@@ -12634,7 +12730,7 @@
       <c r="F396" s="7"/>
       <c r="G396" s="7"/>
       <c r="H396" s="7"/>
-      <c r="I396" s="8"/>
+      <c r="I396" s="12"/>
       <c r="J396" s="9"/>
       <c r="K396" s="7"/>
       <c r="L396" s="10" t="str">
@@ -12664,7 +12760,7 @@
       <c r="F397" s="7"/>
       <c r="G397" s="7"/>
       <c r="H397" s="7"/>
-      <c r="I397" s="8"/>
+      <c r="I397" s="12"/>
       <c r="J397" s="9"/>
       <c r="K397" s="7"/>
       <c r="L397" s="10" t="str">
@@ -12694,7 +12790,7 @@
       <c r="F398" s="7"/>
       <c r="G398" s="7"/>
       <c r="H398" s="7"/>
-      <c r="I398" s="8"/>
+      <c r="I398" s="12"/>
       <c r="J398" s="9"/>
       <c r="K398" s="7"/>
       <c r="L398" s="10" t="str">
@@ -12724,7 +12820,7 @@
       <c r="F399" s="7"/>
       <c r="G399" s="7"/>
       <c r="H399" s="7"/>
-      <c r="I399" s="8"/>
+      <c r="I399" s="12"/>
       <c r="J399" s="9"/>
       <c r="K399" s="7"/>
       <c r="L399" s="10" t="str">
@@ -12754,7 +12850,7 @@
       <c r="F400" s="7"/>
       <c r="G400" s="7"/>
       <c r="H400" s="7"/>
-      <c r="I400" s="8"/>
+      <c r="I400" s="12"/>
       <c r="J400" s="9"/>
       <c r="K400" s="7"/>
       <c r="L400" s="10" t="str">
@@ -12784,7 +12880,7 @@
       <c r="F401" s="7"/>
       <c r="G401" s="7"/>
       <c r="H401" s="7"/>
-      <c r="I401" s="8"/>
+      <c r="I401" s="12"/>
       <c r="J401" s="9"/>
       <c r="K401" s="7"/>
       <c r="L401" s="10" t="str">
@@ -12814,7 +12910,7 @@
       <c r="F402" s="7"/>
       <c r="G402" s="7"/>
       <c r="H402" s="7"/>
-      <c r="I402" s="8"/>
+      <c r="I402" s="12"/>
       <c r="J402" s="9"/>
       <c r="K402" s="7"/>
       <c r="L402" s="10" t="str">
@@ -12844,7 +12940,7 @@
       <c r="F403" s="7"/>
       <c r="G403" s="7"/>
       <c r="H403" s="7"/>
-      <c r="I403" s="8"/>
+      <c r="I403" s="12"/>
       <c r="J403" s="9"/>
       <c r="K403" s="7"/>
       <c r="L403" s="10" t="str">
@@ -12874,7 +12970,7 @@
       <c r="F404" s="7"/>
       <c r="G404" s="7"/>
       <c r="H404" s="7"/>
-      <c r="I404" s="8"/>
+      <c r="I404" s="12"/>
       <c r="J404" s="9"/>
       <c r="K404" s="7"/>
       <c r="L404" s="10" t="str">
@@ -12904,7 +13000,7 @@
       <c r="F405" s="7"/>
       <c r="G405" s="7"/>
       <c r="H405" s="7"/>
-      <c r="I405" s="8"/>
+      <c r="I405" s="12"/>
       <c r="J405" s="9"/>
       <c r="K405" s="7"/>
       <c r="L405" s="10" t="str">
@@ -12934,7 +13030,7 @@
       <c r="F406" s="7"/>
       <c r="G406" s="7"/>
       <c r="H406" s="7"/>
-      <c r="I406" s="8"/>
+      <c r="I406" s="12"/>
       <c r="J406" s="9"/>
       <c r="K406" s="7"/>
       <c r="L406" s="10" t="str">
@@ -12964,7 +13060,7 @@
       <c r="F407" s="7"/>
       <c r="G407" s="7"/>
       <c r="H407" s="7"/>
-      <c r="I407" s="8"/>
+      <c r="I407" s="12"/>
       <c r="J407" s="9"/>
       <c r="K407" s="7"/>
       <c r="L407" s="10" t="str">
@@ -12994,7 +13090,7 @@
       <c r="F408" s="7"/>
       <c r="G408" s="7"/>
       <c r="H408" s="7"/>
-      <c r="I408" s="8"/>
+      <c r="I408" s="12"/>
       <c r="J408" s="9"/>
       <c r="K408" s="7"/>
       <c r="L408" s="10" t="str">
@@ -13024,7 +13120,7 @@
       <c r="F409" s="7"/>
       <c r="G409" s="7"/>
       <c r="H409" s="7"/>
-      <c r="I409" s="8"/>
+      <c r="I409" s="12"/>
       <c r="J409" s="9"/>
       <c r="K409" s="7"/>
       <c r="L409" s="10" t="str">
@@ -13054,7 +13150,7 @@
       <c r="F410" s="7"/>
       <c r="G410" s="7"/>
       <c r="H410" s="7"/>
-      <c r="I410" s="8"/>
+      <c r="I410" s="12"/>
       <c r="J410" s="9"/>
       <c r="K410" s="7"/>
       <c r="L410" s="10" t="str">
@@ -13084,7 +13180,7 @@
       <c r="F411" s="7"/>
       <c r="G411" s="7"/>
       <c r="H411" s="7"/>
-      <c r="I411" s="8"/>
+      <c r="I411" s="12"/>
       <c r="J411" s="9"/>
       <c r="K411" s="7"/>
       <c r="L411" s="10" t="str">
@@ -13114,7 +13210,7 @@
       <c r="F412" s="7"/>
       <c r="G412" s="7"/>
       <c r="H412" s="7"/>
-      <c r="I412" s="8"/>
+      <c r="I412" s="12"/>
       <c r="J412" s="9"/>
       <c r="K412" s="7"/>
       <c r="L412" s="10" t="str">
@@ -13144,7 +13240,7 @@
       <c r="F413" s="7"/>
       <c r="G413" s="7"/>
       <c r="H413" s="7"/>
-      <c r="I413" s="8"/>
+      <c r="I413" s="12"/>
       <c r="J413" s="9"/>
       <c r="K413" s="7"/>
       <c r="L413" s="10" t="str">
@@ -13174,7 +13270,7 @@
       <c r="F414" s="7"/>
       <c r="G414" s="7"/>
       <c r="H414" s="7"/>
-      <c r="I414" s="8"/>
+      <c r="I414" s="12"/>
       <c r="J414" s="9"/>
       <c r="K414" s="7"/>
       <c r="L414" s="10" t="str">
@@ -13204,7 +13300,7 @@
       <c r="F415" s="7"/>
       <c r="G415" s="7"/>
       <c r="H415" s="7"/>
-      <c r="I415" s="8"/>
+      <c r="I415" s="12"/>
       <c r="J415" s="9"/>
       <c r="K415" s="7"/>
       <c r="L415" s="10" t="str">
@@ -13234,7 +13330,7 @@
       <c r="F416" s="7"/>
       <c r="G416" s="7"/>
       <c r="H416" s="7"/>
-      <c r="I416" s="8"/>
+      <c r="I416" s="12"/>
       <c r="J416" s="9"/>
       <c r="K416" s="7"/>
       <c r="L416" s="10" t="str">
@@ -13264,7 +13360,7 @@
       <c r="F417" s="7"/>
       <c r="G417" s="7"/>
       <c r="H417" s="7"/>
-      <c r="I417" s="8"/>
+      <c r="I417" s="12"/>
       <c r="J417" s="9"/>
       <c r="K417" s="7"/>
       <c r="L417" s="10" t="str">
@@ -13294,7 +13390,7 @@
       <c r="F418" s="7"/>
       <c r="G418" s="7"/>
       <c r="H418" s="7"/>
-      <c r="I418" s="8"/>
+      <c r="I418" s="12"/>
       <c r="J418" s="9"/>
       <c r="K418" s="7"/>
       <c r="L418" s="10" t="str">
@@ -13324,7 +13420,7 @@
       <c r="F419" s="7"/>
       <c r="G419" s="7"/>
       <c r="H419" s="7"/>
-      <c r="I419" s="8"/>
+      <c r="I419" s="12"/>
       <c r="J419" s="9"/>
       <c r="K419" s="7"/>
       <c r="L419" s="10" t="str">
@@ -13354,7 +13450,7 @@
       <c r="F420" s="7"/>
       <c r="G420" s="7"/>
       <c r="H420" s="7"/>
-      <c r="I420" s="8"/>
+      <c r="I420" s="12"/>
       <c r="J420" s="9"/>
       <c r="K420" s="7"/>
       <c r="L420" s="10" t="str">
@@ -13384,7 +13480,7 @@
       <c r="F421" s="7"/>
       <c r="G421" s="7"/>
       <c r="H421" s="7"/>
-      <c r="I421" s="8"/>
+      <c r="I421" s="12"/>
       <c r="J421" s="9"/>
       <c r="K421" s="7"/>
       <c r="L421" s="10" t="str">
@@ -13414,7 +13510,7 @@
       <c r="F422" s="7"/>
       <c r="G422" s="7"/>
       <c r="H422" s="7"/>
-      <c r="I422" s="8"/>
+      <c r="I422" s="12"/>
       <c r="J422" s="9"/>
       <c r="K422" s="7"/>
       <c r="L422" s="10" t="str">
@@ -13444,7 +13540,7 @@
       <c r="F423" s="7"/>
       <c r="G423" s="7"/>
       <c r="H423" s="7"/>
-      <c r="I423" s="8"/>
+      <c r="I423" s="12"/>
       <c r="J423" s="9"/>
       <c r="K423" s="7"/>
       <c r="L423" s="10" t="str">
@@ -13474,7 +13570,7 @@
       <c r="F424" s="7"/>
       <c r="G424" s="7"/>
       <c r="H424" s="7"/>
-      <c r="I424" s="8"/>
+      <c r="I424" s="12"/>
       <c r="J424" s="9"/>
       <c r="K424" s="7"/>
       <c r="L424" s="10" t="str">
@@ -13504,7 +13600,7 @@
       <c r="F425" s="7"/>
       <c r="G425" s="7"/>
       <c r="H425" s="7"/>
-      <c r="I425" s="8"/>
+      <c r="I425" s="12"/>
       <c r="J425" s="9"/>
       <c r="K425" s="7"/>
       <c r="L425" s="10" t="str">
@@ -13534,7 +13630,7 @@
       <c r="F426" s="7"/>
       <c r="G426" s="7"/>
       <c r="H426" s="7"/>
-      <c r="I426" s="8"/>
+      <c r="I426" s="12"/>
       <c r="J426" s="9"/>
       <c r="K426" s="7"/>
       <c r="L426" s="10" t="str">
@@ -13564,7 +13660,7 @@
       <c r="F427" s="7"/>
       <c r="G427" s="7"/>
       <c r="H427" s="7"/>
-      <c r="I427" s="8"/>
+      <c r="I427" s="12"/>
       <c r="J427" s="9"/>
       <c r="K427" s="7"/>
       <c r="L427" s="10" t="str">
@@ -13594,7 +13690,7 @@
       <c r="F428" s="7"/>
       <c r="G428" s="7"/>
       <c r="H428" s="7"/>
-      <c r="I428" s="8"/>
+      <c r="I428" s="12"/>
       <c r="J428" s="9"/>
       <c r="K428" s="7"/>
       <c r="L428" s="10" t="str">
@@ -13624,7 +13720,7 @@
       <c r="F429" s="7"/>
       <c r="G429" s="7"/>
       <c r="H429" s="7"/>
-      <c r="I429" s="8"/>
+      <c r="I429" s="12"/>
       <c r="J429" s="9"/>
       <c r="K429" s="7"/>
       <c r="L429" s="10" t="str">
@@ -13654,7 +13750,7 @@
       <c r="F430" s="7"/>
       <c r="G430" s="7"/>
       <c r="H430" s="7"/>
-      <c r="I430" s="8"/>
+      <c r="I430" s="12"/>
       <c r="J430" s="9"/>
       <c r="K430" s="7"/>
       <c r="L430" s="10" t="str">
@@ -13684,7 +13780,7 @@
       <c r="F431" s="7"/>
       <c r="G431" s="7"/>
       <c r="H431" s="7"/>
-      <c r="I431" s="8"/>
+      <c r="I431" s="12"/>
       <c r="J431" s="9"/>
       <c r="K431" s="7"/>
       <c r="L431" s="10" t="str">
@@ -13714,7 +13810,7 @@
       <c r="F432" s="7"/>
       <c r="G432" s="7"/>
       <c r="H432" s="7"/>
-      <c r="I432" s="8"/>
+      <c r="I432" s="12"/>
       <c r="J432" s="9"/>
       <c r="K432" s="7"/>
       <c r="L432" s="10" t="str">
@@ -13744,7 +13840,7 @@
       <c r="F433" s="7"/>
       <c r="G433" s="7"/>
       <c r="H433" s="7"/>
-      <c r="I433" s="8"/>
+      <c r="I433" s="12"/>
       <c r="J433" s="9"/>
       <c r="K433" s="7"/>
       <c r="L433" s="10" t="str">
@@ -13774,7 +13870,7 @@
       <c r="F434" s="7"/>
       <c r="G434" s="7"/>
       <c r="H434" s="7"/>
-      <c r="I434" s="8"/>
+      <c r="I434" s="12"/>
       <c r="J434" s="9"/>
       <c r="K434" s="7"/>
       <c r="L434" s="10" t="str">
@@ -13804,7 +13900,7 @@
       <c r="F435" s="7"/>
       <c r="G435" s="7"/>
       <c r="H435" s="7"/>
-      <c r="I435" s="8"/>
+      <c r="I435" s="12"/>
       <c r="J435" s="9"/>
       <c r="K435" s="7"/>
       <c r="L435" s="10" t="str">
@@ -13834,7 +13930,7 @@
       <c r="F436" s="7"/>
       <c r="G436" s="7"/>
       <c r="H436" s="7"/>
-      <c r="I436" s="8"/>
+      <c r="I436" s="12"/>
       <c r="J436" s="9"/>
       <c r="K436" s="7"/>
       <c r="L436" s="10" t="str">
@@ -13864,7 +13960,7 @@
       <c r="F437" s="7"/>
       <c r="G437" s="7"/>
       <c r="H437" s="7"/>
-      <c r="I437" s="8"/>
+      <c r="I437" s="12"/>
       <c r="J437" s="9"/>
       <c r="K437" s="7"/>
       <c r="L437" s="10" t="str">
@@ -13894,7 +13990,7 @@
       <c r="F438" s="7"/>
       <c r="G438" s="7"/>
       <c r="H438" s="7"/>
-      <c r="I438" s="8"/>
+      <c r="I438" s="12"/>
       <c r="J438" s="9"/>
       <c r="K438" s="7"/>
       <c r="L438" s="10" t="str">
@@ -13924,7 +14020,7 @@
       <c r="F439" s="7"/>
       <c r="G439" s="7"/>
       <c r="H439" s="7"/>
-      <c r="I439" s="8"/>
+      <c r="I439" s="12"/>
       <c r="J439" s="9"/>
       <c r="K439" s="7"/>
       <c r="L439" s="10" t="str">
@@ -13954,7 +14050,7 @@
       <c r="F440" s="7"/>
       <c r="G440" s="7"/>
       <c r="H440" s="7"/>
-      <c r="I440" s="8"/>
+      <c r="I440" s="12"/>
       <c r="J440" s="9"/>
       <c r="K440" s="7"/>
       <c r="L440" s="10" t="str">
@@ -13984,7 +14080,7 @@
       <c r="F441" s="7"/>
       <c r="G441" s="7"/>
       <c r="H441" s="7"/>
-      <c r="I441" s="8"/>
+      <c r="I441" s="12"/>
       <c r="J441" s="9"/>
       <c r="K441" s="7"/>
       <c r="L441" s="10" t="str">
@@ -14014,7 +14110,7 @@
       <c r="F442" s="7"/>
       <c r="G442" s="7"/>
       <c r="H442" s="7"/>
-      <c r="I442" s="8"/>
+      <c r="I442" s="12"/>
       <c r="J442" s="9"/>
       <c r="K442" s="7"/>
       <c r="L442" s="10" t="str">
@@ -14044,7 +14140,7 @@
       <c r="F443" s="7"/>
       <c r="G443" s="7"/>
       <c r="H443" s="7"/>
-      <c r="I443" s="8"/>
+      <c r="I443" s="12"/>
       <c r="J443" s="9"/>
       <c r="K443" s="7"/>
       <c r="L443" s="10" t="str">
@@ -14074,7 +14170,7 @@
       <c r="F444" s="7"/>
       <c r="G444" s="7"/>
       <c r="H444" s="7"/>
-      <c r="I444" s="8"/>
+      <c r="I444" s="12"/>
       <c r="J444" s="9"/>
       <c r="K444" s="7"/>
       <c r="L444" s="10" t="str">
@@ -14104,7 +14200,7 @@
       <c r="F445" s="7"/>
       <c r="G445" s="7"/>
       <c r="H445" s="7"/>
-      <c r="I445" s="8"/>
+      <c r="I445" s="12"/>
       <c r="J445" s="9"/>
       <c r="K445" s="7"/>
       <c r="L445" s="10" t="str">
@@ -14134,7 +14230,7 @@
       <c r="F446" s="7"/>
       <c r="G446" s="7"/>
       <c r="H446" s="7"/>
-      <c r="I446" s="8"/>
+      <c r="I446" s="12"/>
       <c r="J446" s="9"/>
       <c r="K446" s="7"/>
       <c r="L446" s="10" t="str">
@@ -14164,7 +14260,7 @@
       <c r="F447" s="7"/>
       <c r="G447" s="7"/>
       <c r="H447" s="7"/>
-      <c r="I447" s="8"/>
+      <c r="I447" s="12"/>
       <c r="J447" s="9"/>
       <c r="K447" s="7"/>
       <c r="L447" s="10" t="str">
@@ -14194,7 +14290,7 @@
       <c r="F448" s="7"/>
       <c r="G448" s="7"/>
       <c r="H448" s="7"/>
-      <c r="I448" s="8"/>
+      <c r="I448" s="12"/>
       <c r="J448" s="9"/>
       <c r="K448" s="7"/>
       <c r="L448" s="10" t="str">
@@ -14224,7 +14320,7 @@
       <c r="F449" s="7"/>
       <c r="G449" s="7"/>
       <c r="H449" s="7"/>
-      <c r="I449" s="8"/>
+      <c r="I449" s="12"/>
       <c r="J449" s="9"/>
       <c r="K449" s="7"/>
       <c r="L449" s="10" t="str">
@@ -14254,7 +14350,7 @@
       <c r="F450" s="7"/>
       <c r="G450" s="7"/>
       <c r="H450" s="7"/>
-      <c r="I450" s="8"/>
+      <c r="I450" s="12"/>
       <c r="J450" s="9"/>
       <c r="K450" s="7"/>
       <c r="L450" s="10" t="str">
@@ -14284,7 +14380,7 @@
       <c r="F451" s="7"/>
       <c r="G451" s="7"/>
       <c r="H451" s="7"/>
-      <c r="I451" s="8"/>
+      <c r="I451" s="12"/>
       <c r="J451" s="9"/>
       <c r="K451" s="7"/>
       <c r="L451" s="10" t="str">
@@ -14314,7 +14410,7 @@
       <c r="F452" s="7"/>
       <c r="G452" s="7"/>
       <c r="H452" s="7"/>
-      <c r="I452" s="8"/>
+      <c r="I452" s="12"/>
       <c r="J452" s="9"/>
       <c r="K452" s="7"/>
       <c r="L452" s="10" t="str">
@@ -14344,7 +14440,7 @@
       <c r="F453" s="7"/>
       <c r="G453" s="7"/>
       <c r="H453" s="7"/>
-      <c r="I453" s="8"/>
+      <c r="I453" s="12"/>
       <c r="J453" s="9"/>
       <c r="K453" s="7"/>
       <c r="L453" s="10" t="str">
@@ -14374,7 +14470,7 @@
       <c r="F454" s="7"/>
       <c r="G454" s="7"/>
       <c r="H454" s="7"/>
-      <c r="I454" s="8"/>
+      <c r="I454" s="12"/>
       <c r="J454" s="9"/>
       <c r="K454" s="7"/>
       <c r="L454" s="10" t="str">
@@ -14404,7 +14500,7 @@
       <c r="F455" s="7"/>
       <c r="G455" s="7"/>
       <c r="H455" s="7"/>
-      <c r="I455" s="8"/>
+      <c r="I455" s="12"/>
       <c r="J455" s="9"/>
       <c r="K455" s="7"/>
       <c r="L455" s="10" t="str">
@@ -14434,7 +14530,7 @@
       <c r="F456" s="7"/>
       <c r="G456" s="7"/>
       <c r="H456" s="7"/>
-      <c r="I456" s="8"/>
+      <c r="I456" s="12"/>
       <c r="J456" s="9"/>
       <c r="K456" s="7"/>
       <c r="L456" s="10" t="str">
@@ -14464,7 +14560,7 @@
       <c r="F457" s="7"/>
       <c r="G457" s="7"/>
       <c r="H457" s="7"/>
-      <c r="I457" s="8"/>
+      <c r="I457" s="12"/>
       <c r="J457" s="9"/>
       <c r="K457" s="7"/>
       <c r="L457" s="10" t="str">
@@ -14494,7 +14590,7 @@
       <c r="F458" s="7"/>
       <c r="G458" s="7"/>
       <c r="H458" s="7"/>
-      <c r="I458" s="8"/>
+      <c r="I458" s="12"/>
       <c r="J458" s="9"/>
       <c r="K458" s="7"/>
       <c r="L458" s="10" t="str">
@@ -14524,7 +14620,7 @@
       <c r="F459" s="7"/>
       <c r="G459" s="7"/>
       <c r="H459" s="7"/>
-      <c r="I459" s="8"/>
+      <c r="I459" s="12"/>
       <c r="J459" s="9"/>
       <c r="K459" s="7"/>
       <c r="L459" s="10" t="str">
@@ -14554,7 +14650,7 @@
       <c r="F460" s="7"/>
       <c r="G460" s="7"/>
       <c r="H460" s="7"/>
-      <c r="I460" s="8"/>
+      <c r="I460" s="12"/>
       <c r="J460" s="9"/>
       <c r="K460" s="7"/>
       <c r="L460" s="10" t="str">
@@ -14584,7 +14680,7 @@
       <c r="F461" s="7"/>
       <c r="G461" s="7"/>
       <c r="H461" s="7"/>
-      <c r="I461" s="8"/>
+      <c r="I461" s="12"/>
       <c r="J461" s="9"/>
       <c r="K461" s="7"/>
       <c r="L461" s="10" t="str">
@@ -14614,7 +14710,7 @@
       <c r="F462" s="7"/>
       <c r="G462" s="7"/>
       <c r="H462" s="7"/>
-      <c r="I462" s="8"/>
+      <c r="I462" s="12"/>
       <c r="J462" s="9"/>
       <c r="K462" s="7"/>
       <c r="L462" s="10" t="str">
@@ -14644,7 +14740,7 @@
       <c r="F463" s="7"/>
       <c r="G463" s="7"/>
       <c r="H463" s="7"/>
-      <c r="I463" s="8"/>
+      <c r="I463" s="12"/>
       <c r="J463" s="9"/>
       <c r="K463" s="7"/>
       <c r="L463" s="10" t="str">
@@ -14674,7 +14770,7 @@
       <c r="F464" s="7"/>
       <c r="G464" s="7"/>
       <c r="H464" s="7"/>
-      <c r="I464" s="8"/>
+      <c r="I464" s="12"/>
       <c r="J464" s="9"/>
       <c r="K464" s="7"/>
       <c r="L464" s="10" t="str">
@@ -14704,7 +14800,7 @@
       <c r="F465" s="7"/>
       <c r="G465" s="7"/>
       <c r="H465" s="7"/>
-      <c r="I465" s="8"/>
+      <c r="I465" s="12"/>
       <c r="J465" s="9"/>
       <c r="K465" s="7"/>
       <c r="L465" s="10" t="str">
@@ -14734,7 +14830,7 @@
       <c r="F466" s="7"/>
       <c r="G466" s="7"/>
       <c r="H466" s="7"/>
-      <c r="I466" s="8"/>
+      <c r="I466" s="12"/>
       <c r="J466" s="9"/>
       <c r="K466" s="7"/>
       <c r="L466" s="10" t="str">
@@ -14764,7 +14860,7 @@
       <c r="F467" s="7"/>
       <c r="G467" s="7"/>
       <c r="H467" s="7"/>
-      <c r="I467" s="8"/>
+      <c r="I467" s="12"/>
       <c r="J467" s="9"/>
       <c r="K467" s="7"/>
       <c r="L467" s="10" t="str">
@@ -14794,7 +14890,7 @@
       <c r="F468" s="7"/>
       <c r="G468" s="7"/>
       <c r="H468" s="7"/>
-      <c r="I468" s="8"/>
+      <c r="I468" s="12"/>
       <c r="J468" s="9"/>
       <c r="K468" s="7"/>
       <c r="L468" s="10" t="str">
@@ -14824,7 +14920,7 @@
       <c r="F469" s="7"/>
       <c r="G469" s="7"/>
       <c r="H469" s="7"/>
-      <c r="I469" s="8"/>
+      <c r="I469" s="12"/>
       <c r="J469" s="9"/>
       <c r="K469" s="7"/>
       <c r="L469" s="10" t="str">
@@ -14854,7 +14950,7 @@
       <c r="F470" s="7"/>
       <c r="G470" s="7"/>
       <c r="H470" s="7"/>
-      <c r="I470" s="8"/>
+      <c r="I470" s="12"/>
       <c r="J470" s="9"/>
       <c r="K470" s="7"/>
       <c r="L470" s="10" t="str">
@@ -14884,7 +14980,7 @@
       <c r="F471" s="7"/>
       <c r="G471" s="7"/>
       <c r="H471" s="7"/>
-      <c r="I471" s="8"/>
+      <c r="I471" s="12"/>
       <c r="J471" s="9"/>
       <c r="K471" s="7"/>
       <c r="L471" s="10" t="str">
@@ -14914,7 +15010,7 @@
       <c r="F472" s="7"/>
       <c r="G472" s="7"/>
       <c r="H472" s="7"/>
-      <c r="I472" s="8"/>
+      <c r="I472" s="12"/>
       <c r="J472" s="9"/>
       <c r="K472" s="7"/>
       <c r="L472" s="10" t="str">
@@ -14944,7 +15040,7 @@
       <c r="F473" s="7"/>
       <c r="G473" s="7"/>
       <c r="H473" s="7"/>
-      <c r="I473" s="8"/>
+      <c r="I473" s="12"/>
       <c r="J473" s="9"/>
       <c r="K473" s="7"/>
       <c r="L473" s="10" t="str">
@@ -14974,7 +15070,7 @@
       <c r="F474" s="7"/>
       <c r="G474" s="7"/>
       <c r="H474" s="7"/>
-      <c r="I474" s="8"/>
+      <c r="I474" s="12"/>
       <c r="J474" s="9"/>
       <c r="K474" s="7"/>
       <c r="L474" s="10" t="str">
@@ -15004,7 +15100,7 @@
       <c r="F475" s="7"/>
       <c r="G475" s="7"/>
       <c r="H475" s="7"/>
-      <c r="I475" s="8"/>
+      <c r="I475" s="12"/>
       <c r="J475" s="9"/>
       <c r="K475" s="7"/>
       <c r="L475" s="10" t="str">
@@ -15034,7 +15130,7 @@
       <c r="F476" s="7"/>
       <c r="G476" s="7"/>
       <c r="H476" s="7"/>
-      <c r="I476" s="8"/>
+      <c r="I476" s="12"/>
       <c r="J476" s="9"/>
       <c r="K476" s="7"/>
       <c r="L476" s="10" t="str">
@@ -15064,7 +15160,7 @@
       <c r="F477" s="7"/>
       <c r="G477" s="7"/>
       <c r="H477" s="7"/>
-      <c r="I477" s="8"/>
+      <c r="I477" s="12"/>
       <c r="J477" s="9"/>
       <c r="K477" s="7"/>
       <c r="L477" s="10" t="str">
@@ -15094,7 +15190,7 @@
       <c r="F478" s="7"/>
       <c r="G478" s="7"/>
       <c r="H478" s="7"/>
-      <c r="I478" s="8"/>
+      <c r="I478" s="12"/>
       <c r="J478" s="9"/>
       <c r="K478" s="7"/>
       <c r="L478" s="10" t="str">
@@ -15124,7 +15220,7 @@
       <c r="F479" s="7"/>
       <c r="G479" s="7"/>
       <c r="H479" s="7"/>
-      <c r="I479" s="8"/>
+      <c r="I479" s="12"/>
       <c r="J479" s="9"/>
       <c r="K479" s="7"/>
       <c r="L479" s="10" t="str">
@@ -15154,7 +15250,7 @@
       <c r="F480" s="7"/>
       <c r="G480" s="7"/>
       <c r="H480" s="7"/>
-      <c r="I480" s="8"/>
+      <c r="I480" s="12"/>
       <c r="J480" s="9"/>
       <c r="K480" s="7"/>
       <c r="L480" s="10" t="str">
@@ -15184,7 +15280,7 @@
       <c r="F481" s="7"/>
       <c r="G481" s="7"/>
       <c r="H481" s="7"/>
-      <c r="I481" s="8"/>
+      <c r="I481" s="12"/>
       <c r="J481" s="9"/>
       <c r="K481" s="7"/>
       <c r="L481" s="10" t="str">
@@ -15214,7 +15310,7 @@
       <c r="F482" s="7"/>
       <c r="G482" s="7"/>
       <c r="H482" s="7"/>
-      <c r="I482" s="8"/>
+      <c r="I482" s="12"/>
       <c r="J482" s="9"/>
       <c r="K482" s="7"/>
       <c r="L482" s="10" t="str">
@@ -15244,7 +15340,7 @@
       <c r="F483" s="7"/>
       <c r="G483" s="7"/>
       <c r="H483" s="7"/>
-      <c r="I483" s="8"/>
+      <c r="I483" s="12"/>
       <c r="J483" s="9"/>
       <c r="K483" s="7"/>
       <c r="L483" s="10" t="str">
@@ -15274,7 +15370,7 @@
       <c r="F484" s="7"/>
       <c r="G484" s="7"/>
       <c r="H484" s="7"/>
-      <c r="I484" s="8"/>
+      <c r="I484" s="12"/>
       <c r="J484" s="9"/>
       <c r="K484" s="7"/>
       <c r="L484" s="10" t="str">
@@ -15304,7 +15400,7 @@
       <c r="F485" s="7"/>
       <c r="G485" s="7"/>
       <c r="H485" s="7"/>
-      <c r="I485" s="8"/>
+      <c r="I485" s="12"/>
       <c r="J485" s="9"/>
       <c r="K485" s="7"/>
       <c r="L485" s="10" t="str">
@@ -15334,7 +15430,7 @@
       <c r="F486" s="7"/>
       <c r="G486" s="7"/>
       <c r="H486" s="7"/>
-      <c r="I486" s="8"/>
+      <c r="I486" s="12"/>
       <c r="J486" s="9"/>
       <c r="K486" s="7"/>
       <c r="L486" s="10" t="str">
@@ -15364,7 +15460,7 @@
       <c r="F487" s="7"/>
       <c r="G487" s="7"/>
       <c r="H487" s="7"/>
-      <c r="I487" s="8"/>
+      <c r="I487" s="12"/>
       <c r="J487" s="9"/>
       <c r="K487" s="7"/>
       <c r="L487" s="10" t="str">
@@ -15394,7 +15490,7 @@
       <c r="F488" s="7"/>
       <c r="G488" s="7"/>
       <c r="H488" s="7"/>
-      <c r="I488" s="8"/>
+      <c r="I488" s="12"/>
       <c r="J488" s="9"/>
       <c r="K488" s="7"/>
       <c r="L488" s="10" t="str">
@@ -15424,7 +15520,7 @@
       <c r="F489" s="7"/>
       <c r="G489" s="7"/>
       <c r="H489" s="7"/>
-      <c r="I489" s="8"/>
+      <c r="I489" s="12"/>
       <c r="J489" s="9"/>
       <c r="K489" s="7"/>
       <c r="L489" s="10" t="str">
@@ -15454,7 +15550,7 @@
       <c r="F490" s="7"/>
       <c r="G490" s="7"/>
       <c r="H490" s="7"/>
-      <c r="I490" s="8"/>
+      <c r="I490" s="12"/>
       <c r="J490" s="9"/>
       <c r="K490" s="7"/>
       <c r="L490" s="10" t="str">
@@ -15484,7 +15580,7 @@
       <c r="F491" s="7"/>
       <c r="G491" s="7"/>
       <c r="H491" s="7"/>
-      <c r="I491" s="8"/>
+      <c r="I491" s="12"/>
       <c r="J491" s="9"/>
       <c r="K491" s="7"/>
       <c r="L491" s="10" t="str">
@@ -15514,7 +15610,7 @@
       <c r="F492" s="7"/>
       <c r="G492" s="7"/>
       <c r="H492" s="7"/>
-      <c r="I492" s="8"/>
+      <c r="I492" s="12"/>
       <c r="J492" s="9"/>
       <c r="K492" s="7"/>
       <c r="L492" s="10" t="str">
@@ -15544,7 +15640,7 @@
       <c r="F493" s="7"/>
       <c r="G493" s="7"/>
       <c r="H493" s="7"/>
-      <c r="I493" s="8"/>
+      <c r="I493" s="12"/>
       <c r="J493" s="9"/>
       <c r="K493" s="7"/>
       <c r="L493" s="10" t="str">
@@ -15574,7 +15670,7 @@
       <c r="F494" s="7"/>
       <c r="G494" s="7"/>
       <c r="H494" s="7"/>
-      <c r="I494" s="8"/>
+      <c r="I494" s="12"/>
       <c r="J494" s="9"/>
       <c r="K494" s="7"/>
       <c r="L494" s="10" t="str">
@@ -15604,7 +15700,7 @@
       <c r="F495" s="7"/>
       <c r="G495" s="7"/>
       <c r="H495" s="7"/>
-      <c r="I495" s="8"/>
+      <c r="I495" s="12"/>
       <c r="J495" s="9"/>
       <c r="K495" s="7"/>
       <c r="L495" s="10" t="str">
@@ -15634,7 +15730,7 @@
       <c r="F496" s="7"/>
       <c r="G496" s="7"/>
       <c r="H496" s="7"/>
-      <c r="I496" s="8"/>
+      <c r="I496" s="12"/>
       <c r="J496" s="9"/>
       <c r="K496" s="7"/>
       <c r="L496" s="10" t="str">
@@ -15664,7 +15760,7 @@
       <c r="F497" s="7"/>
       <c r="G497" s="7"/>
       <c r="H497" s="7"/>
-      <c r="I497" s="8"/>
+      <c r="I497" s="12"/>
       <c r="J497" s="9"/>
       <c r="K497" s="7"/>
       <c r="L497" s="10" t="str">
@@ -15694,7 +15790,7 @@
       <c r="F498" s="7"/>
       <c r="G498" s="7"/>
       <c r="H498" s="7"/>
-      <c r="I498" s="8"/>
+      <c r="I498" s="12"/>
       <c r="J498" s="9"/>
       <c r="K498" s="7"/>
       <c r="L498" s="10" t="str">
@@ -15724,7 +15820,7 @@
       <c r="F499" s="7"/>
       <c r="G499" s="7"/>
       <c r="H499" s="7"/>
-      <c r="I499" s="8"/>
+      <c r="I499" s="12"/>
       <c r="J499" s="9"/>
       <c r="K499" s="7"/>
       <c r="L499" s="10" t="str">
@@ -15754,7 +15850,7 @@
       <c r="F500" s="7"/>
       <c r="G500" s="7"/>
       <c r="H500" s="7"/>
-      <c r="I500" s="8"/>
+      <c r="I500" s="12"/>
       <c r="J500" s="9"/>
       <c r="K500" s="7"/>
       <c r="L500" s="10" t="str">
@@ -15784,7 +15880,7 @@
       <c r="F501" s="7"/>
       <c r="G501" s="7"/>
       <c r="H501" s="7"/>
-      <c r="I501" s="8"/>
+      <c r="I501" s="12"/>
       <c r="J501" s="9"/>
       <c r="K501" s="7"/>
       <c r="L501" s="10" t="str">
@@ -15814,7 +15910,7 @@
       <c r="F502" s="7"/>
       <c r="G502" s="7"/>
       <c r="H502" s="7"/>
-      <c r="I502" s="8"/>
+      <c r="I502" s="12"/>
       <c r="J502" s="9"/>
       <c r="K502" s="7"/>
       <c r="L502" s="10" t="str">
@@ -15844,7 +15940,7 @@
       <c r="F503" s="7"/>
       <c r="G503" s="7"/>
       <c r="H503" s="7"/>
-      <c r="I503" s="8"/>
+      <c r="I503" s="12"/>
       <c r="J503" s="9"/>
       <c r="K503" s="7"/>
       <c r="L503" s="10" t="str">
@@ -15873,7 +15969,7 @@
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="D4:D503" type="list">
-      <formula1>"DIMM (Desktop),Gaming DIMM (Heat Spreader),SODIMM (Laptop),Server (ECC/RDIMM),Mixed"</formula1>
+      <formula1>"Regular,Server/Gaming (Heat Spreader),DIMM (Desktop),SODIMM (Laptop),Mixed"</formula1>
       <formula2>0</formula2>
     </dataValidation>
     <dataValidation allowBlank="true" errorStyle="stop" operator="between" showDropDown="false" showErrorMessage="false" showInputMessage="false" sqref="K4:K503" type="list">
@@ -15897,548 +15993,665 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:F38"/>
+  <dimension ref="A1:L38"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="22"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>20</v>
+        <v>25</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" s="13" t="n">
+      <c r="A3" s="13" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" s="14" t="n">
         <f aca="false">COUNT(Purchases!J4:J503)</f>
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="12" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="14" t="n">
+      <c r="A4" s="13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B4" s="15" t="n">
         <f aca="false">SUM(Purchases!J4:J503)</f>
-        <v>967.5</v>
+        <v>1882.5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="B5" s="15" t="n">
+      <c r="A5" s="13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B5" s="16" t="n">
         <f aca="false">SUM(Purchases!H4:H503)</f>
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="B6" s="16" t="n">
+      <c r="A6" s="13" t="s">
+        <v>29</v>
+      </c>
+      <c r="B6" s="17" t="n">
         <f aca="false">SUM(Purchases!I4:I503)</f>
-        <v>15</v>
+        <v>32.1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="12" t="s">
+      <c r="A7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="15" t="n">
+      <c r="B7" s="16" t="n">
         <f aca="false">SUM(Purchases!L4:L503)</f>
         <v>0</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="12" t="s">
-        <v>25</v>
-      </c>
-      <c r="B8" s="14" t="n">
+      <c r="A8" s="13" t="s">
+        <v>30</v>
+      </c>
+      <c r="B8" s="15" t="n">
         <f aca="false">IF(B5=0,0,B4/B5)</f>
         <v>0</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
-        <v>26</v>
-      </c>
-      <c r="B9" s="14" t="n">
+      <c r="A9" s="13" t="s">
+        <v>31</v>
+      </c>
+      <c r="B9" s="15" t="n">
         <f aca="false">IF(B6=0,0,B4/B6)</f>
-        <v>64.5</v>
+        <v>58.6448598130841</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="B10" s="14" t="n">
+      <c r="A10" s="13" t="s">
+        <v>32</v>
+      </c>
+      <c r="B10" s="15" t="n">
         <f aca="false">IF(B7=0,0,B4/B7)</f>
         <v>0</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="17" t="s">
-        <v>28</v>
+      <c r="A13" s="18" t="s">
+        <v>33</v>
+      </c>
+      <c r="H13" s="19" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="18" t="s">
-        <v>29</v>
-      </c>
-      <c r="B14" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C14" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D14" s="18" t="s">
-        <v>32</v>
-      </c>
-      <c r="E14" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="F14" s="18" t="s">
-        <v>34</v>
+      <c r="A14" s="20" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="20" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D14" s="20" t="s">
+        <v>38</v>
+      </c>
+      <c r="E14" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="F14" s="20" t="s">
+        <v>40</v>
+      </c>
+      <c r="H14" s="21" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" s="21" t="s">
+        <v>42</v>
+      </c>
+      <c r="J14" s="21" t="s">
+        <v>10</v>
+      </c>
+      <c r="K14" s="21" t="s">
+        <v>39</v>
+      </c>
+      <c r="L14" s="21" t="s">
+        <v>43</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="13" t="s">
-        <v>35</v>
-      </c>
-      <c r="B15" s="13" t="n">
+      <c r="A15" s="14" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A15)</f>
         <v>0</v>
       </c>
-      <c r="C15" s="13" t="n">
+      <c r="C15" s="14" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A15,Purchases!H4:H503)</f>
         <v>0</v>
       </c>
-      <c r="D15" s="13" t="n">
+      <c r="D15" s="14" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A15,Purchases!L4:L503)</f>
         <v>0</v>
       </c>
-      <c r="E15" s="14" t="n">
+      <c r="E15" s="15" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A15,Purchases!J4:J503)</f>
         <v>0</v>
       </c>
-      <c r="F15" s="14" t="n">
+      <c r="F15" s="15" t="n">
         <f aca="false">IF(C15=0,0,E15/C15)</f>
         <v>0</v>
       </c>
+      <c r="H15" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="I15" s="22" t="n">
+        <f aca="false">COUNTIF(Purchases!D4:D503,H15)</f>
+        <v>3</v>
+      </c>
+      <c r="J15" s="23" t="n">
+        <f aca="false">SUMIF(Purchases!D4:D503,H15,Purchases!I4:I503)</f>
+        <v>13.875</v>
+      </c>
+      <c r="K15" s="24" t="n">
+        <f aca="false">SUMIF(Purchases!D4:D503,H15,Purchases!J4:J503)</f>
+        <v>971.25</v>
+      </c>
+      <c r="L15" s="24" t="n">
+        <f aca="false">IF(J15=0,0,K15/J15)</f>
+        <v>70</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="13" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="13" t="n">
+      <c r="A16" s="14" t="s">
+        <v>45</v>
+      </c>
+      <c r="B16" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A16)</f>
         <v>0</v>
       </c>
-      <c r="C16" s="13" t="n">
+      <c r="C16" s="14" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A16,Purchases!H4:H503)</f>
         <v>0</v>
       </c>
-      <c r="D16" s="13" t="n">
+      <c r="D16" s="14" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A16,Purchases!L4:L503)</f>
         <v>0</v>
       </c>
-      <c r="E16" s="14" t="n">
+      <c r="E16" s="15" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A16,Purchases!J4:J503)</f>
         <v>0</v>
       </c>
-      <c r="F16" s="14" t="n">
+      <c r="F16" s="15" t="n">
         <f aca="false">IF(C16=0,0,E16/C16)</f>
         <v>0</v>
       </c>
+      <c r="H16" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="I16" s="22" t="n">
+        <f aca="false">COUNTIF(Purchases!D4:D503,H16)</f>
+        <v>2</v>
+      </c>
+      <c r="J16" s="23" t="n">
+        <f aca="false">SUMIF(Purchases!D4:D503,H16,Purchases!I4:I503)</f>
+        <v>18.225</v>
+      </c>
+      <c r="K16" s="24" t="n">
+        <f aca="false">SUMIF(Purchases!D4:D503,H16,Purchases!J4:J503)</f>
+        <v>911.25</v>
+      </c>
+      <c r="L16" s="24" t="n">
+        <f aca="false">IF(J16=0,0,K16/J16)</f>
+        <v>50</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="13" t="s">
-        <v>37</v>
-      </c>
-      <c r="B17" s="13" t="n">
+      <c r="A17" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="B17" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A17)</f>
         <v>0</v>
       </c>
-      <c r="C17" s="13" t="n">
+      <c r="C17" s="14" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A17,Purchases!H4:H503)</f>
         <v>0</v>
       </c>
-      <c r="D17" s="13" t="n">
+      <c r="D17" s="14" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A17,Purchases!L4:L503)</f>
         <v>0</v>
       </c>
-      <c r="E17" s="14" t="n">
+      <c r="E17" s="15" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A17,Purchases!J4:J503)</f>
         <v>0</v>
       </c>
-      <c r="F17" s="14" t="n">
+      <c r="F17" s="15" t="n">
         <f aca="false">IF(C17=0,0,E17/C17)</f>
         <v>0</v>
       </c>
+      <c r="H17" s="22" t="s">
+        <v>47</v>
+      </c>
+      <c r="I17" s="22" t="n">
+        <f aca="false">COUNTIF(Purchases!D4:D503,H17)</f>
+        <v>0</v>
+      </c>
+      <c r="J17" s="23" t="n">
+        <f aca="false">SUMIF(Purchases!D4:D503,H17,Purchases!I4:I503)</f>
+        <v>0</v>
+      </c>
+      <c r="K17" s="24" t="n">
+        <f aca="false">SUMIF(Purchases!D4:D503,H17,Purchases!J4:J503)</f>
+        <v>0</v>
+      </c>
+      <c r="L17" s="24" t="n">
+        <f aca="false">IF(J17=0,0,K17/J17)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="13" t="s">
-        <v>38</v>
-      </c>
-      <c r="B18" s="13" t="n">
+      <c r="A18" s="14" t="s">
+        <v>48</v>
+      </c>
+      <c r="B18" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A18)</f>
         <v>0</v>
       </c>
-      <c r="C18" s="13" t="n">
+      <c r="C18" s="14" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A18,Purchases!H4:H503)</f>
         <v>0</v>
       </c>
-      <c r="D18" s="13" t="n">
+      <c r="D18" s="14" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A18,Purchases!L4:L503)</f>
         <v>0</v>
       </c>
-      <c r="E18" s="14" t="n">
+      <c r="E18" s="15" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A18,Purchases!J4:J503)</f>
         <v>0</v>
       </c>
-      <c r="F18" s="14" t="n">
+      <c r="F18" s="15" t="n">
         <f aca="false">IF(C18=0,0,E18/C18)</f>
         <v>0</v>
       </c>
+      <c r="H18" s="22" t="s">
+        <v>49</v>
+      </c>
+      <c r="I18" s="22" t="n">
+        <f aca="false">COUNTIF(Purchases!D4:D503,H18)</f>
+        <v>0</v>
+      </c>
+      <c r="J18" s="23" t="n">
+        <f aca="false">SUMIF(Purchases!D4:D503,H18,Purchases!I4:I503)</f>
+        <v>0</v>
+      </c>
+      <c r="K18" s="24" t="n">
+        <f aca="false">SUMIF(Purchases!D4:D503,H18,Purchases!J4:J503)</f>
+        <v>0</v>
+      </c>
+      <c r="L18" s="24" t="n">
+        <f aca="false">IF(J18=0,0,K18/J18)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="13" t="s">
-        <v>18</v>
-      </c>
-      <c r="B19" s="13" t="n">
+      <c r="A19" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B19" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A19)</f>
         <v>0</v>
       </c>
-      <c r="C19" s="13" t="n">
+      <c r="C19" s="14" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A19,Purchases!H4:H503)</f>
         <v>0</v>
       </c>
-      <c r="D19" s="13" t="n">
+      <c r="D19" s="14" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A19,Purchases!L4:L503)</f>
         <v>0</v>
       </c>
-      <c r="E19" s="14" t="n">
+      <c r="E19" s="15" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A19,Purchases!J4:J503)</f>
         <v>0</v>
       </c>
-      <c r="F19" s="14" t="n">
+      <c r="F19" s="15" t="n">
         <f aca="false">IF(C19=0,0,E19/C19)</f>
         <v>0</v>
       </c>
+      <c r="H19" s="22" t="s">
+        <v>50</v>
+      </c>
+      <c r="I19" s="22" t="n">
+        <f aca="false">COUNTIF(Purchases!D4:D503,H19)</f>
+        <v>0</v>
+      </c>
+      <c r="J19" s="23" t="n">
+        <f aca="false">SUMIF(Purchases!D4:D503,H19,Purchases!I4:I503)</f>
+        <v>0</v>
+      </c>
+      <c r="K19" s="24" t="n">
+        <f aca="false">SUMIF(Purchases!D4:D503,H19,Purchases!J4:J503)</f>
+        <v>0</v>
+      </c>
+      <c r="L19" s="24" t="n">
+        <f aca="false">IF(J19=0,0,K19/J19)</f>
+        <v>0</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B20" s="13" t="n">
+      <c r="A20" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="B20" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A20)</f>
         <v>0</v>
       </c>
-      <c r="C20" s="13" t="n">
+      <c r="C20" s="14" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A20,Purchases!H4:H503)</f>
         <v>0</v>
       </c>
-      <c r="D20" s="13" t="n">
+      <c r="D20" s="14" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A20,Purchases!L4:L503)</f>
         <v>0</v>
       </c>
-      <c r="E20" s="14" t="n">
+      <c r="E20" s="15" t="n">
         <f aca="false">SUMIF(Purchases!C4:C503,A20,Purchases!J4:J503)</f>
         <v>0</v>
       </c>
-      <c r="F20" s="14" t="n">
+      <c r="F20" s="15" t="n">
         <f aca="false">IF(C20=0,0,E20/C20)</f>
         <v>0</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
-        <v>40</v>
+      <c r="A23" s="18" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="19" t="s">
-        <v>41</v>
-      </c>
-      <c r="B24" s="20" t="n">
+      <c r="A24" s="25" t="s">
+        <v>53</v>
+      </c>
+      <c r="B24" s="26" t="n">
         <v>2026</v>
       </c>
-      <c r="C24" s="21" t="s">
+      <c r="C24" s="27" t="s">
+        <v>54</v>
+      </c>
+      <c r="D24" s="25"/>
+      <c r="E24" s="25"/>
+      <c r="F24" s="25"/>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B25" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
-    </row>
-    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
-        <v>43</v>
-      </c>
-      <c r="B25" s="18" t="s">
-        <v>30</v>
-      </c>
-      <c r="C25" s="18" t="s">
-        <v>31</v>
-      </c>
-      <c r="D25" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+      <c r="C25" s="20" t="s">
+        <v>37</v>
+      </c>
+      <c r="D25" s="20" t="s">
+        <v>39</v>
+      </c>
+      <c r="E25" s="25"/>
+      <c r="F25" s="25"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="19" t="s">
-        <v>44</v>
-      </c>
-      <c r="B26" s="19" t="n">
+      <c r="A26" s="25" t="s">
+        <v>56</v>
+      </c>
+      <c r="B26" s="25" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,1,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,1+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C26" s="19" t="n">
+      <c r="C26" s="25" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,1,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,1+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D26" s="22" t="n">
+      <c r="D26" s="28" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,1,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,1+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="E26" s="25"/>
+      <c r="F26" s="25"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="19" t="s">
-        <v>45</v>
-      </c>
-      <c r="B27" s="19" t="n">
+      <c r="A27" s="25" t="s">
+        <v>57</v>
+      </c>
+      <c r="B27" s="25" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,2,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,2+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C27" s="19" t="n">
+      <c r="C27" s="25" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,2,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,2+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D27" s="22" t="n">
+      <c r="D27" s="28" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,2,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,2+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="E27" s="25"/>
+      <c r="F27" s="25"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="19" t="s">
-        <v>46</v>
-      </c>
-      <c r="B28" s="19" t="n">
+      <c r="A28" s="25" t="s">
+        <v>58</v>
+      </c>
+      <c r="B28" s="25" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,3,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,3+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C28" s="19" t="n">
+      <c r="C28" s="25" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,3,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,3+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D28" s="22" t="n">
+      <c r="D28" s="28" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,3,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,3+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
+      <c r="E28" s="25"/>
+      <c r="F28" s="25"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="19" t="s">
-        <v>47</v>
-      </c>
-      <c r="B29" s="19" t="n">
+      <c r="A29" s="25" t="s">
+        <v>59</v>
+      </c>
+      <c r="B29" s="25" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,4,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,4+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C29" s="19" t="n">
+      <c r="C29" s="25" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,4,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,4+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D29" s="22" t="n">
+      <c r="D29" s="28" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,4,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,4+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="19" t="s">
-        <v>48</v>
-      </c>
-      <c r="B30" s="19" t="n">
+      <c r="A30" s="25" t="s">
+        <v>60</v>
+      </c>
+      <c r="B30" s="25" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,5,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,5+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C30" s="19" t="n">
+      <c r="C30" s="25" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,5,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,5+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D30" s="22" t="n">
+      <c r="D30" s="28" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,5,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,5+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
+      <c r="E30" s="25"/>
+      <c r="F30" s="25"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="19" t="s">
-        <v>49</v>
-      </c>
-      <c r="B31" s="19" t="n">
+      <c r="A31" s="25" t="s">
+        <v>61</v>
+      </c>
+      <c r="B31" s="25" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,6,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,6+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C31" s="19" t="n">
+      <c r="C31" s="25" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,6,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,6+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D31" s="22" t="n">
+      <c r="D31" s="28" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,6,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,6+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
+      <c r="E31" s="25"/>
+      <c r="F31" s="25"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="19" t="s">
-        <v>50</v>
-      </c>
-      <c r="B32" s="19" t="n">
+      <c r="A32" s="25" t="s">
+        <v>62</v>
+      </c>
+      <c r="B32" s="25" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,7,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,7+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C32" s="19" t="n">
+      <c r="C32" s="25" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,7,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,7+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D32" s="22" t="n">
+      <c r="D32" s="28" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,7,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,7+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
+      <c r="E32" s="25"/>
+      <c r="F32" s="25"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="19" t="s">
-        <v>51</v>
-      </c>
-      <c r="B33" s="19" t="n">
+      <c r="A33" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="B33" s="25" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,8,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,8+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C33" s="19" t="n">
+      <c r="C33" s="25" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,8,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,8+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D33" s="22" t="n">
+      <c r="D33" s="28" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,8,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,8+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
+      <c r="E33" s="25"/>
+      <c r="F33" s="25"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="19" t="s">
-        <v>52</v>
-      </c>
-      <c r="B34" s="19" t="n">
+      <c r="A34" s="25" t="s">
+        <v>64</v>
+      </c>
+      <c r="B34" s="25" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,9,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,9+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C34" s="19" t="n">
+      <c r="C34" s="25" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,9,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,9+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D34" s="22" t="n">
+      <c r="D34" s="28" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,9,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,9+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
+      <c r="E34" s="25"/>
+      <c r="F34" s="25"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="19" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" s="19" t="n">
+      <c r="A35" s="25" t="s">
+        <v>65</v>
+      </c>
+      <c r="B35" s="25" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,10,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,10+1,1))</f>
-        <v>2</v>
-      </c>
-      <c r="C35" s="19" t="n">
+        <v>5</v>
+      </c>
+      <c r="C35" s="25" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,10,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,10+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D35" s="22" t="n">
+      <c r="D35" s="28" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,10,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,10+1,1))</f>
-        <v>967.5</v>
-      </c>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
+        <v>1882.5</v>
+      </c>
+      <c r="E35" s="25"/>
+      <c r="F35" s="25"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="19" t="s">
-        <v>54</v>
-      </c>
-      <c r="B36" s="19" t="n">
+      <c r="A36" s="25" t="s">
+        <v>66</v>
+      </c>
+      <c r="B36" s="25" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,11,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,11+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C36" s="19" t="n">
+      <c r="C36" s="25" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,11,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,11+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D36" s="22" t="n">
+      <c r="D36" s="28" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,11,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,11+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
+      <c r="E36" s="25"/>
+      <c r="F36" s="25"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="19" t="s">
-        <v>55</v>
-      </c>
-      <c r="B37" s="19" t="n">
+      <c r="A37" s="25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" s="25" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,12,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,12+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C37" s="19" t="n">
+      <c r="C37" s="25" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,12,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,12+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D37" s="22" t="n">
+      <c r="D37" s="28" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,12,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,12+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
+      <c r="E37" s="25"/>
+      <c r="F37" s="25"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="23" t="s">
-        <v>56</v>
-      </c>
-      <c r="B38" s="23" t="n">
+      <c r="A38" s="29" t="s">
+        <v>68</v>
+      </c>
+      <c r="B38" s="29" t="n">
         <f aca="false">SUM(B26:B37)</f>
-        <v>2</v>
-      </c>
-      <c r="C38" s="23" t="n">
+        <v>5</v>
+      </c>
+      <c r="C38" s="29" t="n">
         <f aca="false">SUM(C26:C37)</f>
         <v>0</v>
       </c>
-      <c r="D38" s="24" t="n">
+      <c r="D38" s="30" t="n">
         <f aca="false">SUM(D26:D37)</f>
-        <v>967.5</v>
-      </c>
-      <c r="E38" s="23"/>
-      <c r="F38" s="23"/>
+        <v>1882.5</v>
+      </c>
+      <c r="E38" s="29"/>
+      <c r="F38" s="29"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>

--- a/BW_Scrap_RAM_Purchases.xlsx
+++ b/BW_Scrap_RAM_Purchases.xlsx
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="71">
   <si>
     <t xml:space="preserve">B&amp;W Scrap Yard – RAM Purchase Log</t>
   </si>
@@ -99,6 +99,12 @@
   </si>
   <si>
     <t xml:space="preserve">$50/lb; weight calculated as ($915 - $210) / $50.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17 lbs @ $70/lb. Oct 30 total paid $2,640.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">29 lbs @ $50/lb.</t>
   </si>
   <si>
     <t xml:space="preserve">RAM Purchase Summary</t>
@@ -237,7 +243,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="9">
+  <numFmts count="8">
     <numFmt numFmtId="164" formatCode="General"/>
     <numFmt numFmtId="165" formatCode="mm/dd/yyyy"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
@@ -246,7 +252,6 @@
     <numFmt numFmtId="169" formatCode="General"/>
     <numFmt numFmtId="170" formatCode="#,##0"/>
     <numFmt numFmtId="171" formatCode="#,##0.00"/>
-    <numFmt numFmtId="172" formatCode="\$#,##0.00"/>
   </numFmts>
   <fonts count="14">
     <font>
@@ -412,7 +417,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="26">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -489,27 +494,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="171" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="172" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1112,16 +1097,24 @@
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6"/>
+      <c r="A9" s="6" t="n">
+        <v>46325</v>
+      </c>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
+      <c r="D9" s="7" t="s">
+        <v>18</v>
+      </c>
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
       <c r="H9" s="7"/>
-      <c r="I9" s="12"/>
-      <c r="J9" s="9"/>
+      <c r="I9" s="8" t="n">
+        <v>17</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>1190</v>
+      </c>
       <c r="K9" s="7"/>
       <c r="L9" s="10" t="str">
         <f aca="false">IF(OR(E9="",H9=""),"",E9*H9)</f>
@@ -1131,27 +1124,37 @@
         <f aca="false">IF(OR(J9="",H9="",H9=0),"",J9/H9)</f>
         <v/>
       </c>
-      <c r="N9" s="11" t="str">
+      <c r="N9" s="11" t="n">
         <f aca="false">IF(OR(J9="",I9="",I9=0),"",J9/I9)</f>
-        <v/>
+        <v>70</v>
       </c>
       <c r="O9" s="11" t="str">
         <f aca="false">IF(OR(J9="",L9="",L9=0),"",J9/L9)</f>
         <v/>
       </c>
-      <c r="P9" s="7"/>
+      <c r="P9" s="7" t="s">
+        <v>25</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6"/>
+      <c r="A10" s="6" t="n">
+        <v>46325</v>
+      </c>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
+      <c r="D10" s="7" t="s">
+        <v>21</v>
+      </c>
       <c r="E10" s="7"/>
       <c r="F10" s="7"/>
       <c r="G10" s="7"/>
       <c r="H10" s="7"/>
-      <c r="I10" s="12"/>
-      <c r="J10" s="9"/>
+      <c r="I10" s="8" t="n">
+        <v>29</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>1450</v>
+      </c>
       <c r="K10" s="7"/>
       <c r="L10" s="10" t="str">
         <f aca="false">IF(OR(E10="",H10=""),"",E10*H10)</f>
@@ -1161,15 +1164,17 @@
         <f aca="false">IF(OR(J10="",H10="",H10=0),"",J10/H10)</f>
         <v/>
       </c>
-      <c r="N10" s="11" t="str">
+      <c r="N10" s="11" t="n">
         <f aca="false">IF(OR(J10="",I10="",I10=0),"",J10/I10)</f>
-        <v/>
+        <v>50</v>
       </c>
       <c r="O10" s="11" t="str">
         <f aca="false">IF(OR(J10="",L10="",L10=0),"",J10/L10)</f>
         <v/>
       </c>
-      <c r="P10" s="7"/>
+      <c r="P10" s="7" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="6"/>
@@ -16000,38 +16005,38 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="14"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="3" style="1" width="12"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="5" style="1" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="30"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="0" width="11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="0" width="13"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="0" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="30"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="11"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="11" min="10" style="1" width="13"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="12" min="12" style="1" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="B3" s="14" t="n">
         <f aca="false">COUNT(Purchases!J4:J503)</f>
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="13" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="B4" s="15" t="n">
         <f aca="false">SUM(Purchases!J4:J503)</f>
-        <v>1882.5</v>
+        <v>4522.5</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="13" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="B5" s="16" t="n">
         <f aca="false">SUM(Purchases!H4:H503)</f>
@@ -16040,11 +16045,11 @@
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="B6" s="17" t="n">
         <f aca="false">SUM(Purchases!I4:I503)</f>
-        <v>32.1</v>
+        <v>78.1</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -16058,7 +16063,7 @@
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B8" s="15" t="n">
         <f aca="false">IF(B5=0,0,B4/B5)</f>
@@ -16067,16 +16072,16 @@
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="13" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="B9" s="15" t="n">
         <f aca="false">IF(B6=0,0,B4/B6)</f>
-        <v>58.6448598130841</v>
+        <v>57.9065300896287</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="B10" s="15" t="n">
         <f aca="false">IF(B7=0,0,B4/B7)</f>
@@ -16085,50 +16090,50 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="18" t="s">
-        <v>33</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>34</v>
+        <v>35</v>
+      </c>
+      <c r="H13" s="18" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="20" t="s">
-        <v>35</v>
-      </c>
-      <c r="B14" s="20" t="s">
-        <v>36</v>
-      </c>
-      <c r="C14" s="20" t="s">
+      <c r="A14" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D14" s="20" t="s">
+      <c r="B14" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="E14" s="20" t="s">
+      <c r="C14" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="20" t="s">
+      <c r="D14" s="19" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="21" t="s">
+      <c r="E14" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="I14" s="21" t="s">
+      <c r="F14" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="J14" s="21" t="s">
+      <c r="H14" s="19" t="s">
+        <v>43</v>
+      </c>
+      <c r="I14" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="J14" s="19" t="s">
         <v>10</v>
       </c>
-      <c r="K14" s="21" t="s">
-        <v>39</v>
-      </c>
-      <c r="L14" s="21" t="s">
-        <v>43</v>
+      <c r="K14" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="L14" s="19" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="B15" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A15)</f>
@@ -16150,29 +16155,29 @@
         <f aca="false">IF(C15=0,0,E15/C15)</f>
         <v>0</v>
       </c>
-      <c r="H15" s="22" t="s">
+      <c r="H15" s="14" t="s">
         <v>18</v>
       </c>
-      <c r="I15" s="22" t="n">
+      <c r="I15" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!D4:D503,H15)</f>
-        <v>3</v>
-      </c>
-      <c r="J15" s="23" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="17" t="n">
         <f aca="false">SUMIF(Purchases!D4:D503,H15,Purchases!I4:I503)</f>
-        <v>13.875</v>
-      </c>
-      <c r="K15" s="24" t="n">
+        <v>30.875</v>
+      </c>
+      <c r="K15" s="15" t="n">
         <f aca="false">SUMIF(Purchases!D4:D503,H15,Purchases!J4:J503)</f>
-        <v>971.25</v>
-      </c>
-      <c r="L15" s="24" t="n">
+        <v>2161.25</v>
+      </c>
+      <c r="L15" s="15" t="n">
         <f aca="false">IF(J15=0,0,K15/J15)</f>
         <v>70</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="14" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="B16" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A16)</f>
@@ -16194,29 +16199,29 @@
         <f aca="false">IF(C16=0,0,E16/C16)</f>
         <v>0</v>
       </c>
-      <c r="H16" s="22" t="s">
+      <c r="H16" s="14" t="s">
         <v>21</v>
       </c>
-      <c r="I16" s="22" t="n">
+      <c r="I16" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!D4:D503,H16)</f>
-        <v>2</v>
-      </c>
-      <c r="J16" s="23" t="n">
+        <v>3</v>
+      </c>
+      <c r="J16" s="17" t="n">
         <f aca="false">SUMIF(Purchases!D4:D503,H16,Purchases!I4:I503)</f>
-        <v>18.225</v>
-      </c>
-      <c r="K16" s="24" t="n">
+        <v>47.225</v>
+      </c>
+      <c r="K16" s="15" t="n">
         <f aca="false">SUMIF(Purchases!D4:D503,H16,Purchases!J4:J503)</f>
-        <v>911.25</v>
-      </c>
-      <c r="L16" s="24" t="n">
+        <v>2361.25</v>
+      </c>
+      <c r="L16" s="15" t="n">
         <f aca="false">IF(J16=0,0,K16/J16)</f>
         <v>50</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="14" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="B17" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A17)</f>
@@ -16238,29 +16243,29 @@
         <f aca="false">IF(C17=0,0,E17/C17)</f>
         <v>0</v>
       </c>
-      <c r="H17" s="22" t="s">
-        <v>47</v>
-      </c>
-      <c r="I17" s="22" t="n">
+      <c r="H17" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="I17" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!D4:D503,H17)</f>
         <v>0</v>
       </c>
-      <c r="J17" s="23" t="n">
+      <c r="J17" s="17" t="n">
         <f aca="false">SUMIF(Purchases!D4:D503,H17,Purchases!I4:I503)</f>
         <v>0</v>
       </c>
-      <c r="K17" s="24" t="n">
+      <c r="K17" s="15" t="n">
         <f aca="false">SUMIF(Purchases!D4:D503,H17,Purchases!J4:J503)</f>
         <v>0</v>
       </c>
-      <c r="L17" s="24" t="n">
+      <c r="L17" s="15" t="n">
         <f aca="false">IF(J17=0,0,K17/J17)</f>
         <v>0</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="14" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="B18" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A18)</f>
@@ -16282,29 +16287,29 @@
         <f aca="false">IF(C18=0,0,E18/C18)</f>
         <v>0</v>
       </c>
-      <c r="H18" s="22" t="s">
-        <v>49</v>
-      </c>
-      <c r="I18" s="22" t="n">
+      <c r="H18" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="I18" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!D4:D503,H18)</f>
         <v>0</v>
       </c>
-      <c r="J18" s="23" t="n">
+      <c r="J18" s="17" t="n">
         <f aca="false">SUMIF(Purchases!D4:D503,H18,Purchases!I4:I503)</f>
         <v>0</v>
       </c>
-      <c r="K18" s="24" t="n">
+      <c r="K18" s="15" t="n">
         <f aca="false">SUMIF(Purchases!D4:D503,H18,Purchases!J4:J503)</f>
         <v>0</v>
       </c>
-      <c r="L18" s="24" t="n">
+      <c r="L18" s="15" t="n">
         <f aca="false">IF(J18=0,0,K18/J18)</f>
         <v>0</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="14" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="B19" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A19)</f>
@@ -16326,29 +16331,29 @@
         <f aca="false">IF(C19=0,0,E19/C19)</f>
         <v>0</v>
       </c>
-      <c r="H19" s="22" t="s">
-        <v>50</v>
-      </c>
-      <c r="I19" s="22" t="n">
+      <c r="H19" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!D4:D503,H19)</f>
         <v>0</v>
       </c>
-      <c r="J19" s="23" t="n">
+      <c r="J19" s="17" t="n">
         <f aca="false">SUMIF(Purchases!D4:D503,H19,Purchases!I4:I503)</f>
         <v>0</v>
       </c>
-      <c r="K19" s="24" t="n">
+      <c r="K19" s="15" t="n">
         <f aca="false">SUMIF(Purchases!D4:D503,H19,Purchases!J4:J503)</f>
         <v>0</v>
       </c>
-      <c r="L19" s="24" t="n">
+      <c r="L19" s="15" t="n">
         <f aca="false">IF(J19=0,0,K19/J19)</f>
         <v>0</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="14" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="B20" s="14" t="n">
         <f aca="false">COUNTIF(Purchases!C4:C503,A20)</f>
@@ -16373,285 +16378,285 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="18" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="25" t="s">
-        <v>53</v>
-      </c>
-      <c r="B24" s="26" t="n">
+      <c r="A24" s="20" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="21" t="n">
         <v>2026</v>
       </c>
-      <c r="C24" s="27" t="s">
-        <v>54</v>
-      </c>
-      <c r="D24" s="25"/>
-      <c r="E24" s="25"/>
-      <c r="F24" s="25"/>
+      <c r="C24" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D24" s="20"/>
+      <c r="E24" s="20"/>
+      <c r="F24" s="20"/>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="20" t="s">
-        <v>55</v>
-      </c>
-      <c r="B25" s="20" t="s">
-        <v>42</v>
-      </c>
-      <c r="C25" s="20" t="s">
-        <v>37</v>
-      </c>
-      <c r="D25" s="20" t="s">
+      <c r="A25" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="B25" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="C25" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="E25" s="25"/>
-      <c r="F25" s="25"/>
+      <c r="D25" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="E25" s="20"/>
+      <c r="F25" s="20"/>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="25" t="s">
-        <v>56</v>
-      </c>
-      <c r="B26" s="25" t="n">
+      <c r="A26" s="20" t="s">
+        <v>58</v>
+      </c>
+      <c r="B26" s="20" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,1,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,1+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C26" s="25" t="n">
+      <c r="C26" s="20" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,1,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,1+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D26" s="28" t="n">
+      <c r="D26" s="23" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,1,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,1+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E26" s="25"/>
-      <c r="F26" s="25"/>
+      <c r="E26" s="20"/>
+      <c r="F26" s="20"/>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="25" t="s">
-        <v>57</v>
-      </c>
-      <c r="B27" s="25" t="n">
+      <c r="A27" s="20" t="s">
+        <v>59</v>
+      </c>
+      <c r="B27" s="20" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,2,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,2+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C27" s="25" t="n">
+      <c r="C27" s="20" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,2,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,2+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D27" s="28" t="n">
+      <c r="D27" s="23" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,2,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,2+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E27" s="25"/>
-      <c r="F27" s="25"/>
+      <c r="E27" s="20"/>
+      <c r="F27" s="20"/>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="25" t="s">
-        <v>58</v>
-      </c>
-      <c r="B28" s="25" t="n">
+      <c r="A28" s="20" t="s">
+        <v>60</v>
+      </c>
+      <c r="B28" s="20" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,3,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,3+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C28" s="25" t="n">
+      <c r="C28" s="20" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,3,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,3+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D28" s="28" t="n">
+      <c r="D28" s="23" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,3,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,3+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E28" s="25"/>
-      <c r="F28" s="25"/>
+      <c r="E28" s="20"/>
+      <c r="F28" s="20"/>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="25" t="s">
-        <v>59</v>
-      </c>
-      <c r="B29" s="25" t="n">
+      <c r="A29" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="B29" s="20" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,4,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,4+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C29" s="25" t="n">
+      <c r="C29" s="20" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,4,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,4+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D29" s="28" t="n">
+      <c r="D29" s="23" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,4,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,4+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E29" s="25"/>
-      <c r="F29" s="25"/>
+      <c r="E29" s="20"/>
+      <c r="F29" s="20"/>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="25" t="s">
-        <v>60</v>
-      </c>
-      <c r="B30" s="25" t="n">
+      <c r="A30" s="20" t="s">
+        <v>62</v>
+      </c>
+      <c r="B30" s="20" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,5,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,5+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C30" s="25" t="n">
+      <c r="C30" s="20" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,5,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,5+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D30" s="28" t="n">
+      <c r="D30" s="23" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,5,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,5+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E30" s="25"/>
-      <c r="F30" s="25"/>
+      <c r="E30" s="20"/>
+      <c r="F30" s="20"/>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="25" t="s">
-        <v>61</v>
-      </c>
-      <c r="B31" s="25" t="n">
+      <c r="A31" s="20" t="s">
+        <v>63</v>
+      </c>
+      <c r="B31" s="20" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,6,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,6+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C31" s="25" t="n">
+      <c r="C31" s="20" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,6,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,6+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D31" s="28" t="n">
+      <c r="D31" s="23" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,6,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,6+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E31" s="25"/>
-      <c r="F31" s="25"/>
+      <c r="E31" s="20"/>
+      <c r="F31" s="20"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="25" t="s">
-        <v>62</v>
-      </c>
-      <c r="B32" s="25" t="n">
+      <c r="A32" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="B32" s="20" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,7,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,7+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C32" s="25" t="n">
+      <c r="C32" s="20" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,7,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,7+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D32" s="28" t="n">
+      <c r="D32" s="23" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,7,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,7+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E32" s="25"/>
-      <c r="F32" s="25"/>
+      <c r="E32" s="20"/>
+      <c r="F32" s="20"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="B33" s="25" t="n">
+      <c r="A33" s="20" t="s">
+        <v>65</v>
+      </c>
+      <c r="B33" s="20" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,8,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,8+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C33" s="25" t="n">
+      <c r="C33" s="20" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,8,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,8+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D33" s="28" t="n">
+      <c r="D33" s="23" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,8,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,8+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E33" s="25"/>
-      <c r="F33" s="25"/>
+      <c r="E33" s="20"/>
+      <c r="F33" s="20"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="25" t="s">
-        <v>64</v>
-      </c>
-      <c r="B34" s="25" t="n">
+      <c r="A34" s="20" t="s">
+        <v>66</v>
+      </c>
+      <c r="B34" s="20" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,9,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,9+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C34" s="25" t="n">
+      <c r="C34" s="20" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,9,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,9+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D34" s="28" t="n">
+      <c r="D34" s="23" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,9,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,9+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E34" s="25"/>
-      <c r="F34" s="25"/>
+      <c r="E34" s="20"/>
+      <c r="F34" s="20"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="25" t="s">
-        <v>65</v>
-      </c>
-      <c r="B35" s="25" t="n">
+      <c r="A35" s="20" t="s">
+        <v>67</v>
+      </c>
+      <c r="B35" s="20" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,10,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,10+1,1))</f>
-        <v>5</v>
-      </c>
-      <c r="C35" s="25" t="n">
+        <v>7</v>
+      </c>
+      <c r="C35" s="20" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,10,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,10+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D35" s="28" t="n">
+      <c r="D35" s="23" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,10,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,10+1,1))</f>
-        <v>1882.5</v>
-      </c>
-      <c r="E35" s="25"/>
-      <c r="F35" s="25"/>
+        <v>4522.5</v>
+      </c>
+      <c r="E35" s="20"/>
+      <c r="F35" s="20"/>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="B36" s="25" t="n">
+      <c r="A36" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="B36" s="20" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,11,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,11+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C36" s="25" t="n">
+      <c r="C36" s="20" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,11,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,11+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D36" s="28" t="n">
+      <c r="D36" s="23" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,11,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,11+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E36" s="25"/>
-      <c r="F36" s="25"/>
+      <c r="E36" s="20"/>
+      <c r="F36" s="20"/>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="25" t="s">
-        <v>67</v>
-      </c>
-      <c r="B37" s="25" t="n">
+      <c r="A37" s="20" t="s">
+        <v>69</v>
+      </c>
+      <c r="B37" s="20" t="n">
         <f aca="false">COUNTIFS(Purchases!A4:A503,"&gt;="&amp;DATE($B$24,12,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,12+1,1))</f>
         <v>0</v>
       </c>
-      <c r="C37" s="25" t="n">
+      <c r="C37" s="20" t="n">
         <f aca="false">SUMIFS(Purchases!H4:H503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,12,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,12+1,1))</f>
         <v>0</v>
       </c>
-      <c r="D37" s="28" t="n">
+      <c r="D37" s="23" t="n">
         <f aca="false">SUMIFS(Purchases!J4:J503,Purchases!A4:A503,"&gt;="&amp;DATE($B$24,12,1),Purchases!A4:A503,"&lt;"&amp;DATE($B$24,12+1,1))</f>
         <v>0</v>
       </c>
-      <c r="E37" s="25"/>
-      <c r="F37" s="25"/>
+      <c r="E37" s="20"/>
+      <c r="F37" s="20"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="B38" s="29" t="n">
+      <c r="A38" s="24" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" s="24" t="n">
         <f aca="false">SUM(B26:B37)</f>
-        <v>5</v>
-      </c>
-      <c r="C38" s="29" t="n">
+        <v>7</v>
+      </c>
+      <c r="C38" s="24" t="n">
         <f aca="false">SUM(C26:C37)</f>
         <v>0</v>
       </c>
-      <c r="D38" s="30" t="n">
+      <c r="D38" s="25" t="n">
         <f aca="false">SUM(D26:D37)</f>
-        <v>1882.5</v>
-      </c>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
+        <v>4522.5</v>
+      </c>
+      <c r="E38" s="24"/>
+      <c r="F38" s="24"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
